--- a/WWW.xlsx
+++ b/WWW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B05F2F-89B1-42FB-BF05-8B9794A988BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB8E4A8-60EB-46DE-B3DC-E8FD6BD27FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{BF6AB992-A367-41FE-B952-7A79782DC4DD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>Wolverine World Wide</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -679,7 +682,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -687,10 +690,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="3">
-        <v>81.967896999999994</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -699,7 +702,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>1475.4221459999999</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -707,10 +710,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>133.9</v>
+        <v>206.3</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -718,11 +721,11 @@
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <f>546.4+130</f>
-        <v>676.4</v>
+        <f>75+546.7</f>
+        <v>621.70000000000005</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -731,7 +734,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>2017.9221459999999</v>
+        <v>2053.4</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -819,6 +822,9 @@
       <c r="P2" s="4" t="s">
         <v>19</v>
       </c>
+      <c r="Q2" s="14" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="3" spans="1:53" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -843,7 +849,9 @@
       <c r="I3" s="3">
         <v>352.8</v>
       </c>
-      <c r="J3" s="3"/>
+      <c r="J3" s="3">
+        <v>372.7</v>
+      </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -854,7 +862,9 @@
       <c r="P3" s="3">
         <v>1246.0999999999999</v>
       </c>
-      <c r="Q3" s="3"/>
+      <c r="Q3" s="3">
+        <v>1407.8</v>
+      </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -915,7 +925,9 @@
       <c r="I4" s="3">
         <v>105.9</v>
       </c>
-      <c r="J4" s="3"/>
+      <c r="J4" s="3">
+        <v>134</v>
+      </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -926,7 +938,9 @@
       <c r="P4" s="3">
         <v>455.3</v>
       </c>
-      <c r="Q4" s="3"/>
+      <c r="Q4" s="3">
+        <v>422.2</v>
+      </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
@@ -987,7 +1001,9 @@
       <c r="I5" s="3">
         <v>11.6</v>
       </c>
-      <c r="J5" s="3"/>
+      <c r="J5" s="3">
+        <v>10.8</v>
+      </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -998,7 +1014,9 @@
       <c r="P5" s="3">
         <v>53.6</v>
       </c>
-      <c r="Q5" s="3"/>
+      <c r="Q5" s="3">
+        <v>44.3</v>
+      </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
@@ -1059,7 +1077,9 @@
       <c r="I6" s="3">
         <v>363.5</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="3">
+        <v>160.69999999999999</v>
+      </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -1075,7 +1095,9 @@
         <f>430.4+45.4+8.1</f>
         <v>483.9</v>
       </c>
-      <c r="Q6" s="3"/>
+      <c r="Q6" s="3">
+        <v>475.5</v>
+      </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
@@ -1136,7 +1158,10 @@
       <c r="I7" s="3">
         <v>106.8</v>
       </c>
-      <c r="J7" s="3"/>
+      <c r="J7" s="3">
+        <f>+J8-J6</f>
+        <v>356.8</v>
+      </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -1152,7 +1177,10 @@
         <f>815.7+409.9+45.5</f>
         <v>1271.0999999999999</v>
       </c>
-      <c r="Q7" s="3"/>
+      <c r="Q7" s="3">
+        <f>+Q8-Q6</f>
+        <v>1398.8</v>
+      </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
@@ -1213,7 +1241,9 @@
       <c r="I8" s="7">
         <v>470.3</v>
       </c>
-      <c r="J8" s="3"/>
+      <c r="J8" s="7">
+        <v>517.5</v>
+      </c>
       <c r="K8" s="3"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
@@ -1226,7 +1256,9 @@
       <c r="P8" s="7">
         <v>1755</v>
       </c>
-      <c r="Q8" s="3"/>
+      <c r="Q8" s="7">
+        <v>1874.3</v>
+      </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -1287,7 +1319,9 @@
       <c r="I9" s="3">
         <v>247.1</v>
       </c>
-      <c r="J9" s="3"/>
+      <c r="J9" s="3">
+        <v>274.10000000000002</v>
+      </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -1300,7 +1334,9 @@
       <c r="P9" s="3">
         <v>973.5</v>
       </c>
-      <c r="Q9" s="3"/>
+      <c r="Q9" s="3">
+        <v>987.6</v>
+      </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
@@ -1372,7 +1408,7 @@
       </c>
       <c r="J10" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>243.39999999999998</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1392,7 +1428,10 @@
         <f>+P8-P9</f>
         <v>781.5</v>
       </c>
-      <c r="Q10" s="3"/>
+      <c r="Q10" s="3">
+        <f>+Q8-Q9</f>
+        <v>886.69999999999993</v>
+      </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
@@ -1453,7 +1492,9 @@
       <c r="I11" s="3">
         <v>183.1</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="J11" s="3">
+        <v>192.4</v>
+      </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1466,7 +1507,9 @@
       <c r="P11" s="3">
         <v>690</v>
       </c>
-      <c r="Q11" s="3"/>
+      <c r="Q11" s="3">
+        <v>729.9</v>
+      </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
@@ -1527,7 +1570,9 @@
       <c r="I12" s="3">
         <v>0</v>
       </c>
-      <c r="J12" s="3"/>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -1540,7 +1585,9 @@
       <c r="P12" s="3">
         <v>-8.5</v>
       </c>
-      <c r="Q12" s="3"/>
+      <c r="Q12" s="3">
+        <v>0</v>
+      </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
@@ -1601,7 +1648,9 @@
       <c r="I13" s="3">
         <v>0</v>
       </c>
-      <c r="J13" s="3"/>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -1614,7 +1663,9 @@
       <c r="P13" s="3">
         <v>9.3000000000000007</v>
       </c>
-      <c r="Q13" s="3"/>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
@@ -1675,7 +1726,9 @@
       <c r="I14" s="3">
         <v>0.5</v>
       </c>
-      <c r="J14" s="3"/>
+      <c r="J14" s="3">
+        <v>2.1</v>
+      </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -1688,7 +1741,9 @@
       <c r="P14" s="3">
         <v>-10.3</v>
       </c>
-      <c r="Q14" s="3"/>
+      <c r="Q14" s="3">
+        <v>6.6</v>
+      </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -1760,7 +1815,7 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>48.899999999999977</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1780,7 +1835,10 @@
         <f>+P10-SUM(P11:P14)</f>
         <v>101</v>
       </c>
-      <c r="Q15" s="3"/>
+      <c r="Q15" s="3">
+        <f>+Q10-SUM(Q11:Q14)</f>
+        <v>150.19999999999993</v>
+      </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
@@ -1841,7 +1899,9 @@
       <c r="I16" s="3">
         <v>8.1</v>
       </c>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3">
+        <v>8.1999999999999993</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -1854,7 +1914,9 @@
       <c r="P16" s="3">
         <v>42.7</v>
       </c>
-      <c r="Q16" s="3"/>
+      <c r="Q16" s="3">
+        <v>32.799999999999997</v>
+      </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
@@ -1915,7 +1977,9 @@
       <c r="I17" s="3">
         <v>-1.6</v>
       </c>
-      <c r="J17" s="3"/>
+      <c r="J17" s="3">
+        <v>0.4</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -1928,7 +1992,9 @@
       <c r="P17" s="3">
         <v>-3.3</v>
       </c>
-      <c r="Q17" s="3"/>
+      <c r="Q17" s="3">
+        <v>-4.0999999999999996</v>
+      </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
@@ -2000,7 +2066,7 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>40.299999999999976</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -2020,7 +2086,10 @@
         <f>+P15-SUM(P16:P17)</f>
         <v>61.599999999999994</v>
       </c>
-      <c r="Q18" s="3"/>
+      <c r="Q18" s="3">
+        <f>+Q15-SUM(Q16:Q17)</f>
+        <v>121.49999999999994</v>
+      </c>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
@@ -2081,7 +2150,9 @@
       <c r="I19" s="3">
         <v>6.8</v>
       </c>
-      <c r="J19" s="3"/>
+      <c r="J19" s="3">
+        <v>7.8</v>
+      </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -2094,7 +2165,9 @@
       <c r="P19" s="3">
         <v>10.1</v>
       </c>
-      <c r="Q19" s="3"/>
+      <c r="Q19" s="3">
+        <v>20.5</v>
+      </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
@@ -2166,7 +2239,7 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>32.499999999999979</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
@@ -2186,7 +2259,10 @@
         <f>+P18-P19</f>
         <v>51.499999999999993</v>
       </c>
-      <c r="Q20" s="3"/>
+      <c r="Q20" s="3">
+        <f>+Q18-Q19</f>
+        <v>100.99999999999994</v>
+      </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
@@ -2247,7 +2323,9 @@
       <c r="I21" s="3">
         <v>1.2</v>
       </c>
-      <c r="J21" s="3"/>
+      <c r="J21" s="3">
+        <v>0.7</v>
+      </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -2260,7 +2338,9 @@
       <c r="P21" s="3">
         <v>3.6</v>
       </c>
-      <c r="Q21" s="3"/>
+      <c r="Q21" s="3">
+        <v>5.2</v>
+      </c>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
@@ -2332,7 +2412,7 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>31.799999999999979</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
@@ -2352,7 +2432,10 @@
         <f>+P20-P21</f>
         <v>47.899999999999991</v>
       </c>
-      <c r="Q22" s="3"/>
+      <c r="Q22" s="3">
+        <f>+Q20-Q21</f>
+        <v>95.79999999999994</v>
+      </c>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
@@ -2475,9 +2558,9 @@
         <f t="shared" si="10"/>
         <v>0.30759803921568657</v>
       </c>
-      <c r="J24" s="8" t="e">
+      <c r="J24" s="8">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>0.38827838827838801</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
@@ -2497,7 +2580,10 @@
         <f>+P22/P25</f>
         <v>0.59874999999999989</v>
       </c>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="8">
+        <f>+Q22/Q25</f>
+        <v>1.1725826193390445</v>
+      </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
@@ -2558,7 +2644,9 @@
       <c r="I25" s="3">
         <v>81.599999999999994</v>
       </c>
-      <c r="J25" s="3"/>
+      <c r="J25" s="3">
+        <v>81.900000000000006</v>
+      </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -2571,7 +2659,9 @@
       <c r="P25" s="3">
         <v>80</v>
       </c>
-      <c r="Q25" s="3"/>
+      <c r="Q25" s="3">
+        <v>81.7</v>
+      </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
@@ -2704,10 +2794,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" ref="P27:P31" si="17">+P3/O3-1</f>
+        <f t="shared" ref="P27:Q31" si="17">+P3/O3-1</f>
         <v>-0.1341115975262317</v>
       </c>
-      <c r="Q27" s="3"/>
+      <c r="Q27" s="9">
+        <f t="shared" si="17"/>
+        <v>0.12976486638311546</v>
+      </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
@@ -2790,7 +2883,10 @@
         <f t="shared" si="17"/>
         <v>-5.2642530170620039E-2</v>
       </c>
-      <c r="Q28" s="3"/>
+      <c r="Q28" s="9">
+        <f t="shared" si="17"/>
+        <v>-7.2699319130243856E-2</v>
+      </c>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
@@ -2873,7 +2969,10 @@
         <f t="shared" si="17"/>
         <v>-0.83415841584158412</v>
       </c>
-      <c r="Q29" s="3"/>
+      <c r="Q29" s="9">
+        <f t="shared" si="17"/>
+        <v>-0.17350746268656725</v>
+      </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -2956,7 +3055,10 @@
         <f t="shared" si="17"/>
         <v>-0.16912774725274726</v>
       </c>
-      <c r="Q30" s="3"/>
+      <c r="Q30" s="9">
+        <f t="shared" si="17"/>
+        <v>-1.7358958462492247E-2</v>
+      </c>
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
@@ -3039,7 +3141,10 @@
         <f t="shared" si="17"/>
         <v>-0.23450767841011744</v>
       </c>
-      <c r="Q31" s="3"/>
+      <c r="Q31" s="9">
+        <f t="shared" si="17"/>
+        <v>0.1004641648965463</v>
+      </c>
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
@@ -3119,7 +3224,10 @@
         <f>+P8/O8-1</f>
         <v>-0.21753087520620629</v>
       </c>
-      <c r="Q32" s="3"/>
+      <c r="Q32" s="10">
+        <f>+Q8/P8-1</f>
+        <v>6.7977207977207854E-2</v>
+      </c>
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
@@ -3189,9 +3297,9 @@
         <f t="shared" si="20"/>
         <v>0.47459068679566235</v>
       </c>
-      <c r="J33" s="9" t="e">
+      <c r="J33" s="9">
         <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
+        <v>0.47033816425120767</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="9" t="e">
@@ -3214,7 +3322,10 @@
         <f>+P10/P8</f>
         <v>0.44529914529914527</v>
       </c>
-      <c r="Q33" s="3"/>
+      <c r="Q33" s="9">
+        <f>+Q10/Q8</f>
+        <v>0.47308328442618575</v>
+      </c>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
@@ -3284,9 +3395,9 @@
         <f t="shared" si="22"/>
         <v>8.4201573463746585E-2</v>
       </c>
-      <c r="J34" s="9" t="e">
+      <c r="J34" s="9">
         <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
+        <v>9.4492753623188361E-2</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="9" t="e">
@@ -3309,7 +3420,10 @@
         <f>+P15/P8</f>
         <v>5.7549857549857551E-2</v>
       </c>
-      <c r="Q34" s="3"/>
+      <c r="Q34" s="9">
+        <f>+Q15/Q8</f>
+        <v>8.0136584324814561E-2</v>
+      </c>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
@@ -3379,9 +3493,9 @@
         <f t="shared" si="24"/>
         <v>0.20543806646525664</v>
       </c>
-      <c r="J35" s="9" t="e">
+      <c r="J35" s="9">
         <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
+        <v>0.1935483870967743</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="9" t="e">
@@ -3404,7 +3518,10 @@
         <f>+P19/P18</f>
         <v>0.16396103896103897</v>
       </c>
-      <c r="Q35" s="3"/>
+      <c r="Q35" s="9">
+        <f>+Q19/Q18</f>
+        <v>0.16872427983539104</v>
+      </c>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>

--- a/WWW.xlsx
+++ b/WWW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB8E4A8-60EB-46DE-B3DC-E8FD6BD27FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE02BCF-C7EF-4F5E-8EE8-FDC6EFE087AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{BF6AB992-A367-41FE-B952-7A79782DC4DD}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>Wolverine World Wide</t>
   </si>
@@ -209,6 +209,18 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -218,13 +230,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -301,28 +319,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -682,7 +703,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>20</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -690,10 +711,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="3">
-        <v>81.900000000000006</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>55</v>
+        <v>81.989541000000003</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -702,7 +723,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>1638</v>
+        <v>1258.5394543499999</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -710,10 +731,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>206.3</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>55</v>
+        <v>119.6</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -721,11 +742,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <f>75+546.7</f>
-        <v>621.70000000000005</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>55</v>
+        <v>546.9</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -734,7 +754,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>2053.4</v>
+        <v>1685.8394543499999</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -769,7 +789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEAE483-AC6A-456C-A62D-6F90DD190CC4}">
-  <dimension ref="A1:BA515"/>
+  <dimension ref="A1:BE515"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -777,12 +797,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.2">
       <c r="C2" s="11" t="s">
         <v>49</v>
       </c>
@@ -807,26 +827,38 @@
       <c r="J2" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="S2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="T2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="U2" s="14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
@@ -852,23 +884,25 @@
       <c r="J3" s="3">
         <v>372.7</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>371.6</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="3">
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3">
         <v>1439.1</v>
       </c>
-      <c r="P3" s="3">
+      <c r="T3" s="3">
         <v>1246.0999999999999</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="U3" s="3">
         <v>1407.8</v>
       </c>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
@@ -901,8 +935,12 @@
       <c r="AY3" s="3"/>
       <c r="AZ3" s="3"/>
       <c r="BA3" s="3"/>
-    </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB3" s="3"/>
+      <c r="BC3" s="3"/>
+      <c r="BD3" s="3"/>
+      <c r="BE3" s="3"/>
+    </row>
+    <row r="4" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
@@ -928,23 +966,25 @@
       <c r="J4" s="3">
         <v>134</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>75.7</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="3">
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3">
         <v>480.6</v>
       </c>
-      <c r="P4" s="3">
+      <c r="T4" s="3">
         <v>455.3</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="U4" s="3">
         <v>422.2</v>
       </c>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
@@ -977,8 +1017,12 @@
       <c r="AY4" s="3"/>
       <c r="AZ4" s="3"/>
       <c r="BA4" s="3"/>
-    </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB4" s="3"/>
+      <c r="BC4" s="3"/>
+      <c r="BD4" s="3"/>
+      <c r="BE4" s="3"/>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
@@ -1004,23 +1048,25 @@
       <c r="J5" s="3">
         <v>10.8</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>10.3</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="3">
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3">
         <v>323.2</v>
       </c>
-      <c r="P5" s="3">
+      <c r="T5" s="3">
         <v>53.6</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="U5" s="3">
         <v>44.3</v>
       </c>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
@@ -1053,8 +1099,12 @@
       <c r="AY5" s="3"/>
       <c r="AZ5" s="3"/>
       <c r="BA5" s="3"/>
-    </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB5" s="3"/>
+      <c r="BC5" s="3"/>
+      <c r="BD5" s="3"/>
+      <c r="BE5" s="3"/>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>38</v>
       </c>
@@ -1080,28 +1130,30 @@
       <c r="J6" s="3">
         <v>160.69999999999999</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>99.1</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="3">
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3">
         <f>483.6+58.5+149.7</f>
         <v>691.8</v>
       </c>
-      <c r="O6" s="3">
+      <c r="S6" s="3">
         <f>440+52+90.4</f>
         <v>582.4</v>
       </c>
-      <c r="P6" s="3">
+      <c r="T6" s="3">
         <f>430.4+45.4+8.1</f>
         <v>483.9</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="U6" s="3">
         <v>475.5</v>
       </c>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
@@ -1134,8 +1186,12 @@
       <c r="AY6" s="3"/>
       <c r="AZ6" s="3"/>
       <c r="BA6" s="3"/>
-    </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB6" s="3"/>
+      <c r="BC6" s="3"/>
+      <c r="BD6" s="3"/>
+      <c r="BE6" s="3"/>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
@@ -1162,29 +1218,32 @@
         <f>+J8-J6</f>
         <v>356.8</v>
       </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <f>+K8-K6</f>
+        <v>358.5</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="3">
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3">
         <f>1086.6+532+374.4</f>
         <v>1993</v>
       </c>
-      <c r="O7" s="3">
+      <c r="S7" s="3">
         <f>999.1+428.6+232.8</f>
         <v>1660.5</v>
       </c>
-      <c r="P7" s="3">
+      <c r="T7" s="3">
         <f>815.7+409.9+45.5</f>
         <v>1271.0999999999999</v>
       </c>
-      <c r="Q7" s="3">
-        <f>+Q8-Q6</f>
+      <c r="U7" s="3">
+        <f>+U8-U6</f>
         <v>1398.8</v>
       </c>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
@@ -1217,8 +1276,12 @@
       <c r="AY7" s="3"/>
       <c r="AZ7" s="3"/>
       <c r="BA7" s="3"/>
-    </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB7" s="3"/>
+      <c r="BC7" s="3"/>
+      <c r="BD7" s="3"/>
+      <c r="BE7" s="3"/>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1244,25 +1307,27 @@
       <c r="J8" s="7">
         <v>517.5</v>
       </c>
-      <c r="K8" s="3"/>
+      <c r="K8" s="7">
+        <v>457.6</v>
+      </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
-      <c r="N8" s="7">
+      <c r="N8" s="7"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7">
         <v>2684.8</v>
       </c>
-      <c r="O8" s="7">
+      <c r="S8" s="7">
         <v>2242.9</v>
       </c>
-      <c r="P8" s="7">
+      <c r="T8" s="7">
         <v>1755</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="U8" s="7">
         <v>1874.3</v>
       </c>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
@@ -1295,8 +1360,12 @@
       <c r="AY8" s="3"/>
       <c r="AZ8" s="3"/>
       <c r="BA8" s="3"/>
-    </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB8" s="3"/>
+      <c r="BC8" s="3"/>
+      <c r="BD8" s="3"/>
+      <c r="BE8" s="3"/>
+    </row>
+    <row r="9" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
@@ -1322,25 +1391,27 @@
       <c r="J9" s="3">
         <v>274.10000000000002</v>
       </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>239.8</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="3">
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3">
         <v>1614.4</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>1370.4</v>
       </c>
-      <c r="P9" s="3">
+      <c r="T9" s="3">
         <v>973.5</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>987.6</v>
       </c>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
@@ -1373,13 +1444,17 @@
       <c r="AY9" s="3"/>
       <c r="AZ9" s="3"/>
       <c r="BA9" s="3"/>
-    </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB9" s="3"/>
+      <c r="BC9" s="3"/>
+      <c r="BD9" s="3"/>
+      <c r="BE9" s="3"/>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C10" s="3">
-        <f t="shared" ref="C10:J10" si="0">+C8-C9</f>
+        <f t="shared" ref="C10:K10" si="0">+C8-C9</f>
         <v>181.39999999999998</v>
       </c>
       <c r="D10" s="3">
@@ -1410,32 +1485,35 @@
         <f t="shared" si="0"/>
         <v>243.39999999999998</v>
       </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <f t="shared" si="0"/>
+        <v>217.8</v>
+      </c>
       <c r="L10" s="3"/>
-      <c r="M10" s="3">
-        <f t="shared" ref="M10:O10" si="1">+M8-M9</f>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3">
+        <f t="shared" ref="Q10:S10" si="1">+Q8-Q9</f>
         <v>0</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <f t="shared" si="1"/>
         <v>1070.4000000000001</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <f t="shared" si="1"/>
         <v>872.5</v>
       </c>
-      <c r="P10" s="3">
-        <f>+P8-P9</f>
+      <c r="T10" s="3">
+        <f>+T8-T9</f>
         <v>781.5</v>
       </c>
-      <c r="Q10" s="3">
-        <f>+Q8-Q9</f>
+      <c r="U10" s="3">
+        <f>+U8-U9</f>
         <v>886.69999999999993</v>
       </c>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
@@ -1468,8 +1546,12 @@
       <c r="AY10" s="3"/>
       <c r="AZ10" s="3"/>
       <c r="BA10" s="3"/>
-    </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB10" s="3"/>
+      <c r="BC10" s="3"/>
+      <c r="BD10" s="3"/>
+      <c r="BE10" s="3"/>
+    </row>
+    <row r="11" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1495,25 +1577,27 @@
       <c r="J11" s="3">
         <v>192.4</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>182.7</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="3">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3">
         <v>906.4</v>
       </c>
-      <c r="O11" s="3">
+      <c r="S11" s="3">
         <v>856.2</v>
       </c>
-      <c r="P11" s="3">
+      <c r="T11" s="3">
         <v>690</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="U11" s="3">
         <v>729.9</v>
       </c>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
@@ -1546,8 +1630,12 @@
       <c r="AY11" s="3"/>
       <c r="AZ11" s="3"/>
       <c r="BA11" s="3"/>
-    </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB11" s="3"/>
+      <c r="BC11" s="3"/>
+      <c r="BD11" s="3"/>
+      <c r="BE11" s="3"/>
+    </row>
+    <row r="12" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1573,25 +1661,27 @@
       <c r="J12" s="3">
         <v>0</v>
       </c>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="3">
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3">
         <v>-90</v>
       </c>
-      <c r="O12" s="3">
+      <c r="S12" s="3">
         <v>-90.4</v>
       </c>
-      <c r="P12" s="3">
+      <c r="T12" s="3">
         <v>-8.5</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="U12" s="3">
         <v>0</v>
       </c>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
@@ -1624,8 +1714,12 @@
       <c r="AY12" s="3"/>
       <c r="AZ12" s="3"/>
       <c r="BA12" s="3"/>
-    </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB12" s="3"/>
+      <c r="BC12" s="3"/>
+      <c r="BD12" s="3"/>
+      <c r="BE12" s="3"/>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1651,25 +1745,27 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="3">
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3">
         <v>428.7</v>
       </c>
-      <c r="O13" s="3">
+      <c r="S13" s="3">
         <v>185.3</v>
       </c>
-      <c r="P13" s="3">
+      <c r="T13" s="3">
         <v>9.3000000000000007</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="U13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
@@ -1702,8 +1798,12 @@
       <c r="AY13" s="3"/>
       <c r="AZ13" s="3"/>
       <c r="BA13" s="3"/>
-    </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB13" s="3"/>
+      <c r="BC13" s="3"/>
+      <c r="BD13" s="3"/>
+      <c r="BE13" s="3"/>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1729,25 +1829,27 @@
       <c r="J14" s="3">
         <v>2.1</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>1.2</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="3">
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3">
         <v>33.700000000000003</v>
       </c>
-      <c r="O14" s="3">
+      <c r="S14" s="3">
         <v>-10.4</v>
       </c>
-      <c r="P14" s="3">
+      <c r="T14" s="3">
         <v>-10.3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="U14" s="3">
         <v>6.6</v>
       </c>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
@@ -1780,13 +1882,17 @@
       <c r="AY14" s="3"/>
       <c r="AZ14" s="3"/>
       <c r="BA14" s="3"/>
-    </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB14" s="3"/>
+      <c r="BC14" s="3"/>
+      <c r="BD14" s="3"/>
+      <c r="BE14" s="3"/>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" ref="C15:J15" si="2">+C10-SUM(C11:C14)</f>
+        <f t="shared" ref="C15:I15" si="2">+C10-SUM(C11:C14)</f>
         <v>-3.1000000000000227</v>
       </c>
       <c r="D15" s="3">
@@ -1814,35 +1920,38 @@
         <v>39.600000000000023</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="2"/>
+        <f>+J10-SUM(J11:J14)</f>
         <v>48.899999999999977</v>
       </c>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <f>+K10-SUM(K11:K14)</f>
+        <v>33.900000000000034</v>
+      </c>
       <c r="L15" s="3"/>
-      <c r="M15" s="3">
-        <f t="shared" ref="M15:O15" si="3">+M10-SUM(M11:M14)</f>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3">
+        <f t="shared" ref="Q15:S15" si="3">+Q10-SUM(Q11:Q14)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="3">
+      <c r="R15" s="3">
         <f t="shared" si="3"/>
         <v>-208.39999999999986</v>
       </c>
-      <c r="O15" s="3">
+      <c r="S15" s="3">
         <f t="shared" si="3"/>
         <v>-68.200000000000159</v>
       </c>
-      <c r="P15" s="3">
-        <f>+P10-SUM(P11:P14)</f>
+      <c r="T15" s="3">
+        <f>+T10-SUM(T11:T14)</f>
         <v>101</v>
       </c>
-      <c r="Q15" s="3">
-        <f>+Q10-SUM(Q11:Q14)</f>
+      <c r="U15" s="3">
+        <f>+U10-SUM(U11:U14)</f>
         <v>150.19999999999993</v>
       </c>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
@@ -1875,8 +1984,12 @@
       <c r="AY15" s="3"/>
       <c r="AZ15" s="3"/>
       <c r="BA15" s="3"/>
-    </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="BB15" s="3"/>
+      <c r="BC15" s="3"/>
+      <c r="BD15" s="3"/>
+      <c r="BE15" s="3"/>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
@@ -1902,25 +2015,27 @@
       <c r="J16" s="3">
         <v>8.1999999999999993</v>
       </c>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3">
+        <v>6.5</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="3">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3">
         <v>47.3</v>
       </c>
-      <c r="O16" s="3">
+      <c r="S16" s="3">
         <v>63.5</v>
       </c>
-      <c r="P16" s="3">
+      <c r="T16" s="3">
         <v>42.7</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="U16" s="3">
         <v>32.799999999999997</v>
       </c>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
@@ -1953,8 +2068,12 @@
       <c r="AY16" s="3"/>
       <c r="AZ16" s="3"/>
       <c r="BA16" s="3"/>
-    </row>
-    <row r="17" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB16" s="3"/>
+      <c r="BC16" s="3"/>
+      <c r="BD16" s="3"/>
+      <c r="BE16" s="3"/>
+    </row>
+    <row r="17" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>31</v>
       </c>
@@ -1980,25 +2099,27 @@
       <c r="J17" s="3">
         <v>0.4</v>
       </c>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3">
+        <v>-0.2</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
-      <c r="N17" s="3">
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3">
         <v>-2.8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>2.5</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>-3.3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>-4.0999999999999996</v>
       </c>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
@@ -2031,13 +2152,17 @@
       <c r="AY17" s="3"/>
       <c r="AZ17" s="3"/>
       <c r="BA17" s="3"/>
-    </row>
-    <row r="18" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB17" s="3"/>
+      <c r="BC17" s="3"/>
+      <c r="BD17" s="3"/>
+      <c r="BE17" s="3"/>
+    </row>
+    <row r="18" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" ref="C18:J18" si="4">+C15-SUM(C16:C17)</f>
+        <f t="shared" ref="C18:I18" si="4">+C15-SUM(C16:C17)</f>
         <v>-14.300000000000022</v>
       </c>
       <c r="D18" s="3">
@@ -2065,35 +2190,38 @@
         <v>33.100000000000023</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="4"/>
+        <f>+J15-SUM(J16:J17)</f>
         <v>40.299999999999976</v>
       </c>
-      <c r="K18" s="3"/>
+      <c r="K18" s="3">
+        <f>+K15-SUM(K16:K17)</f>
+        <v>27.600000000000033</v>
+      </c>
       <c r="L18" s="3"/>
-      <c r="M18" s="3">
-        <f t="shared" ref="M18:O18" si="5">+M15-SUM(M16:M17)</f>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3">
+        <f t="shared" ref="Q18:S18" si="5">+Q15-SUM(Q16:Q17)</f>
         <v>0</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <f t="shared" si="5"/>
         <v>-252.89999999999986</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <f t="shared" si="5"/>
         <v>-134.20000000000016</v>
       </c>
-      <c r="P18" s="3">
-        <f>+P15-SUM(P16:P17)</f>
+      <c r="T18" s="3">
+        <f>+T15-SUM(T16:T17)</f>
         <v>61.599999999999994</v>
       </c>
-      <c r="Q18" s="3">
-        <f>+Q15-SUM(Q16:Q17)</f>
+      <c r="U18" s="3">
+        <f>+U15-SUM(U16:U17)</f>
         <v>121.49999999999994</v>
       </c>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
@@ -2126,8 +2254,12 @@
       <c r="AY18" s="3"/>
       <c r="AZ18" s="3"/>
       <c r="BA18" s="3"/>
-    </row>
-    <row r="19" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB18" s="3"/>
+      <c r="BC18" s="3"/>
+      <c r="BD18" s="3"/>
+      <c r="BE18" s="3"/>
+    </row>
+    <row r="19" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>33</v>
       </c>
@@ -2153,25 +2285,27 @@
       <c r="J19" s="3">
         <v>7.8</v>
       </c>
-      <c r="K19" s="3"/>
+      <c r="K19" s="3">
+        <v>5.2</v>
+      </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-      <c r="N19" s="3">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3">
         <v>-63.8</v>
       </c>
-      <c r="O19" s="3">
+      <c r="S19" s="3">
         <v>-95</v>
       </c>
-      <c r="P19" s="3">
+      <c r="T19" s="3">
         <v>10.1</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="U19" s="3">
         <v>20.5</v>
       </c>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
@@ -2204,13 +2338,17 @@
       <c r="AY19" s="3"/>
       <c r="AZ19" s="3"/>
       <c r="BA19" s="3"/>
-    </row>
-    <row r="20" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB19" s="3"/>
+      <c r="BC19" s="3"/>
+      <c r="BD19" s="3"/>
+      <c r="BE19" s="3"/>
+    </row>
+    <row r="20" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:J20" si="6">+C18-C19</f>
+        <f t="shared" ref="C20:K20" si="6">+C18-C19</f>
         <v>-13.700000000000022</v>
       </c>
       <c r="D20" s="3">
@@ -2241,32 +2379,35 @@
         <f t="shared" si="6"/>
         <v>32.499999999999979</v>
       </c>
-      <c r="K20" s="3"/>
+      <c r="K20" s="3">
+        <f t="shared" si="6"/>
+        <v>22.400000000000034</v>
+      </c>
       <c r="L20" s="3"/>
-      <c r="M20" s="3">
-        <f t="shared" ref="M20:O20" si="7">+M18-M19</f>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3">
+        <f t="shared" ref="Q20:S20" si="7">+Q18-Q19</f>
         <v>0</v>
       </c>
-      <c r="N20" s="3">
+      <c r="R20" s="3">
         <f t="shared" si="7"/>
         <v>-189.09999999999985</v>
       </c>
-      <c r="O20" s="3">
+      <c r="S20" s="3">
         <f t="shared" si="7"/>
         <v>-39.200000000000159</v>
       </c>
-      <c r="P20" s="3">
-        <f>+P18-P19</f>
+      <c r="T20" s="3">
+        <f>+T18-T19</f>
         <v>51.499999999999993</v>
       </c>
-      <c r="Q20" s="3">
-        <f>+Q18-Q19</f>
+      <c r="U20" s="3">
+        <f>+U18-U19</f>
         <v>100.99999999999994</v>
       </c>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
@@ -2299,8 +2440,12 @@
       <c r="AY20" s="3"/>
       <c r="AZ20" s="3"/>
       <c r="BA20" s="3"/>
-    </row>
-    <row r="21" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB20" s="3"/>
+      <c r="BC20" s="3"/>
+      <c r="BD20" s="3"/>
+      <c r="BE20" s="3"/>
+    </row>
+    <row r="21" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>35</v>
       </c>
@@ -2326,25 +2471,27 @@
       <c r="J21" s="3">
         <v>0.7</v>
       </c>
-      <c r="K21" s="3"/>
+      <c r="K21" s="3">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
-      <c r="N21" s="3">
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3">
         <v>-0.8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="S21" s="3">
         <v>0.4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="T21" s="3">
         <v>3.6</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="U21" s="3">
         <v>5.2</v>
       </c>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
@@ -2377,13 +2524,17 @@
       <c r="AY21" s="3"/>
       <c r="AZ21" s="3"/>
       <c r="BA21" s="3"/>
-    </row>
-    <row r="22" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB21" s="3"/>
+      <c r="BC21" s="3"/>
+      <c r="BD21" s="3"/>
+      <c r="BE21" s="3"/>
+    </row>
+    <row r="22" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C22" s="3">
-        <f t="shared" ref="C22:J22" si="8">+C20-C21</f>
+        <f t="shared" ref="C22:K22" si="8">+C20-C21</f>
         <v>-14.500000000000023</v>
       </c>
       <c r="D22" s="3">
@@ -2414,32 +2565,35 @@
         <f t="shared" si="8"/>
         <v>31.799999999999979</v>
       </c>
-      <c r="K22" s="3"/>
+      <c r="K22" s="3">
+        <f t="shared" si="8"/>
+        <v>20.200000000000035</v>
+      </c>
       <c r="L22" s="3"/>
-      <c r="M22" s="3">
-        <f t="shared" ref="M22:O22" si="9">+M20-M21</f>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3">
+        <f t="shared" ref="Q22:S22" si="9">+Q20-Q21</f>
         <v>0</v>
       </c>
-      <c r="N22" s="3">
+      <c r="R22" s="3">
         <f t="shared" si="9"/>
         <v>-188.29999999999984</v>
       </c>
-      <c r="O22" s="3">
+      <c r="S22" s="3">
         <f t="shared" si="9"/>
         <v>-39.600000000000158</v>
       </c>
-      <c r="P22" s="3">
-        <f>+P20-P21</f>
+      <c r="T22" s="3">
+        <f>+T20-T21</f>
         <v>47.899999999999991</v>
       </c>
-      <c r="Q22" s="3">
-        <f>+Q20-Q21</f>
+      <c r="U22" s="3">
+        <f>+U20-U21</f>
         <v>95.79999999999994</v>
       </c>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
@@ -2472,8 +2626,12 @@
       <c r="AY22" s="3"/>
       <c r="AZ22" s="3"/>
       <c r="BA22" s="3"/>
-    </row>
-    <row r="23" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB22" s="3"/>
+      <c r="BC22" s="3"/>
+      <c r="BD22" s="3"/>
+      <c r="BE22" s="3"/>
+    </row>
+    <row r="23" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -2525,13 +2683,17 @@
       <c r="AY23" s="3"/>
       <c r="AZ23" s="3"/>
       <c r="BA23" s="3"/>
-    </row>
-    <row r="24" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB23" s="3"/>
+      <c r="BC23" s="3"/>
+      <c r="BD23" s="3"/>
+      <c r="BE23" s="3"/>
+    </row>
+    <row r="24" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="8">
-        <f t="shared" ref="C24:J24" si="10">+C22/C25</f>
+        <f t="shared" ref="C24:K24" si="10">+C22/C25</f>
         <v>-0.18170426065162937</v>
       </c>
       <c r="D24" s="8">
@@ -2562,32 +2724,35 @@
         <f t="shared" si="10"/>
         <v>0.38827838827838801</v>
       </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="8" t="e">
-        <f t="shared" ref="M24:O24" si="11">+M22/M25</f>
+      <c r="K24" s="8">
+        <f t="shared" si="10"/>
+        <v>0.24724602203182416</v>
+      </c>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="8" t="e">
+        <f t="shared" ref="Q24:S24" si="11">+Q22/Q25</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N24" s="8">
+      <c r="R24" s="8">
         <f t="shared" si="11"/>
         <v>-2.3626097867001232</v>
       </c>
-      <c r="O24" s="8">
+      <c r="S24" s="8">
         <f t="shared" si="11"/>
         <v>-0.49874055415617324</v>
       </c>
-      <c r="P24" s="8">
-        <f>+P22/P25</f>
+      <c r="T24" s="8">
+        <f>+T22/T25</f>
         <v>0.59874999999999989</v>
       </c>
-      <c r="Q24" s="8">
-        <f>+Q22/Q25</f>
+      <c r="U24" s="8">
+        <f>+U22/U25</f>
         <v>1.1725826193390445</v>
       </c>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
@@ -2620,8 +2785,12 @@
       <c r="AY24" s="3"/>
       <c r="AZ24" s="3"/>
       <c r="BA24" s="3"/>
-    </row>
-    <row r="25" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB24" s="3"/>
+      <c r="BC24" s="3"/>
+      <c r="BD24" s="3"/>
+      <c r="BE24" s="3"/>
+    </row>
+    <row r="25" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>3</v>
       </c>
@@ -2647,25 +2816,27 @@
       <c r="J25" s="3">
         <v>81.900000000000006</v>
       </c>
-      <c r="K25" s="3"/>
+      <c r="K25" s="3">
+        <v>81.7</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
-      <c r="N25" s="3">
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3">
         <v>79.7</v>
       </c>
-      <c r="O25" s="3">
+      <c r="S25" s="3">
         <v>79.400000000000006</v>
       </c>
-      <c r="P25" s="3">
+      <c r="T25" s="3">
         <v>80</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="U25" s="3">
         <v>81.7</v>
       </c>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
@@ -2698,8 +2869,12 @@
       <c r="AY25" s="3"/>
       <c r="AZ25" s="3"/>
       <c r="BA25" s="3"/>
-    </row>
-    <row r="26" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB25" s="3"/>
+      <c r="BC25" s="3"/>
+      <c r="BD25" s="3"/>
+      <c r="BE25" s="3"/>
+    </row>
+    <row r="26" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -2751,8 +2926,12 @@
       <c r="AY26" s="3"/>
       <c r="AZ26" s="3"/>
       <c r="BA26" s="3"/>
-    </row>
-    <row r="27" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB26" s="3"/>
+      <c r="BC26" s="3"/>
+      <c r="BD26" s="3"/>
+      <c r="BE26" s="3"/>
+    </row>
+    <row r="27" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>40</v>
       </c>
@@ -2773,38 +2952,41 @@
         <v>0.10699717602761227</v>
       </c>
       <c r="J27" s="13" t="e">
-        <f t="shared" ref="J27:J32" si="15">+J3/F3-1</f>
+        <f t="shared" ref="J27:K32" si="15">+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="9">
-        <f>+L3/C3-1</f>
+      <c r="K27" s="13">
+        <f t="shared" si="15"/>
+        <v>0.13743495561677399</v>
+      </c>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="9">
+        <f>+P3/C3-1</f>
         <v>-1</v>
       </c>
-      <c r="M27" s="9" t="e">
-        <f t="shared" ref="M27:O31" si="16">+M3/L3-1</f>
+      <c r="Q27" s="9" t="e">
+        <f t="shared" ref="Q27:S31" si="16">+Q3/P3-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N27" s="9" t="e">
+      <c r="R27" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O27" s="9" t="e">
+      <c r="S27" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P27" s="9">
-        <f t="shared" ref="P27:Q31" si="17">+P3/O3-1</f>
+      <c r="T27" s="9">
+        <f t="shared" ref="T27:U31" si="17">+T3/S3-1</f>
         <v>-0.1341115975262317</v>
       </c>
-      <c r="Q27" s="9">
+      <c r="U27" s="9">
         <f t="shared" si="17"/>
         <v>0.12976486638311546</v>
       </c>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
@@ -2837,8 +3019,12 @@
       <c r="AY27" s="3"/>
       <c r="AZ27" s="3"/>
       <c r="BA27" s="3"/>
-    </row>
-    <row r="28" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB27" s="3"/>
+      <c r="BC27" s="3"/>
+      <c r="BD27" s="3"/>
+      <c r="BE27" s="3"/>
+    </row>
+    <row r="28" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
@@ -2862,35 +3048,38 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="9">
-        <f>+L4/C4-1</f>
+      <c r="K28" s="13">
+        <f t="shared" si="15"/>
+        <v>1.2032085561497485E-2</v>
+      </c>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="9">
+        <f>+P4/C4-1</f>
         <v>-1</v>
       </c>
-      <c r="M28" s="9" t="e">
+      <c r="Q28" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N28" s="9" t="e">
+      <c r="R28" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O28" s="9" t="e">
+      <c r="S28" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P28" s="9">
+      <c r="T28" s="9">
         <f t="shared" si="17"/>
         <v>-5.2642530170620039E-2</v>
       </c>
-      <c r="Q28" s="9">
+      <c r="U28" s="9">
         <f t="shared" si="17"/>
         <v>-7.2699319130243856E-2</v>
       </c>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
@@ -2923,8 +3112,12 @@
       <c r="AY28" s="3"/>
       <c r="AZ28" s="3"/>
       <c r="BA28" s="3"/>
-    </row>
-    <row r="29" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB28" s="3"/>
+      <c r="BC28" s="3"/>
+      <c r="BD28" s="3"/>
+      <c r="BE28" s="3"/>
+    </row>
+    <row r="29" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
@@ -2948,35 +3141,38 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K29" s="3"/>
-      <c r="L29" s="9">
-        <f>+L5/C5-1</f>
+      <c r="K29" s="13">
+        <f t="shared" si="15"/>
+        <v>-4.629629629629628E-2</v>
+      </c>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="9">
+        <f>+P5/C5-1</f>
         <v>-1</v>
       </c>
-      <c r="M29" s="9" t="e">
+      <c r="Q29" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N29" s="9" t="e">
+      <c r="R29" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="9" t="e">
+      <c r="S29" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P29" s="9">
+      <c r="T29" s="9">
         <f t="shared" si="17"/>
         <v>-0.83415841584158412</v>
       </c>
-      <c r="Q29" s="9">
+      <c r="U29" s="9">
         <f t="shared" si="17"/>
         <v>-0.17350746268656725</v>
       </c>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
@@ -3009,8 +3205,12 @@
       <c r="AY29" s="3"/>
       <c r="AZ29" s="3"/>
       <c r="BA29" s="3"/>
-    </row>
-    <row r="30" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB29" s="3"/>
+      <c r="BC29" s="3"/>
+      <c r="BD29" s="3"/>
+      <c r="BE29" s="3"/>
+    </row>
+    <row r="30" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>43</v>
       </c>
@@ -3034,35 +3234,38 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K30" s="3"/>
-      <c r="L30" s="9">
-        <f>+L6/C6-1</f>
+      <c r="K30" s="13">
+        <f t="shared" si="15"/>
+        <v>-0.68629313073757525</v>
+      </c>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="9">
+        <f>+P6/C6-1</f>
         <v>-1</v>
       </c>
-      <c r="M30" s="9" t="e">
+      <c r="Q30" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N30" s="9" t="e">
+      <c r="R30" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O30" s="9">
+      <c r="S30" s="9">
         <f t="shared" si="16"/>
         <v>-0.15813819022838971</v>
       </c>
-      <c r="P30" s="9">
+      <c r="T30" s="9">
         <f t="shared" si="17"/>
         <v>-0.16912774725274726</v>
       </c>
-      <c r="Q30" s="9">
+      <c r="U30" s="9">
         <f t="shared" si="17"/>
         <v>-1.7358958462492247E-2</v>
       </c>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
@@ -3095,8 +3298,12 @@
       <c r="AY30" s="3"/>
       <c r="AZ30" s="3"/>
       <c r="BA30" s="3"/>
-    </row>
-    <row r="31" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB30" s="3"/>
+      <c r="BC30" s="3"/>
+      <c r="BD30" s="3"/>
+      <c r="BE30" s="3"/>
+    </row>
+    <row r="31" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>44</v>
       </c>
@@ -3120,35 +3327,38 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="9">
-        <f>+L7/C7-1</f>
+      <c r="K31" s="13">
+        <f t="shared" si="15"/>
+        <v>2.7188796680497922</v>
+      </c>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="9">
+        <f>+P7/C7-1</f>
         <v>-1</v>
       </c>
-      <c r="M31" s="9" t="e">
+      <c r="Q31" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N31" s="9" t="e">
+      <c r="R31" s="9" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O31" s="9">
+      <c r="S31" s="9">
         <f t="shared" si="16"/>
         <v>-0.16683391871550424</v>
       </c>
-      <c r="P31" s="9">
+      <c r="T31" s="9">
         <f t="shared" si="17"/>
         <v>-0.23450767841011744</v>
       </c>
-      <c r="Q31" s="9">
+      <c r="U31" s="9">
         <f t="shared" si="17"/>
         <v>0.1004641648965463</v>
       </c>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
@@ -3181,8 +3391,12 @@
       <c r="AY31" s="3"/>
       <c r="AZ31" s="3"/>
       <c r="BA31" s="3"/>
-    </row>
-    <row r="32" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB31" s="3"/>
+      <c r="BC31" s="3"/>
+      <c r="BD31" s="3"/>
+      <c r="BE31" s="3"/>
+    </row>
+    <row r="32" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B32" s="1" t="s">
         <v>45</v>
       </c>
@@ -3206,32 +3420,35 @@
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="10" t="e">
-        <f t="shared" ref="M32:O32" si="19">+M8/L8-1</f>
+      <c r="K32" s="10">
+        <f t="shared" si="15"/>
+        <v>0.10987145282561239</v>
+      </c>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="10" t="e">
+        <f t="shared" ref="Q32:S32" si="19">+Q8/P8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N32" s="10" t="e">
+      <c r="R32" s="10" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O32" s="10">
+      <c r="S32" s="10">
         <f t="shared" si="19"/>
         <v>-0.16459326579261024</v>
       </c>
-      <c r="P32" s="10">
-        <f>+P8/O8-1</f>
+      <c r="T32" s="10">
+        <f>+T8/S8-1</f>
         <v>-0.21753087520620629</v>
       </c>
-      <c r="Q32" s="10">
-        <f>+Q8/P8-1</f>
+      <c r="U32" s="10">
+        <f>+U8/T8-1</f>
         <v>6.7977207977207854E-2</v>
       </c>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
@@ -3264,8 +3481,12 @@
       <c r="AY32" s="3"/>
       <c r="AZ32" s="3"/>
       <c r="BA32" s="3"/>
-    </row>
-    <row r="33" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB32" s="3"/>
+      <c r="BC32" s="3"/>
+      <c r="BD32" s="3"/>
+      <c r="BE32" s="3"/>
+    </row>
+    <row r="33" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>46</v>
       </c>
@@ -3301,35 +3522,38 @@
         <f t="shared" si="20"/>
         <v>0.47033816425120767</v>
       </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="9" t="e">
-        <f t="shared" ref="L33:O33" si="21">+L10/L8</f>
+      <c r="K33" s="9">
+        <f t="shared" ref="K33" si="21">+K10/K8</f>
+        <v>0.47596153846153844</v>
+      </c>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="9" t="e">
+        <f t="shared" ref="P33:S33" si="22">+P10/P8</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M33" s="9" t="e">
-        <f t="shared" si="21"/>
+      <c r="Q33" s="9" t="e">
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N33" s="9">
-        <f t="shared" si="21"/>
+      <c r="R33" s="9">
+        <f t="shared" si="22"/>
         <v>0.39868891537544698</v>
       </c>
-      <c r="O33" s="9">
-        <f t="shared" si="21"/>
+      <c r="S33" s="9">
+        <f t="shared" si="22"/>
         <v>0.38900530563110258</v>
       </c>
-      <c r="P33" s="9">
-        <f>+P10/P8</f>
+      <c r="T33" s="9">
+        <f>+T10/T8</f>
         <v>0.44529914529914527</v>
       </c>
-      <c r="Q33" s="9">
-        <f>+Q10/Q8</f>
+      <c r="U33" s="9">
+        <f>+U10/U8</f>
         <v>0.47308328442618575</v>
       </c>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
@@ -3362,72 +3586,79 @@
       <c r="AY33" s="3"/>
       <c r="AZ33" s="3"/>
       <c r="BA33" s="3"/>
-    </row>
-    <row r="34" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB33" s="3"/>
+      <c r="BC33" s="3"/>
+      <c r="BD33" s="3"/>
+      <c r="BE33" s="3"/>
+    </row>
+    <row r="34" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C34" s="9">
-        <f t="shared" ref="C34:J34" si="22">+C15/C8</f>
+        <f t="shared" ref="C34:I34" si="23">+C15/C8</f>
         <v>-7.850088630032977E-3</v>
       </c>
       <c r="D34" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6.843838193791156E-2</v>
       </c>
       <c r="E34" s="9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>7.8827805542935003E-2</v>
       </c>
       <c r="F34" s="9" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G34" s="9">
-        <f t="shared" si="22"/>
-        <v>4.7780742178025748E-2</v>
-      </c>
-      <c r="H34" s="9">
-        <f t="shared" si="22"/>
-        <v>8.5828764234500185E-2</v>
-      </c>
-      <c r="I34" s="9">
-        <f t="shared" si="22"/>
-        <v>8.4201573463746585E-2</v>
-      </c>
-      <c r="J34" s="9">
-        <f t="shared" si="22"/>
-        <v>9.4492753623188361E-2</v>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="9" t="e">
-        <f t="shared" ref="L34:O34" si="23">+L15/L8</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M34" s="9" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N34" s="9">
+      <c r="G34" s="9">
         <f t="shared" si="23"/>
+        <v>4.7780742178025748E-2</v>
+      </c>
+      <c r="H34" s="9">
+        <f t="shared" si="23"/>
+        <v>8.5828764234500185E-2</v>
+      </c>
+      <c r="I34" s="9">
+        <f t="shared" si="23"/>
+        <v>8.4201573463746585E-2</v>
+      </c>
+      <c r="J34" s="9">
+        <f>+J15/J8</f>
+        <v>9.4492753623188361E-2</v>
+      </c>
+      <c r="K34" s="9">
+        <f>+K15/K8</f>
+        <v>7.4082167832167908E-2</v>
+      </c>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="9" t="e">
+        <f t="shared" ref="P34:S34" si="24">+P15/P8</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q34" s="9" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" si="24"/>
         <v>-7.7622169249106018E-2</v>
       </c>
-      <c r="O34" s="9">
-        <f t="shared" si="23"/>
+      <c r="S34" s="9">
+        <f t="shared" si="24"/>
         <v>-3.0407062285434105E-2</v>
       </c>
-      <c r="P34" s="9">
-        <f>+P15/P8</f>
+      <c r="T34" s="9">
+        <f>+T15/T8</f>
         <v>5.7549857549857551E-2</v>
       </c>
-      <c r="Q34" s="9">
-        <f>+Q15/Q8</f>
+      <c r="U34" s="9">
+        <f>+U15/U8</f>
         <v>8.0136584324814561E-2</v>
       </c>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
@@ -3460,72 +3691,79 @@
       <c r="AY34" s="3"/>
       <c r="AZ34" s="3"/>
       <c r="BA34" s="3"/>
-    </row>
-    <row r="35" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB34" s="3"/>
+      <c r="BC34" s="3"/>
+      <c r="BD34" s="3"/>
+      <c r="BE34" s="3"/>
+    </row>
+    <row r="35" spans="2:57" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C35" s="9">
-        <f t="shared" ref="C35:J35" si="24">+C19/C18</f>
+        <f t="shared" ref="C35:J35" si="25">+C19/C18</f>
         <v>4.195804195804189E-2</v>
       </c>
       <c r="D35" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.13333333333333339</v>
       </c>
       <c r="E35" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.17301038062283744</v>
       </c>
       <c r="F35" s="9" t="e">
-        <f t="shared" si="24"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G35" s="9">
-        <f t="shared" si="24"/>
-        <v>7.5757575757575663E-2</v>
-      </c>
-      <c r="H35" s="9">
-        <f t="shared" si="24"/>
-        <v>0.13690476190476195</v>
-      </c>
-      <c r="I35" s="9">
-        <f t="shared" si="24"/>
-        <v>0.20543806646525664</v>
-      </c>
-      <c r="J35" s="9">
-        <f t="shared" si="24"/>
-        <v>0.1935483870967743</v>
-      </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="9" t="e">
-        <f t="shared" ref="L35:O35" si="25">+L19/L18</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M35" s="9" t="e">
         <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N35" s="9">
+      <c r="G35" s="9">
         <f t="shared" si="25"/>
+        <v>7.5757575757575663E-2</v>
+      </c>
+      <c r="H35" s="9">
+        <f t="shared" si="25"/>
+        <v>0.13690476190476195</v>
+      </c>
+      <c r="I35" s="9">
+        <f t="shared" si="25"/>
+        <v>0.20543806646525664</v>
+      </c>
+      <c r="J35" s="9">
+        <f t="shared" si="25"/>
+        <v>0.1935483870967743</v>
+      </c>
+      <c r="K35" s="9">
+        <f t="shared" ref="K35" si="26">+K19/K18</f>
+        <v>0.18840579710144906</v>
+      </c>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="9" t="e">
+        <f t="shared" ref="P35:S35" si="27">+P19/P18</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q35" s="9" t="e">
+        <f t="shared" si="27"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R35" s="9">
+        <f t="shared" si="27"/>
         <v>0.25227362593910652</v>
       </c>
-      <c r="O35" s="9">
-        <f t="shared" si="25"/>
+      <c r="S35" s="9">
+        <f t="shared" si="27"/>
         <v>0.70789865871833002</v>
       </c>
-      <c r="P35" s="9">
-        <f>+P19/P18</f>
+      <c r="T35" s="9">
+        <f>+T19/T18</f>
         <v>0.16396103896103897</v>
       </c>
-      <c r="Q35" s="9">
-        <f>+Q19/Q18</f>
+      <c r="U35" s="9">
+        <f>+U19/U18</f>
         <v>0.16872427983539104</v>
       </c>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
       <c r="X35" s="3"/>
@@ -3558,8 +3796,12 @@
       <c r="AY35" s="3"/>
       <c r="AZ35" s="3"/>
       <c r="BA35" s="3"/>
-    </row>
-    <row r="36" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB35" s="3"/>
+      <c r="BC35" s="3"/>
+      <c r="BD35" s="3"/>
+      <c r="BE35" s="3"/>
+    </row>
+    <row r="36" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -3611,8 +3853,12 @@
       <c r="AY36" s="3"/>
       <c r="AZ36" s="3"/>
       <c r="BA36" s="3"/>
-    </row>
-    <row r="37" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB36" s="3"/>
+      <c r="BC36" s="3"/>
+      <c r="BD36" s="3"/>
+      <c r="BE36" s="3"/>
+    </row>
+    <row r="37" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -3664,8 +3910,12 @@
       <c r="AY37" s="3"/>
       <c r="AZ37" s="3"/>
       <c r="BA37" s="3"/>
-    </row>
-    <row r="38" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB37" s="3"/>
+      <c r="BC37" s="3"/>
+      <c r="BD37" s="3"/>
+      <c r="BE37" s="3"/>
+    </row>
+    <row r="38" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -3717,8 +3967,12 @@
       <c r="AY38" s="3"/>
       <c r="AZ38" s="3"/>
       <c r="BA38" s="3"/>
-    </row>
-    <row r="39" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB38" s="3"/>
+      <c r="BC38" s="3"/>
+      <c r="BD38" s="3"/>
+      <c r="BE38" s="3"/>
+    </row>
+    <row r="39" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -3770,8 +4024,12 @@
       <c r="AY39" s="3"/>
       <c r="AZ39" s="3"/>
       <c r="BA39" s="3"/>
-    </row>
-    <row r="40" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB39" s="3"/>
+      <c r="BC39" s="3"/>
+      <c r="BD39" s="3"/>
+      <c r="BE39" s="3"/>
+    </row>
+    <row r="40" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -3823,8 +4081,12 @@
       <c r="AY40" s="3"/>
       <c r="AZ40" s="3"/>
       <c r="BA40" s="3"/>
-    </row>
-    <row r="41" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB40" s="3"/>
+      <c r="BC40" s="3"/>
+      <c r="BD40" s="3"/>
+      <c r="BE40" s="3"/>
+    </row>
+    <row r="41" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3876,8 +4138,12 @@
       <c r="AY41" s="3"/>
       <c r="AZ41" s="3"/>
       <c r="BA41" s="3"/>
-    </row>
-    <row r="42" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB41" s="3"/>
+      <c r="BC41" s="3"/>
+      <c r="BD41" s="3"/>
+      <c r="BE41" s="3"/>
+    </row>
+    <row r="42" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -3929,8 +4195,12 @@
       <c r="AY42" s="3"/>
       <c r="AZ42" s="3"/>
       <c r="BA42" s="3"/>
-    </row>
-    <row r="43" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB42" s="3"/>
+      <c r="BC42" s="3"/>
+      <c r="BD42" s="3"/>
+      <c r="BE42" s="3"/>
+    </row>
+    <row r="43" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -3982,8 +4252,12 @@
       <c r="AY43" s="3"/>
       <c r="AZ43" s="3"/>
       <c r="BA43" s="3"/>
-    </row>
-    <row r="44" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB43" s="3"/>
+      <c r="BC43" s="3"/>
+      <c r="BD43" s="3"/>
+      <c r="BE43" s="3"/>
+    </row>
+    <row r="44" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -4035,8 +4309,12 @@
       <c r="AY44" s="3"/>
       <c r="AZ44" s="3"/>
       <c r="BA44" s="3"/>
-    </row>
-    <row r="45" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB44" s="3"/>
+      <c r="BC44" s="3"/>
+      <c r="BD44" s="3"/>
+      <c r="BE44" s="3"/>
+    </row>
+    <row r="45" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -4088,8 +4366,12 @@
       <c r="AY45" s="3"/>
       <c r="AZ45" s="3"/>
       <c r="BA45" s="3"/>
-    </row>
-    <row r="46" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB45" s="3"/>
+      <c r="BC45" s="3"/>
+      <c r="BD45" s="3"/>
+      <c r="BE45" s="3"/>
+    </row>
+    <row r="46" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -4141,8 +4423,12 @@
       <c r="AY46" s="3"/>
       <c r="AZ46" s="3"/>
       <c r="BA46" s="3"/>
-    </row>
-    <row r="47" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB46" s="3"/>
+      <c r="BC46" s="3"/>
+      <c r="BD46" s="3"/>
+      <c r="BE46" s="3"/>
+    </row>
+    <row r="47" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -4194,8 +4480,12 @@
       <c r="AY47" s="3"/>
       <c r="AZ47" s="3"/>
       <c r="BA47" s="3"/>
-    </row>
-    <row r="48" spans="2:53" x14ac:dyDescent="0.2">
+      <c r="BB47" s="3"/>
+      <c r="BC47" s="3"/>
+      <c r="BD47" s="3"/>
+      <c r="BE47" s="3"/>
+    </row>
+    <row r="48" spans="2:57" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -4247,8 +4537,12 @@
       <c r="AY48" s="3"/>
       <c r="AZ48" s="3"/>
       <c r="BA48" s="3"/>
-    </row>
-    <row r="49" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB48" s="3"/>
+      <c r="BC48" s="3"/>
+      <c r="BD48" s="3"/>
+      <c r="BE48" s="3"/>
+    </row>
+    <row r="49" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -4300,8 +4594,12 @@
       <c r="AY49" s="3"/>
       <c r="AZ49" s="3"/>
       <c r="BA49" s="3"/>
-    </row>
-    <row r="50" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB49" s="3"/>
+      <c r="BC49" s="3"/>
+      <c r="BD49" s="3"/>
+      <c r="BE49" s="3"/>
+    </row>
+    <row r="50" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -4353,8 +4651,12 @@
       <c r="AY50" s="3"/>
       <c r="AZ50" s="3"/>
       <c r="BA50" s="3"/>
-    </row>
-    <row r="51" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB50" s="3"/>
+      <c r="BC50" s="3"/>
+      <c r="BD50" s="3"/>
+      <c r="BE50" s="3"/>
+    </row>
+    <row r="51" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -4406,8 +4708,12 @@
       <c r="AY51" s="3"/>
       <c r="AZ51" s="3"/>
       <c r="BA51" s="3"/>
-    </row>
-    <row r="52" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB51" s="3"/>
+      <c r="BC51" s="3"/>
+      <c r="BD51" s="3"/>
+      <c r="BE51" s="3"/>
+    </row>
+    <row r="52" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -4459,8 +4765,12 @@
       <c r="AY52" s="3"/>
       <c r="AZ52" s="3"/>
       <c r="BA52" s="3"/>
-    </row>
-    <row r="53" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB52" s="3"/>
+      <c r="BC52" s="3"/>
+      <c r="BD52" s="3"/>
+      <c r="BE52" s="3"/>
+    </row>
+    <row r="53" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -4512,8 +4822,12 @@
       <c r="AY53" s="3"/>
       <c r="AZ53" s="3"/>
       <c r="BA53" s="3"/>
-    </row>
-    <row r="54" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB53" s="3"/>
+      <c r="BC53" s="3"/>
+      <c r="BD53" s="3"/>
+      <c r="BE53" s="3"/>
+    </row>
+    <row r="54" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -4565,8 +4879,12 @@
       <c r="AY54" s="3"/>
       <c r="AZ54" s="3"/>
       <c r="BA54" s="3"/>
-    </row>
-    <row r="55" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB54" s="3"/>
+      <c r="BC54" s="3"/>
+      <c r="BD54" s="3"/>
+      <c r="BE54" s="3"/>
+    </row>
+    <row r="55" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -4618,8 +4936,12 @@
       <c r="AY55" s="3"/>
       <c r="AZ55" s="3"/>
       <c r="BA55" s="3"/>
-    </row>
-    <row r="56" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB55" s="3"/>
+      <c r="BC55" s="3"/>
+      <c r="BD55" s="3"/>
+      <c r="BE55" s="3"/>
+    </row>
+    <row r="56" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -4671,8 +4993,12 @@
       <c r="AY56" s="3"/>
       <c r="AZ56" s="3"/>
       <c r="BA56" s="3"/>
-    </row>
-    <row r="57" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB56" s="3"/>
+      <c r="BC56" s="3"/>
+      <c r="BD56" s="3"/>
+      <c r="BE56" s="3"/>
+    </row>
+    <row r="57" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -4724,8 +5050,12 @@
       <c r="AY57" s="3"/>
       <c r="AZ57" s="3"/>
       <c r="BA57" s="3"/>
-    </row>
-    <row r="58" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB57" s="3"/>
+      <c r="BC57" s="3"/>
+      <c r="BD57" s="3"/>
+      <c r="BE57" s="3"/>
+    </row>
+    <row r="58" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -4777,8 +5107,12 @@
       <c r="AY58" s="3"/>
       <c r="AZ58" s="3"/>
       <c r="BA58" s="3"/>
-    </row>
-    <row r="59" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB58" s="3"/>
+      <c r="BC58" s="3"/>
+      <c r="BD58" s="3"/>
+      <c r="BE58" s="3"/>
+    </row>
+    <row r="59" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -4830,8 +5164,12 @@
       <c r="AY59" s="3"/>
       <c r="AZ59" s="3"/>
       <c r="BA59" s="3"/>
-    </row>
-    <row r="60" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB59" s="3"/>
+      <c r="BC59" s="3"/>
+      <c r="BD59" s="3"/>
+      <c r="BE59" s="3"/>
+    </row>
+    <row r="60" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -4883,8 +5221,12 @@
       <c r="AY60" s="3"/>
       <c r="AZ60" s="3"/>
       <c r="BA60" s="3"/>
-    </row>
-    <row r="61" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB60" s="3"/>
+      <c r="BC60" s="3"/>
+      <c r="BD60" s="3"/>
+      <c r="BE60" s="3"/>
+    </row>
+    <row r="61" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -4936,8 +5278,12 @@
       <c r="AY61" s="3"/>
       <c r="AZ61" s="3"/>
       <c r="BA61" s="3"/>
-    </row>
-    <row r="62" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB61" s="3"/>
+      <c r="BC61" s="3"/>
+      <c r="BD61" s="3"/>
+      <c r="BE61" s="3"/>
+    </row>
+    <row r="62" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -4989,8 +5335,12 @@
       <c r="AY62" s="3"/>
       <c r="AZ62" s="3"/>
       <c r="BA62" s="3"/>
-    </row>
-    <row r="63" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB62" s="3"/>
+      <c r="BC62" s="3"/>
+      <c r="BD62" s="3"/>
+      <c r="BE62" s="3"/>
+    </row>
+    <row r="63" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -5042,8 +5392,12 @@
       <c r="AY63" s="3"/>
       <c r="AZ63" s="3"/>
       <c r="BA63" s="3"/>
-    </row>
-    <row r="64" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB63" s="3"/>
+      <c r="BC63" s="3"/>
+      <c r="BD63" s="3"/>
+      <c r="BE63" s="3"/>
+    </row>
+    <row r="64" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -5095,8 +5449,12 @@
       <c r="AY64" s="3"/>
       <c r="AZ64" s="3"/>
       <c r="BA64" s="3"/>
-    </row>
-    <row r="65" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB64" s="3"/>
+      <c r="BC64" s="3"/>
+      <c r="BD64" s="3"/>
+      <c r="BE64" s="3"/>
+    </row>
+    <row r="65" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -5148,8 +5506,12 @@
       <c r="AY65" s="3"/>
       <c r="AZ65" s="3"/>
       <c r="BA65" s="3"/>
-    </row>
-    <row r="66" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB65" s="3"/>
+      <c r="BC65" s="3"/>
+      <c r="BD65" s="3"/>
+      <c r="BE65" s="3"/>
+    </row>
+    <row r="66" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -5201,8 +5563,12 @@
       <c r="AY66" s="3"/>
       <c r="AZ66" s="3"/>
       <c r="BA66" s="3"/>
-    </row>
-    <row r="67" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB66" s="3"/>
+      <c r="BC66" s="3"/>
+      <c r="BD66" s="3"/>
+      <c r="BE66" s="3"/>
+    </row>
+    <row r="67" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -5254,8 +5620,12 @@
       <c r="AY67" s="3"/>
       <c r="AZ67" s="3"/>
       <c r="BA67" s="3"/>
-    </row>
-    <row r="68" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB67" s="3"/>
+      <c r="BC67" s="3"/>
+      <c r="BD67" s="3"/>
+      <c r="BE67" s="3"/>
+    </row>
+    <row r="68" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -5307,8 +5677,12 @@
       <c r="AY68" s="3"/>
       <c r="AZ68" s="3"/>
       <c r="BA68" s="3"/>
-    </row>
-    <row r="69" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB68" s="3"/>
+      <c r="BC68" s="3"/>
+      <c r="BD68" s="3"/>
+      <c r="BE68" s="3"/>
+    </row>
+    <row r="69" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -5360,8 +5734,12 @@
       <c r="AY69" s="3"/>
       <c r="AZ69" s="3"/>
       <c r="BA69" s="3"/>
-    </row>
-    <row r="70" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB69" s="3"/>
+      <c r="BC69" s="3"/>
+      <c r="BD69" s="3"/>
+      <c r="BE69" s="3"/>
+    </row>
+    <row r="70" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -5413,8 +5791,12 @@
       <c r="AY70" s="3"/>
       <c r="AZ70" s="3"/>
       <c r="BA70" s="3"/>
-    </row>
-    <row r="71" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB70" s="3"/>
+      <c r="BC70" s="3"/>
+      <c r="BD70" s="3"/>
+      <c r="BE70" s="3"/>
+    </row>
+    <row r="71" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -5466,8 +5848,12 @@
       <c r="AY71" s="3"/>
       <c r="AZ71" s="3"/>
       <c r="BA71" s="3"/>
-    </row>
-    <row r="72" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB71" s="3"/>
+      <c r="BC71" s="3"/>
+      <c r="BD71" s="3"/>
+      <c r="BE71" s="3"/>
+    </row>
+    <row r="72" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -5519,8 +5905,12 @@
       <c r="AY72" s="3"/>
       <c r="AZ72" s="3"/>
       <c r="BA72" s="3"/>
-    </row>
-    <row r="73" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB72" s="3"/>
+      <c r="BC72" s="3"/>
+      <c r="BD72" s="3"/>
+      <c r="BE72" s="3"/>
+    </row>
+    <row r="73" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -5572,8 +5962,12 @@
       <c r="AY73" s="3"/>
       <c r="AZ73" s="3"/>
       <c r="BA73" s="3"/>
-    </row>
-    <row r="74" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB73" s="3"/>
+      <c r="BC73" s="3"/>
+      <c r="BD73" s="3"/>
+      <c r="BE73" s="3"/>
+    </row>
+    <row r="74" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -5625,8 +6019,12 @@
       <c r="AY74" s="3"/>
       <c r="AZ74" s="3"/>
       <c r="BA74" s="3"/>
-    </row>
-    <row r="75" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB74" s="3"/>
+      <c r="BC74" s="3"/>
+      <c r="BD74" s="3"/>
+      <c r="BE74" s="3"/>
+    </row>
+    <row r="75" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -5678,8 +6076,12 @@
       <c r="AY75" s="3"/>
       <c r="AZ75" s="3"/>
       <c r="BA75" s="3"/>
-    </row>
-    <row r="76" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB75" s="3"/>
+      <c r="BC75" s="3"/>
+      <c r="BD75" s="3"/>
+      <c r="BE75" s="3"/>
+    </row>
+    <row r="76" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -5731,8 +6133,12 @@
       <c r="AY76" s="3"/>
       <c r="AZ76" s="3"/>
       <c r="BA76" s="3"/>
-    </row>
-    <row r="77" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB76" s="3"/>
+      <c r="BC76" s="3"/>
+      <c r="BD76" s="3"/>
+      <c r="BE76" s="3"/>
+    </row>
+    <row r="77" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -5784,8 +6190,12 @@
       <c r="AY77" s="3"/>
       <c r="AZ77" s="3"/>
       <c r="BA77" s="3"/>
-    </row>
-    <row r="78" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB77" s="3"/>
+      <c r="BC77" s="3"/>
+      <c r="BD77" s="3"/>
+      <c r="BE77" s="3"/>
+    </row>
+    <row r="78" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -5837,8 +6247,12 @@
       <c r="AY78" s="3"/>
       <c r="AZ78" s="3"/>
       <c r="BA78" s="3"/>
-    </row>
-    <row r="79" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB78" s="3"/>
+      <c r="BC78" s="3"/>
+      <c r="BD78" s="3"/>
+      <c r="BE78" s="3"/>
+    </row>
+    <row r="79" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -5890,8 +6304,12 @@
       <c r="AY79" s="3"/>
       <c r="AZ79" s="3"/>
       <c r="BA79" s="3"/>
-    </row>
-    <row r="80" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB79" s="3"/>
+      <c r="BC79" s="3"/>
+      <c r="BD79" s="3"/>
+      <c r="BE79" s="3"/>
+    </row>
+    <row r="80" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -5943,8 +6361,12 @@
       <c r="AY80" s="3"/>
       <c r="AZ80" s="3"/>
       <c r="BA80" s="3"/>
-    </row>
-    <row r="81" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB80" s="3"/>
+      <c r="BC80" s="3"/>
+      <c r="BD80" s="3"/>
+      <c r="BE80" s="3"/>
+    </row>
+    <row r="81" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -5996,8 +6418,12 @@
       <c r="AY81" s="3"/>
       <c r="AZ81" s="3"/>
       <c r="BA81" s="3"/>
-    </row>
-    <row r="82" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB81" s="3"/>
+      <c r="BC81" s="3"/>
+      <c r="BD81" s="3"/>
+      <c r="BE81" s="3"/>
+    </row>
+    <row r="82" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -6049,8 +6475,12 @@
       <c r="AY82" s="3"/>
       <c r="AZ82" s="3"/>
       <c r="BA82" s="3"/>
-    </row>
-    <row r="83" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB82" s="3"/>
+      <c r="BC82" s="3"/>
+      <c r="BD82" s="3"/>
+      <c r="BE82" s="3"/>
+    </row>
+    <row r="83" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -6102,8 +6532,12 @@
       <c r="AY83" s="3"/>
       <c r="AZ83" s="3"/>
       <c r="BA83" s="3"/>
-    </row>
-    <row r="84" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB83" s="3"/>
+      <c r="BC83" s="3"/>
+      <c r="BD83" s="3"/>
+      <c r="BE83" s="3"/>
+    </row>
+    <row r="84" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -6155,8 +6589,12 @@
       <c r="AY84" s="3"/>
       <c r="AZ84" s="3"/>
       <c r="BA84" s="3"/>
-    </row>
-    <row r="85" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB84" s="3"/>
+      <c r="BC84" s="3"/>
+      <c r="BD84" s="3"/>
+      <c r="BE84" s="3"/>
+    </row>
+    <row r="85" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -6208,8 +6646,12 @@
       <c r="AY85" s="3"/>
       <c r="AZ85" s="3"/>
       <c r="BA85" s="3"/>
-    </row>
-    <row r="86" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB85" s="3"/>
+      <c r="BC85" s="3"/>
+      <c r="BD85" s="3"/>
+      <c r="BE85" s="3"/>
+    </row>
+    <row r="86" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -6261,8 +6703,12 @@
       <c r="AY86" s="3"/>
       <c r="AZ86" s="3"/>
       <c r="BA86" s="3"/>
-    </row>
-    <row r="87" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB86" s="3"/>
+      <c r="BC86" s="3"/>
+      <c r="BD86" s="3"/>
+      <c r="BE86" s="3"/>
+    </row>
+    <row r="87" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -6314,8 +6760,12 @@
       <c r="AY87" s="3"/>
       <c r="AZ87" s="3"/>
       <c r="BA87" s="3"/>
-    </row>
-    <row r="88" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB87" s="3"/>
+      <c r="BC87" s="3"/>
+      <c r="BD87" s="3"/>
+      <c r="BE87" s="3"/>
+    </row>
+    <row r="88" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -6367,8 +6817,12 @@
       <c r="AY88" s="3"/>
       <c r="AZ88" s="3"/>
       <c r="BA88" s="3"/>
-    </row>
-    <row r="89" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB88" s="3"/>
+      <c r="BC88" s="3"/>
+      <c r="BD88" s="3"/>
+      <c r="BE88" s="3"/>
+    </row>
+    <row r="89" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -6420,8 +6874,12 @@
       <c r="AY89" s="3"/>
       <c r="AZ89" s="3"/>
       <c r="BA89" s="3"/>
-    </row>
-    <row r="90" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB89" s="3"/>
+      <c r="BC89" s="3"/>
+      <c r="BD89" s="3"/>
+      <c r="BE89" s="3"/>
+    </row>
+    <row r="90" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -6473,8 +6931,12 @@
       <c r="AY90" s="3"/>
       <c r="AZ90" s="3"/>
       <c r="BA90" s="3"/>
-    </row>
-    <row r="91" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB90" s="3"/>
+      <c r="BC90" s="3"/>
+      <c r="BD90" s="3"/>
+      <c r="BE90" s="3"/>
+    </row>
+    <row r="91" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -6526,8 +6988,12 @@
       <c r="AY91" s="3"/>
       <c r="AZ91" s="3"/>
       <c r="BA91" s="3"/>
-    </row>
-    <row r="92" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB91" s="3"/>
+      <c r="BC91" s="3"/>
+      <c r="BD91" s="3"/>
+      <c r="BE91" s="3"/>
+    </row>
+    <row r="92" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -6579,8 +7045,12 @@
       <c r="AY92" s="3"/>
       <c r="AZ92" s="3"/>
       <c r="BA92" s="3"/>
-    </row>
-    <row r="93" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB92" s="3"/>
+      <c r="BC92" s="3"/>
+      <c r="BD92" s="3"/>
+      <c r="BE92" s="3"/>
+    </row>
+    <row r="93" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -6632,8 +7102,12 @@
       <c r="AY93" s="3"/>
       <c r="AZ93" s="3"/>
       <c r="BA93" s="3"/>
-    </row>
-    <row r="94" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB93" s="3"/>
+      <c r="BC93" s="3"/>
+      <c r="BD93" s="3"/>
+      <c r="BE93" s="3"/>
+    </row>
+    <row r="94" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -6685,8 +7159,12 @@
       <c r="AY94" s="3"/>
       <c r="AZ94" s="3"/>
       <c r="BA94" s="3"/>
-    </row>
-    <row r="95" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB94" s="3"/>
+      <c r="BC94" s="3"/>
+      <c r="BD94" s="3"/>
+      <c r="BE94" s="3"/>
+    </row>
+    <row r="95" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -6738,8 +7216,12 @@
       <c r="AY95" s="3"/>
       <c r="AZ95" s="3"/>
       <c r="BA95" s="3"/>
-    </row>
-    <row r="96" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB95" s="3"/>
+      <c r="BC95" s="3"/>
+      <c r="BD95" s="3"/>
+      <c r="BE95" s="3"/>
+    </row>
+    <row r="96" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -6791,8 +7273,12 @@
       <c r="AY96" s="3"/>
       <c r="AZ96" s="3"/>
       <c r="BA96" s="3"/>
-    </row>
-    <row r="97" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB96" s="3"/>
+      <c r="BC96" s="3"/>
+      <c r="BD96" s="3"/>
+      <c r="BE96" s="3"/>
+    </row>
+    <row r="97" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -6844,8 +7330,12 @@
       <c r="AY97" s="3"/>
       <c r="AZ97" s="3"/>
       <c r="BA97" s="3"/>
-    </row>
-    <row r="98" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB97" s="3"/>
+      <c r="BC97" s="3"/>
+      <c r="BD97" s="3"/>
+      <c r="BE97" s="3"/>
+    </row>
+    <row r="98" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -6897,8 +7387,12 @@
       <c r="AY98" s="3"/>
       <c r="AZ98" s="3"/>
       <c r="BA98" s="3"/>
-    </row>
-    <row r="99" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB98" s="3"/>
+      <c r="BC98" s="3"/>
+      <c r="BD98" s="3"/>
+      <c r="BE98" s="3"/>
+    </row>
+    <row r="99" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -6950,8 +7444,12 @@
       <c r="AY99" s="3"/>
       <c r="AZ99" s="3"/>
       <c r="BA99" s="3"/>
-    </row>
-    <row r="100" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB99" s="3"/>
+      <c r="BC99" s="3"/>
+      <c r="BD99" s="3"/>
+      <c r="BE99" s="3"/>
+    </row>
+    <row r="100" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -7003,8 +7501,12 @@
       <c r="AY100" s="3"/>
       <c r="AZ100" s="3"/>
       <c r="BA100" s="3"/>
-    </row>
-    <row r="101" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB100" s="3"/>
+      <c r="BC100" s="3"/>
+      <c r="BD100" s="3"/>
+      <c r="BE100" s="3"/>
+    </row>
+    <row r="101" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -7056,8 +7558,12 @@
       <c r="AY101" s="3"/>
       <c r="AZ101" s="3"/>
       <c r="BA101" s="3"/>
-    </row>
-    <row r="102" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB101" s="3"/>
+      <c r="BC101" s="3"/>
+      <c r="BD101" s="3"/>
+      <c r="BE101" s="3"/>
+    </row>
+    <row r="102" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -7109,8 +7615,12 @@
       <c r="AY102" s="3"/>
       <c r="AZ102" s="3"/>
       <c r="BA102" s="3"/>
-    </row>
-    <row r="103" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB102" s="3"/>
+      <c r="BC102" s="3"/>
+      <c r="BD102" s="3"/>
+      <c r="BE102" s="3"/>
+    </row>
+    <row r="103" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -7162,8 +7672,12 @@
       <c r="AY103" s="3"/>
       <c r="AZ103" s="3"/>
       <c r="BA103" s="3"/>
-    </row>
-    <row r="104" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB103" s="3"/>
+      <c r="BC103" s="3"/>
+      <c r="BD103" s="3"/>
+      <c r="BE103" s="3"/>
+    </row>
+    <row r="104" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -7215,8 +7729,12 @@
       <c r="AY104" s="3"/>
       <c r="AZ104" s="3"/>
       <c r="BA104" s="3"/>
-    </row>
-    <row r="105" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB104" s="3"/>
+      <c r="BC104" s="3"/>
+      <c r="BD104" s="3"/>
+      <c r="BE104" s="3"/>
+    </row>
+    <row r="105" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -7268,8 +7786,12 @@
       <c r="AY105" s="3"/>
       <c r="AZ105" s="3"/>
       <c r="BA105" s="3"/>
-    </row>
-    <row r="106" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB105" s="3"/>
+      <c r="BC105" s="3"/>
+      <c r="BD105" s="3"/>
+      <c r="BE105" s="3"/>
+    </row>
+    <row r="106" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -7321,8 +7843,12 @@
       <c r="AY106" s="3"/>
       <c r="AZ106" s="3"/>
       <c r="BA106" s="3"/>
-    </row>
-    <row r="107" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB106" s="3"/>
+      <c r="BC106" s="3"/>
+      <c r="BD106" s="3"/>
+      <c r="BE106" s="3"/>
+    </row>
+    <row r="107" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -7374,8 +7900,12 @@
       <c r="AY107" s="3"/>
       <c r="AZ107" s="3"/>
       <c r="BA107" s="3"/>
-    </row>
-    <row r="108" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB107" s="3"/>
+      <c r="BC107" s="3"/>
+      <c r="BD107" s="3"/>
+      <c r="BE107" s="3"/>
+    </row>
+    <row r="108" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -7427,8 +7957,12 @@
       <c r="AY108" s="3"/>
       <c r="AZ108" s="3"/>
       <c r="BA108" s="3"/>
-    </row>
-    <row r="109" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB108" s="3"/>
+      <c r="BC108" s="3"/>
+      <c r="BD108" s="3"/>
+      <c r="BE108" s="3"/>
+    </row>
+    <row r="109" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -7480,8 +8014,12 @@
       <c r="AY109" s="3"/>
       <c r="AZ109" s="3"/>
       <c r="BA109" s="3"/>
-    </row>
-    <row r="110" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB109" s="3"/>
+      <c r="BC109" s="3"/>
+      <c r="BD109" s="3"/>
+      <c r="BE109" s="3"/>
+    </row>
+    <row r="110" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -7533,8 +8071,12 @@
       <c r="AY110" s="3"/>
       <c r="AZ110" s="3"/>
       <c r="BA110" s="3"/>
-    </row>
-    <row r="111" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB110" s="3"/>
+      <c r="BC110" s="3"/>
+      <c r="BD110" s="3"/>
+      <c r="BE110" s="3"/>
+    </row>
+    <row r="111" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -7586,8 +8128,12 @@
       <c r="AY111" s="3"/>
       <c r="AZ111" s="3"/>
       <c r="BA111" s="3"/>
-    </row>
-    <row r="112" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB111" s="3"/>
+      <c r="BC111" s="3"/>
+      <c r="BD111" s="3"/>
+      <c r="BE111" s="3"/>
+    </row>
+    <row r="112" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -7639,8 +8185,12 @@
       <c r="AY112" s="3"/>
       <c r="AZ112" s="3"/>
       <c r="BA112" s="3"/>
-    </row>
-    <row r="113" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB112" s="3"/>
+      <c r="BC112" s="3"/>
+      <c r="BD112" s="3"/>
+      <c r="BE112" s="3"/>
+    </row>
+    <row r="113" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -7692,8 +8242,12 @@
       <c r="AY113" s="3"/>
       <c r="AZ113" s="3"/>
       <c r="BA113" s="3"/>
-    </row>
-    <row r="114" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB113" s="3"/>
+      <c r="BC113" s="3"/>
+      <c r="BD113" s="3"/>
+      <c r="BE113" s="3"/>
+    </row>
+    <row r="114" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -7745,8 +8299,12 @@
       <c r="AY114" s="3"/>
       <c r="AZ114" s="3"/>
       <c r="BA114" s="3"/>
-    </row>
-    <row r="115" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB114" s="3"/>
+      <c r="BC114" s="3"/>
+      <c r="BD114" s="3"/>
+      <c r="BE114" s="3"/>
+    </row>
+    <row r="115" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -7798,8 +8356,12 @@
       <c r="AY115" s="3"/>
       <c r="AZ115" s="3"/>
       <c r="BA115" s="3"/>
-    </row>
-    <row r="116" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB115" s="3"/>
+      <c r="BC115" s="3"/>
+      <c r="BD115" s="3"/>
+      <c r="BE115" s="3"/>
+    </row>
+    <row r="116" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -7851,8 +8413,12 @@
       <c r="AY116" s="3"/>
       <c r="AZ116" s="3"/>
       <c r="BA116" s="3"/>
-    </row>
-    <row r="117" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB116" s="3"/>
+      <c r="BC116" s="3"/>
+      <c r="BD116" s="3"/>
+      <c r="BE116" s="3"/>
+    </row>
+    <row r="117" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -7904,8 +8470,12 @@
       <c r="AY117" s="3"/>
       <c r="AZ117" s="3"/>
       <c r="BA117" s="3"/>
-    </row>
-    <row r="118" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB117" s="3"/>
+      <c r="BC117" s="3"/>
+      <c r="BD117" s="3"/>
+      <c r="BE117" s="3"/>
+    </row>
+    <row r="118" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -7957,8 +8527,12 @@
       <c r="AY118" s="3"/>
       <c r="AZ118" s="3"/>
       <c r="BA118" s="3"/>
-    </row>
-    <row r="119" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB118" s="3"/>
+      <c r="BC118" s="3"/>
+      <c r="BD118" s="3"/>
+      <c r="BE118" s="3"/>
+    </row>
+    <row r="119" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -8010,8 +8584,12 @@
       <c r="AY119" s="3"/>
       <c r="AZ119" s="3"/>
       <c r="BA119" s="3"/>
-    </row>
-    <row r="120" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB119" s="3"/>
+      <c r="BC119" s="3"/>
+      <c r="BD119" s="3"/>
+      <c r="BE119" s="3"/>
+    </row>
+    <row r="120" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -8063,8 +8641,12 @@
       <c r="AY120" s="3"/>
       <c r="AZ120" s="3"/>
       <c r="BA120" s="3"/>
-    </row>
-    <row r="121" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB120" s="3"/>
+      <c r="BC120" s="3"/>
+      <c r="BD120" s="3"/>
+      <c r="BE120" s="3"/>
+    </row>
+    <row r="121" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -8116,8 +8698,12 @@
       <c r="AY121" s="3"/>
       <c r="AZ121" s="3"/>
       <c r="BA121" s="3"/>
-    </row>
-    <row r="122" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB121" s="3"/>
+      <c r="BC121" s="3"/>
+      <c r="BD121" s="3"/>
+      <c r="BE121" s="3"/>
+    </row>
+    <row r="122" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -8169,8 +8755,12 @@
       <c r="AY122" s="3"/>
       <c r="AZ122" s="3"/>
       <c r="BA122" s="3"/>
-    </row>
-    <row r="123" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB122" s="3"/>
+      <c r="BC122" s="3"/>
+      <c r="BD122" s="3"/>
+      <c r="BE122" s="3"/>
+    </row>
+    <row r="123" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -8222,8 +8812,12 @@
       <c r="AY123" s="3"/>
       <c r="AZ123" s="3"/>
       <c r="BA123" s="3"/>
-    </row>
-    <row r="124" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB123" s="3"/>
+      <c r="BC123" s="3"/>
+      <c r="BD123" s="3"/>
+      <c r="BE123" s="3"/>
+    </row>
+    <row r="124" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -8275,8 +8869,12 @@
       <c r="AY124" s="3"/>
       <c r="AZ124" s="3"/>
       <c r="BA124" s="3"/>
-    </row>
-    <row r="125" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB124" s="3"/>
+      <c r="BC124" s="3"/>
+      <c r="BD124" s="3"/>
+      <c r="BE124" s="3"/>
+    </row>
+    <row r="125" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -8328,8 +8926,12 @@
       <c r="AY125" s="3"/>
       <c r="AZ125" s="3"/>
       <c r="BA125" s="3"/>
-    </row>
-    <row r="126" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB125" s="3"/>
+      <c r="BC125" s="3"/>
+      <c r="BD125" s="3"/>
+      <c r="BE125" s="3"/>
+    </row>
+    <row r="126" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -8381,8 +8983,12 @@
       <c r="AY126" s="3"/>
       <c r="AZ126" s="3"/>
       <c r="BA126" s="3"/>
-    </row>
-    <row r="127" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB126" s="3"/>
+      <c r="BC126" s="3"/>
+      <c r="BD126" s="3"/>
+      <c r="BE126" s="3"/>
+    </row>
+    <row r="127" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -8434,8 +9040,12 @@
       <c r="AY127" s="3"/>
       <c r="AZ127" s="3"/>
       <c r="BA127" s="3"/>
-    </row>
-    <row r="128" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB127" s="3"/>
+      <c r="BC127" s="3"/>
+      <c r="BD127" s="3"/>
+      <c r="BE127" s="3"/>
+    </row>
+    <row r="128" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -8487,8 +9097,12 @@
       <c r="AY128" s="3"/>
       <c r="AZ128" s="3"/>
       <c r="BA128" s="3"/>
-    </row>
-    <row r="129" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB128" s="3"/>
+      <c r="BC128" s="3"/>
+      <c r="BD128" s="3"/>
+      <c r="BE128" s="3"/>
+    </row>
+    <row r="129" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -8540,8 +9154,12 @@
       <c r="AY129" s="3"/>
       <c r="AZ129" s="3"/>
       <c r="BA129" s="3"/>
-    </row>
-    <row r="130" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB129" s="3"/>
+      <c r="BC129" s="3"/>
+      <c r="BD129" s="3"/>
+      <c r="BE129" s="3"/>
+    </row>
+    <row r="130" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -8593,8 +9211,12 @@
       <c r="AY130" s="3"/>
       <c r="AZ130" s="3"/>
       <c r="BA130" s="3"/>
-    </row>
-    <row r="131" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB130" s="3"/>
+      <c r="BC130" s="3"/>
+      <c r="BD130" s="3"/>
+      <c r="BE130" s="3"/>
+    </row>
+    <row r="131" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -8646,8 +9268,12 @@
       <c r="AY131" s="3"/>
       <c r="AZ131" s="3"/>
       <c r="BA131" s="3"/>
-    </row>
-    <row r="132" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB131" s="3"/>
+      <c r="BC131" s="3"/>
+      <c r="BD131" s="3"/>
+      <c r="BE131" s="3"/>
+    </row>
+    <row r="132" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -8699,8 +9325,12 @@
       <c r="AY132" s="3"/>
       <c r="AZ132" s="3"/>
       <c r="BA132" s="3"/>
-    </row>
-    <row r="133" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB132" s="3"/>
+      <c r="BC132" s="3"/>
+      <c r="BD132" s="3"/>
+      <c r="BE132" s="3"/>
+    </row>
+    <row r="133" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -8752,8 +9382,12 @@
       <c r="AY133" s="3"/>
       <c r="AZ133" s="3"/>
       <c r="BA133" s="3"/>
-    </row>
-    <row r="134" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB133" s="3"/>
+      <c r="BC133" s="3"/>
+      <c r="BD133" s="3"/>
+      <c r="BE133" s="3"/>
+    </row>
+    <row r="134" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -8805,8 +9439,12 @@
       <c r="AY134" s="3"/>
       <c r="AZ134" s="3"/>
       <c r="BA134" s="3"/>
-    </row>
-    <row r="135" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB134" s="3"/>
+      <c r="BC134" s="3"/>
+      <c r="BD134" s="3"/>
+      <c r="BE134" s="3"/>
+    </row>
+    <row r="135" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -8858,8 +9496,12 @@
       <c r="AY135" s="3"/>
       <c r="AZ135" s="3"/>
       <c r="BA135" s="3"/>
-    </row>
-    <row r="136" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB135" s="3"/>
+      <c r="BC135" s="3"/>
+      <c r="BD135" s="3"/>
+      <c r="BE135" s="3"/>
+    </row>
+    <row r="136" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -8911,8 +9553,12 @@
       <c r="AY136" s="3"/>
       <c r="AZ136" s="3"/>
       <c r="BA136" s="3"/>
-    </row>
-    <row r="137" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB136" s="3"/>
+      <c r="BC136" s="3"/>
+      <c r="BD136" s="3"/>
+      <c r="BE136" s="3"/>
+    </row>
+    <row r="137" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -8964,8 +9610,12 @@
       <c r="AY137" s="3"/>
       <c r="AZ137" s="3"/>
       <c r="BA137" s="3"/>
-    </row>
-    <row r="138" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB137" s="3"/>
+      <c r="BC137" s="3"/>
+      <c r="BD137" s="3"/>
+      <c r="BE137" s="3"/>
+    </row>
+    <row r="138" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -9017,8 +9667,12 @@
       <c r="AY138" s="3"/>
       <c r="AZ138" s="3"/>
       <c r="BA138" s="3"/>
-    </row>
-    <row r="139" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB138" s="3"/>
+      <c r="BC138" s="3"/>
+      <c r="BD138" s="3"/>
+      <c r="BE138" s="3"/>
+    </row>
+    <row r="139" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -9070,8 +9724,12 @@
       <c r="AY139" s="3"/>
       <c r="AZ139" s="3"/>
       <c r="BA139" s="3"/>
-    </row>
-    <row r="140" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB139" s="3"/>
+      <c r="BC139" s="3"/>
+      <c r="BD139" s="3"/>
+      <c r="BE139" s="3"/>
+    </row>
+    <row r="140" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -9123,8 +9781,12 @@
       <c r="AY140" s="3"/>
       <c r="AZ140" s="3"/>
       <c r="BA140" s="3"/>
-    </row>
-    <row r="141" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB140" s="3"/>
+      <c r="BC140" s="3"/>
+      <c r="BD140" s="3"/>
+      <c r="BE140" s="3"/>
+    </row>
+    <row r="141" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -9176,8 +9838,12 @@
       <c r="AY141" s="3"/>
       <c r="AZ141" s="3"/>
       <c r="BA141" s="3"/>
-    </row>
-    <row r="142" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB141" s="3"/>
+      <c r="BC141" s="3"/>
+      <c r="BD141" s="3"/>
+      <c r="BE141" s="3"/>
+    </row>
+    <row r="142" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -9229,8 +9895,12 @@
       <c r="AY142" s="3"/>
       <c r="AZ142" s="3"/>
       <c r="BA142" s="3"/>
-    </row>
-    <row r="143" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB142" s="3"/>
+      <c r="BC142" s="3"/>
+      <c r="BD142" s="3"/>
+      <c r="BE142" s="3"/>
+    </row>
+    <row r="143" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -9282,8 +9952,12 @@
       <c r="AY143" s="3"/>
       <c r="AZ143" s="3"/>
       <c r="BA143" s="3"/>
-    </row>
-    <row r="144" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB143" s="3"/>
+      <c r="BC143" s="3"/>
+      <c r="BD143" s="3"/>
+      <c r="BE143" s="3"/>
+    </row>
+    <row r="144" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -9335,8 +10009,12 @@
       <c r="AY144" s="3"/>
       <c r="AZ144" s="3"/>
       <c r="BA144" s="3"/>
-    </row>
-    <row r="145" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB144" s="3"/>
+      <c r="BC144" s="3"/>
+      <c r="BD144" s="3"/>
+      <c r="BE144" s="3"/>
+    </row>
+    <row r="145" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -9388,8 +10066,12 @@
       <c r="AY145" s="3"/>
       <c r="AZ145" s="3"/>
       <c r="BA145" s="3"/>
-    </row>
-    <row r="146" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB145" s="3"/>
+      <c r="BC145" s="3"/>
+      <c r="BD145" s="3"/>
+      <c r="BE145" s="3"/>
+    </row>
+    <row r="146" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -9441,8 +10123,12 @@
       <c r="AY146" s="3"/>
       <c r="AZ146" s="3"/>
       <c r="BA146" s="3"/>
-    </row>
-    <row r="147" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB146" s="3"/>
+      <c r="BC146" s="3"/>
+      <c r="BD146" s="3"/>
+      <c r="BE146" s="3"/>
+    </row>
+    <row r="147" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -9494,8 +10180,12 @@
       <c r="AY147" s="3"/>
       <c r="AZ147" s="3"/>
       <c r="BA147" s="3"/>
-    </row>
-    <row r="148" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB147" s="3"/>
+      <c r="BC147" s="3"/>
+      <c r="BD147" s="3"/>
+      <c r="BE147" s="3"/>
+    </row>
+    <row r="148" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -9547,8 +10237,12 @@
       <c r="AY148" s="3"/>
       <c r="AZ148" s="3"/>
       <c r="BA148" s="3"/>
-    </row>
-    <row r="149" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB148" s="3"/>
+      <c r="BC148" s="3"/>
+      <c r="BD148" s="3"/>
+      <c r="BE148" s="3"/>
+    </row>
+    <row r="149" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -9600,8 +10294,12 @@
       <c r="AY149" s="3"/>
       <c r="AZ149" s="3"/>
       <c r="BA149" s="3"/>
-    </row>
-    <row r="150" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB149" s="3"/>
+      <c r="BC149" s="3"/>
+      <c r="BD149" s="3"/>
+      <c r="BE149" s="3"/>
+    </row>
+    <row r="150" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -9653,8 +10351,12 @@
       <c r="AY150" s="3"/>
       <c r="AZ150" s="3"/>
       <c r="BA150" s="3"/>
-    </row>
-    <row r="151" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB150" s="3"/>
+      <c r="BC150" s="3"/>
+      <c r="BD150" s="3"/>
+      <c r="BE150" s="3"/>
+    </row>
+    <row r="151" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -9706,8 +10408,12 @@
       <c r="AY151" s="3"/>
       <c r="AZ151" s="3"/>
       <c r="BA151" s="3"/>
-    </row>
-    <row r="152" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB151" s="3"/>
+      <c r="BC151" s="3"/>
+      <c r="BD151" s="3"/>
+      <c r="BE151" s="3"/>
+    </row>
+    <row r="152" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -9759,8 +10465,12 @@
       <c r="AY152" s="3"/>
       <c r="AZ152" s="3"/>
       <c r="BA152" s="3"/>
-    </row>
-    <row r="153" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB152" s="3"/>
+      <c r="BC152" s="3"/>
+      <c r="BD152" s="3"/>
+      <c r="BE152" s="3"/>
+    </row>
+    <row r="153" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -9812,8 +10522,12 @@
       <c r="AY153" s="3"/>
       <c r="AZ153" s="3"/>
       <c r="BA153" s="3"/>
-    </row>
-    <row r="154" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB153" s="3"/>
+      <c r="BC153" s="3"/>
+      <c r="BD153" s="3"/>
+      <c r="BE153" s="3"/>
+    </row>
+    <row r="154" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -9865,8 +10579,12 @@
       <c r="AY154" s="3"/>
       <c r="AZ154" s="3"/>
       <c r="BA154" s="3"/>
-    </row>
-    <row r="155" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB154" s="3"/>
+      <c r="BC154" s="3"/>
+      <c r="BD154" s="3"/>
+      <c r="BE154" s="3"/>
+    </row>
+    <row r="155" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -9918,8 +10636,12 @@
       <c r="AY155" s="3"/>
       <c r="AZ155" s="3"/>
       <c r="BA155" s="3"/>
-    </row>
-    <row r="156" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB155" s="3"/>
+      <c r="BC155" s="3"/>
+      <c r="BD155" s="3"/>
+      <c r="BE155" s="3"/>
+    </row>
+    <row r="156" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -9971,8 +10693,12 @@
       <c r="AY156" s="3"/>
       <c r="AZ156" s="3"/>
       <c r="BA156" s="3"/>
-    </row>
-    <row r="157" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB156" s="3"/>
+      <c r="BC156" s="3"/>
+      <c r="BD156" s="3"/>
+      <c r="BE156" s="3"/>
+    </row>
+    <row r="157" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -10024,8 +10750,12 @@
       <c r="AY157" s="3"/>
       <c r="AZ157" s="3"/>
       <c r="BA157" s="3"/>
-    </row>
-    <row r="158" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB157" s="3"/>
+      <c r="BC157" s="3"/>
+      <c r="BD157" s="3"/>
+      <c r="BE157" s="3"/>
+    </row>
+    <row r="158" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -10077,8 +10807,12 @@
       <c r="AY158" s="3"/>
       <c r="AZ158" s="3"/>
       <c r="BA158" s="3"/>
-    </row>
-    <row r="159" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB158" s="3"/>
+      <c r="BC158" s="3"/>
+      <c r="BD158" s="3"/>
+      <c r="BE158" s="3"/>
+    </row>
+    <row r="159" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -10130,8 +10864,12 @@
       <c r="AY159" s="3"/>
       <c r="AZ159" s="3"/>
       <c r="BA159" s="3"/>
-    </row>
-    <row r="160" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB159" s="3"/>
+      <c r="BC159" s="3"/>
+      <c r="BD159" s="3"/>
+      <c r="BE159" s="3"/>
+    </row>
+    <row r="160" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -10183,8 +10921,12 @@
       <c r="AY160" s="3"/>
       <c r="AZ160" s="3"/>
       <c r="BA160" s="3"/>
-    </row>
-    <row r="161" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB160" s="3"/>
+      <c r="BC160" s="3"/>
+      <c r="BD160" s="3"/>
+      <c r="BE160" s="3"/>
+    </row>
+    <row r="161" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -10236,8 +10978,12 @@
       <c r="AY161" s="3"/>
       <c r="AZ161" s="3"/>
       <c r="BA161" s="3"/>
-    </row>
-    <row r="162" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB161" s="3"/>
+      <c r="BC161" s="3"/>
+      <c r="BD161" s="3"/>
+      <c r="BE161" s="3"/>
+    </row>
+    <row r="162" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -10289,8 +11035,12 @@
       <c r="AY162" s="3"/>
       <c r="AZ162" s="3"/>
       <c r="BA162" s="3"/>
-    </row>
-    <row r="163" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB162" s="3"/>
+      <c r="BC162" s="3"/>
+      <c r="BD162" s="3"/>
+      <c r="BE162" s="3"/>
+    </row>
+    <row r="163" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -10342,8 +11092,12 @@
       <c r="AY163" s="3"/>
       <c r="AZ163" s="3"/>
       <c r="BA163" s="3"/>
-    </row>
-    <row r="164" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB163" s="3"/>
+      <c r="BC163" s="3"/>
+      <c r="BD163" s="3"/>
+      <c r="BE163" s="3"/>
+    </row>
+    <row r="164" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -10395,8 +11149,12 @@
       <c r="AY164" s="3"/>
       <c r="AZ164" s="3"/>
       <c r="BA164" s="3"/>
-    </row>
-    <row r="165" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB164" s="3"/>
+      <c r="BC164" s="3"/>
+      <c r="BD164" s="3"/>
+      <c r="BE164" s="3"/>
+    </row>
+    <row r="165" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -10448,8 +11206,12 @@
       <c r="AY165" s="3"/>
       <c r="AZ165" s="3"/>
       <c r="BA165" s="3"/>
-    </row>
-    <row r="166" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB165" s="3"/>
+      <c r="BC165" s="3"/>
+      <c r="BD165" s="3"/>
+      <c r="BE165" s="3"/>
+    </row>
+    <row r="166" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -10501,8 +11263,12 @@
       <c r="AY166" s="3"/>
       <c r="AZ166" s="3"/>
       <c r="BA166" s="3"/>
-    </row>
-    <row r="167" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB166" s="3"/>
+      <c r="BC166" s="3"/>
+      <c r="BD166" s="3"/>
+      <c r="BE166" s="3"/>
+    </row>
+    <row r="167" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -10554,8 +11320,12 @@
       <c r="AY167" s="3"/>
       <c r="AZ167" s="3"/>
       <c r="BA167" s="3"/>
-    </row>
-    <row r="168" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB167" s="3"/>
+      <c r="BC167" s="3"/>
+      <c r="BD167" s="3"/>
+      <c r="BE167" s="3"/>
+    </row>
+    <row r="168" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -10607,8 +11377,12 @@
       <c r="AY168" s="3"/>
       <c r="AZ168" s="3"/>
       <c r="BA168" s="3"/>
-    </row>
-    <row r="169" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB168" s="3"/>
+      <c r="BC168" s="3"/>
+      <c r="BD168" s="3"/>
+      <c r="BE168" s="3"/>
+    </row>
+    <row r="169" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -10660,8 +11434,12 @@
       <c r="AY169" s="3"/>
       <c r="AZ169" s="3"/>
       <c r="BA169" s="3"/>
-    </row>
-    <row r="170" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB169" s="3"/>
+      <c r="BC169" s="3"/>
+      <c r="BD169" s="3"/>
+      <c r="BE169" s="3"/>
+    </row>
+    <row r="170" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -10713,8 +11491,12 @@
       <c r="AY170" s="3"/>
       <c r="AZ170" s="3"/>
       <c r="BA170" s="3"/>
-    </row>
-    <row r="171" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB170" s="3"/>
+      <c r="BC170" s="3"/>
+      <c r="BD170" s="3"/>
+      <c r="BE170" s="3"/>
+    </row>
+    <row r="171" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -10766,8 +11548,12 @@
       <c r="AY171" s="3"/>
       <c r="AZ171" s="3"/>
       <c r="BA171" s="3"/>
-    </row>
-    <row r="172" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB171" s="3"/>
+      <c r="BC171" s="3"/>
+      <c r="BD171" s="3"/>
+      <c r="BE171" s="3"/>
+    </row>
+    <row r="172" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -10819,8 +11605,12 @@
       <c r="AY172" s="3"/>
       <c r="AZ172" s="3"/>
       <c r="BA172" s="3"/>
-    </row>
-    <row r="173" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB172" s="3"/>
+      <c r="BC172" s="3"/>
+      <c r="BD172" s="3"/>
+      <c r="BE172" s="3"/>
+    </row>
+    <row r="173" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -10872,8 +11662,12 @@
       <c r="AY173" s="3"/>
       <c r="AZ173" s="3"/>
       <c r="BA173" s="3"/>
-    </row>
-    <row r="174" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB173" s="3"/>
+      <c r="BC173" s="3"/>
+      <c r="BD173" s="3"/>
+      <c r="BE173" s="3"/>
+    </row>
+    <row r="174" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -10925,8 +11719,12 @@
       <c r="AY174" s="3"/>
       <c r="AZ174" s="3"/>
       <c r="BA174" s="3"/>
-    </row>
-    <row r="175" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB174" s="3"/>
+      <c r="BC174" s="3"/>
+      <c r="BD174" s="3"/>
+      <c r="BE174" s="3"/>
+    </row>
+    <row r="175" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -10978,8 +11776,12 @@
       <c r="AY175" s="3"/>
       <c r="AZ175" s="3"/>
       <c r="BA175" s="3"/>
-    </row>
-    <row r="176" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB175" s="3"/>
+      <c r="BC175" s="3"/>
+      <c r="BD175" s="3"/>
+      <c r="BE175" s="3"/>
+    </row>
+    <row r="176" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -11031,8 +11833,12 @@
       <c r="AY176" s="3"/>
       <c r="AZ176" s="3"/>
       <c r="BA176" s="3"/>
-    </row>
-    <row r="177" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB176" s="3"/>
+      <c r="BC176" s="3"/>
+      <c r="BD176" s="3"/>
+      <c r="BE176" s="3"/>
+    </row>
+    <row r="177" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -11084,8 +11890,12 @@
       <c r="AY177" s="3"/>
       <c r="AZ177" s="3"/>
       <c r="BA177" s="3"/>
-    </row>
-    <row r="178" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB177" s="3"/>
+      <c r="BC177" s="3"/>
+      <c r="BD177" s="3"/>
+      <c r="BE177" s="3"/>
+    </row>
+    <row r="178" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -11137,8 +11947,12 @@
       <c r="AY178" s="3"/>
       <c r="AZ178" s="3"/>
       <c r="BA178" s="3"/>
-    </row>
-    <row r="179" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB178" s="3"/>
+      <c r="BC178" s="3"/>
+      <c r="BD178" s="3"/>
+      <c r="BE178" s="3"/>
+    </row>
+    <row r="179" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -11190,8 +12004,12 @@
       <c r="AY179" s="3"/>
       <c r="AZ179" s="3"/>
       <c r="BA179" s="3"/>
-    </row>
-    <row r="180" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB179" s="3"/>
+      <c r="BC179" s="3"/>
+      <c r="BD179" s="3"/>
+      <c r="BE179" s="3"/>
+    </row>
+    <row r="180" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -11243,8 +12061,12 @@
       <c r="AY180" s="3"/>
       <c r="AZ180" s="3"/>
       <c r="BA180" s="3"/>
-    </row>
-    <row r="181" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB180" s="3"/>
+      <c r="BC180" s="3"/>
+      <c r="BD180" s="3"/>
+      <c r="BE180" s="3"/>
+    </row>
+    <row r="181" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -11296,8 +12118,12 @@
       <c r="AY181" s="3"/>
       <c r="AZ181" s="3"/>
       <c r="BA181" s="3"/>
-    </row>
-    <row r="182" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB181" s="3"/>
+      <c r="BC181" s="3"/>
+      <c r="BD181" s="3"/>
+      <c r="BE181" s="3"/>
+    </row>
+    <row r="182" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -11349,8 +12175,12 @@
       <c r="AY182" s="3"/>
       <c r="AZ182" s="3"/>
       <c r="BA182" s="3"/>
-    </row>
-    <row r="183" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB182" s="3"/>
+      <c r="BC182" s="3"/>
+      <c r="BD182" s="3"/>
+      <c r="BE182" s="3"/>
+    </row>
+    <row r="183" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -11402,8 +12232,12 @@
       <c r="AY183" s="3"/>
       <c r="AZ183" s="3"/>
       <c r="BA183" s="3"/>
-    </row>
-    <row r="184" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB183" s="3"/>
+      <c r="BC183" s="3"/>
+      <c r="BD183" s="3"/>
+      <c r="BE183" s="3"/>
+    </row>
+    <row r="184" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -11455,8 +12289,12 @@
       <c r="AY184" s="3"/>
       <c r="AZ184" s="3"/>
       <c r="BA184" s="3"/>
-    </row>
-    <row r="185" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB184" s="3"/>
+      <c r="BC184" s="3"/>
+      <c r="BD184" s="3"/>
+      <c r="BE184" s="3"/>
+    </row>
+    <row r="185" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -11508,8 +12346,12 @@
       <c r="AY185" s="3"/>
       <c r="AZ185" s="3"/>
       <c r="BA185" s="3"/>
-    </row>
-    <row r="186" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB185" s="3"/>
+      <c r="BC185" s="3"/>
+      <c r="BD185" s="3"/>
+      <c r="BE185" s="3"/>
+    </row>
+    <row r="186" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -11561,8 +12403,12 @@
       <c r="AY186" s="3"/>
       <c r="AZ186" s="3"/>
       <c r="BA186" s="3"/>
-    </row>
-    <row r="187" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB186" s="3"/>
+      <c r="BC186" s="3"/>
+      <c r="BD186" s="3"/>
+      <c r="BE186" s="3"/>
+    </row>
+    <row r="187" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -11614,8 +12460,12 @@
       <c r="AY187" s="3"/>
       <c r="AZ187" s="3"/>
       <c r="BA187" s="3"/>
-    </row>
-    <row r="188" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB187" s="3"/>
+      <c r="BC187" s="3"/>
+      <c r="BD187" s="3"/>
+      <c r="BE187" s="3"/>
+    </row>
+    <row r="188" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -11667,8 +12517,12 @@
       <c r="AY188" s="3"/>
       <c r="AZ188" s="3"/>
       <c r="BA188" s="3"/>
-    </row>
-    <row r="189" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB188" s="3"/>
+      <c r="BC188" s="3"/>
+      <c r="BD188" s="3"/>
+      <c r="BE188" s="3"/>
+    </row>
+    <row r="189" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -11720,8 +12574,12 @@
       <c r="AY189" s="3"/>
       <c r="AZ189" s="3"/>
       <c r="BA189" s="3"/>
-    </row>
-    <row r="190" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB189" s="3"/>
+      <c r="BC189" s="3"/>
+      <c r="BD189" s="3"/>
+      <c r="BE189" s="3"/>
+    </row>
+    <row r="190" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -11773,8 +12631,12 @@
       <c r="AY190" s="3"/>
       <c r="AZ190" s="3"/>
       <c r="BA190" s="3"/>
-    </row>
-    <row r="191" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB190" s="3"/>
+      <c r="BC190" s="3"/>
+      <c r="BD190" s="3"/>
+      <c r="BE190" s="3"/>
+    </row>
+    <row r="191" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -11826,8 +12688,12 @@
       <c r="AY191" s="3"/>
       <c r="AZ191" s="3"/>
       <c r="BA191" s="3"/>
-    </row>
-    <row r="192" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB191" s="3"/>
+      <c r="BC191" s="3"/>
+      <c r="BD191" s="3"/>
+      <c r="BE191" s="3"/>
+    </row>
+    <row r="192" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -11879,8 +12745,12 @@
       <c r="AY192" s="3"/>
       <c r="AZ192" s="3"/>
       <c r="BA192" s="3"/>
-    </row>
-    <row r="193" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB192" s="3"/>
+      <c r="BC192" s="3"/>
+      <c r="BD192" s="3"/>
+      <c r="BE192" s="3"/>
+    </row>
+    <row r="193" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -11932,8 +12802,12 @@
       <c r="AY193" s="3"/>
       <c r="AZ193" s="3"/>
       <c r="BA193" s="3"/>
-    </row>
-    <row r="194" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB193" s="3"/>
+      <c r="BC193" s="3"/>
+      <c r="BD193" s="3"/>
+      <c r="BE193" s="3"/>
+    </row>
+    <row r="194" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -11985,8 +12859,12 @@
       <c r="AY194" s="3"/>
       <c r="AZ194" s="3"/>
       <c r="BA194" s="3"/>
-    </row>
-    <row r="195" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB194" s="3"/>
+      <c r="BC194" s="3"/>
+      <c r="BD194" s="3"/>
+      <c r="BE194" s="3"/>
+    </row>
+    <row r="195" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -12038,8 +12916,12 @@
       <c r="AY195" s="3"/>
       <c r="AZ195" s="3"/>
       <c r="BA195" s="3"/>
-    </row>
-    <row r="196" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB195" s="3"/>
+      <c r="BC195" s="3"/>
+      <c r="BD195" s="3"/>
+      <c r="BE195" s="3"/>
+    </row>
+    <row r="196" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -12091,8 +12973,12 @@
       <c r="AY196" s="3"/>
       <c r="AZ196" s="3"/>
       <c r="BA196" s="3"/>
-    </row>
-    <row r="197" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB196" s="3"/>
+      <c r="BC196" s="3"/>
+      <c r="BD196" s="3"/>
+      <c r="BE196" s="3"/>
+    </row>
+    <row r="197" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -12144,8 +13030,12 @@
       <c r="AY197" s="3"/>
       <c r="AZ197" s="3"/>
       <c r="BA197" s="3"/>
-    </row>
-    <row r="198" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB197" s="3"/>
+      <c r="BC197" s="3"/>
+      <c r="BD197" s="3"/>
+      <c r="BE197" s="3"/>
+    </row>
+    <row r="198" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -12197,8 +13087,12 @@
       <c r="AY198" s="3"/>
       <c r="AZ198" s="3"/>
       <c r="BA198" s="3"/>
-    </row>
-    <row r="199" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB198" s="3"/>
+      <c r="BC198" s="3"/>
+      <c r="BD198" s="3"/>
+      <c r="BE198" s="3"/>
+    </row>
+    <row r="199" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -12250,8 +13144,12 @@
       <c r="AY199" s="3"/>
       <c r="AZ199" s="3"/>
       <c r="BA199" s="3"/>
-    </row>
-    <row r="200" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB199" s="3"/>
+      <c r="BC199" s="3"/>
+      <c r="BD199" s="3"/>
+      <c r="BE199" s="3"/>
+    </row>
+    <row r="200" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -12303,8 +13201,12 @@
       <c r="AY200" s="3"/>
       <c r="AZ200" s="3"/>
       <c r="BA200" s="3"/>
-    </row>
-    <row r="201" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB200" s="3"/>
+      <c r="BC200" s="3"/>
+      <c r="BD200" s="3"/>
+      <c r="BE200" s="3"/>
+    </row>
+    <row r="201" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -12356,8 +13258,12 @@
       <c r="AY201" s="3"/>
       <c r="AZ201" s="3"/>
       <c r="BA201" s="3"/>
-    </row>
-    <row r="202" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB201" s="3"/>
+      <c r="BC201" s="3"/>
+      <c r="BD201" s="3"/>
+      <c r="BE201" s="3"/>
+    </row>
+    <row r="202" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -12409,8 +13315,12 @@
       <c r="AY202" s="3"/>
       <c r="AZ202" s="3"/>
       <c r="BA202" s="3"/>
-    </row>
-    <row r="203" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB202" s="3"/>
+      <c r="BC202" s="3"/>
+      <c r="BD202" s="3"/>
+      <c r="BE202" s="3"/>
+    </row>
+    <row r="203" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -12462,8 +13372,12 @@
       <c r="AY203" s="3"/>
       <c r="AZ203" s="3"/>
       <c r="BA203" s="3"/>
-    </row>
-    <row r="204" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB203" s="3"/>
+      <c r="BC203" s="3"/>
+      <c r="BD203" s="3"/>
+      <c r="BE203" s="3"/>
+    </row>
+    <row r="204" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -12515,8 +13429,12 @@
       <c r="AY204" s="3"/>
       <c r="AZ204" s="3"/>
       <c r="BA204" s="3"/>
-    </row>
-    <row r="205" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB204" s="3"/>
+      <c r="BC204" s="3"/>
+      <c r="BD204" s="3"/>
+      <c r="BE204" s="3"/>
+    </row>
+    <row r="205" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -12568,8 +13486,12 @@
       <c r="AY205" s="3"/>
       <c r="AZ205" s="3"/>
       <c r="BA205" s="3"/>
-    </row>
-    <row r="206" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB205" s="3"/>
+      <c r="BC205" s="3"/>
+      <c r="BD205" s="3"/>
+      <c r="BE205" s="3"/>
+    </row>
+    <row r="206" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -12621,8 +13543,12 @@
       <c r="AY206" s="3"/>
       <c r="AZ206" s="3"/>
       <c r="BA206" s="3"/>
-    </row>
-    <row r="207" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB206" s="3"/>
+      <c r="BC206" s="3"/>
+      <c r="BD206" s="3"/>
+      <c r="BE206" s="3"/>
+    </row>
+    <row r="207" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -12674,8 +13600,12 @@
       <c r="AY207" s="3"/>
       <c r="AZ207" s="3"/>
       <c r="BA207" s="3"/>
-    </row>
-    <row r="208" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB207" s="3"/>
+      <c r="BC207" s="3"/>
+      <c r="BD207" s="3"/>
+      <c r="BE207" s="3"/>
+    </row>
+    <row r="208" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -12727,8 +13657,12 @@
       <c r="AY208" s="3"/>
       <c r="AZ208" s="3"/>
       <c r="BA208" s="3"/>
-    </row>
-    <row r="209" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB208" s="3"/>
+      <c r="BC208" s="3"/>
+      <c r="BD208" s="3"/>
+      <c r="BE208" s="3"/>
+    </row>
+    <row r="209" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -12780,8 +13714,12 @@
       <c r="AY209" s="3"/>
       <c r="AZ209" s="3"/>
       <c r="BA209" s="3"/>
-    </row>
-    <row r="210" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB209" s="3"/>
+      <c r="BC209" s="3"/>
+      <c r="BD209" s="3"/>
+      <c r="BE209" s="3"/>
+    </row>
+    <row r="210" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -12833,8 +13771,12 @@
       <c r="AY210" s="3"/>
       <c r="AZ210" s="3"/>
       <c r="BA210" s="3"/>
-    </row>
-    <row r="211" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB210" s="3"/>
+      <c r="BC210" s="3"/>
+      <c r="BD210" s="3"/>
+      <c r="BE210" s="3"/>
+    </row>
+    <row r="211" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -12886,8 +13828,12 @@
       <c r="AY211" s="3"/>
       <c r="AZ211" s="3"/>
       <c r="BA211" s="3"/>
-    </row>
-    <row r="212" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB211" s="3"/>
+      <c r="BC211" s="3"/>
+      <c r="BD211" s="3"/>
+      <c r="BE211" s="3"/>
+    </row>
+    <row r="212" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -12939,8 +13885,12 @@
       <c r="AY212" s="3"/>
       <c r="AZ212" s="3"/>
       <c r="BA212" s="3"/>
-    </row>
-    <row r="213" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB212" s="3"/>
+      <c r="BC212" s="3"/>
+      <c r="BD212" s="3"/>
+      <c r="BE212" s="3"/>
+    </row>
+    <row r="213" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -12992,8 +13942,12 @@
       <c r="AY213" s="3"/>
       <c r="AZ213" s="3"/>
       <c r="BA213" s="3"/>
-    </row>
-    <row r="214" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB213" s="3"/>
+      <c r="BC213" s="3"/>
+      <c r="BD213" s="3"/>
+      <c r="BE213" s="3"/>
+    </row>
+    <row r="214" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -13045,8 +13999,12 @@
       <c r="AY214" s="3"/>
       <c r="AZ214" s="3"/>
       <c r="BA214" s="3"/>
-    </row>
-    <row r="215" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB214" s="3"/>
+      <c r="BC214" s="3"/>
+      <c r="BD214" s="3"/>
+      <c r="BE214" s="3"/>
+    </row>
+    <row r="215" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -13098,8 +14056,12 @@
       <c r="AY215" s="3"/>
       <c r="AZ215" s="3"/>
       <c r="BA215" s="3"/>
-    </row>
-    <row r="216" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB215" s="3"/>
+      <c r="BC215" s="3"/>
+      <c r="BD215" s="3"/>
+      <c r="BE215" s="3"/>
+    </row>
+    <row r="216" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -13151,8 +14113,12 @@
       <c r="AY216" s="3"/>
       <c r="AZ216" s="3"/>
       <c r="BA216" s="3"/>
-    </row>
-    <row r="217" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB216" s="3"/>
+      <c r="BC216" s="3"/>
+      <c r="BD216" s="3"/>
+      <c r="BE216" s="3"/>
+    </row>
+    <row r="217" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -13204,8 +14170,12 @@
       <c r="AY217" s="3"/>
       <c r="AZ217" s="3"/>
       <c r="BA217" s="3"/>
-    </row>
-    <row r="218" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB217" s="3"/>
+      <c r="BC217" s="3"/>
+      <c r="BD217" s="3"/>
+      <c r="BE217" s="3"/>
+    </row>
+    <row r="218" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -13257,8 +14227,12 @@
       <c r="AY218" s="3"/>
       <c r="AZ218" s="3"/>
       <c r="BA218" s="3"/>
-    </row>
-    <row r="219" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB218" s="3"/>
+      <c r="BC218" s="3"/>
+      <c r="BD218" s="3"/>
+      <c r="BE218" s="3"/>
+    </row>
+    <row r="219" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -13310,8 +14284,12 @@
       <c r="AY219" s="3"/>
       <c r="AZ219" s="3"/>
       <c r="BA219" s="3"/>
-    </row>
-    <row r="220" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB219" s="3"/>
+      <c r="BC219" s="3"/>
+      <c r="BD219" s="3"/>
+      <c r="BE219" s="3"/>
+    </row>
+    <row r="220" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -13363,8 +14341,12 @@
       <c r="AY220" s="3"/>
       <c r="AZ220" s="3"/>
       <c r="BA220" s="3"/>
-    </row>
-    <row r="221" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB220" s="3"/>
+      <c r="BC220" s="3"/>
+      <c r="BD220" s="3"/>
+      <c r="BE220" s="3"/>
+    </row>
+    <row r="221" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -13416,8 +14398,12 @@
       <c r="AY221" s="3"/>
       <c r="AZ221" s="3"/>
       <c r="BA221" s="3"/>
-    </row>
-    <row r="222" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB221" s="3"/>
+      <c r="BC221" s="3"/>
+      <c r="BD221" s="3"/>
+      <c r="BE221" s="3"/>
+    </row>
+    <row r="222" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -13469,8 +14455,12 @@
       <c r="AY222" s="3"/>
       <c r="AZ222" s="3"/>
       <c r="BA222" s="3"/>
-    </row>
-    <row r="223" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB222" s="3"/>
+      <c r="BC222" s="3"/>
+      <c r="BD222" s="3"/>
+      <c r="BE222" s="3"/>
+    </row>
+    <row r="223" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -13522,8 +14512,12 @@
       <c r="AY223" s="3"/>
       <c r="AZ223" s="3"/>
       <c r="BA223" s="3"/>
-    </row>
-    <row r="224" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB223" s="3"/>
+      <c r="BC223" s="3"/>
+      <c r="BD223" s="3"/>
+      <c r="BE223" s="3"/>
+    </row>
+    <row r="224" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -13575,8 +14569,12 @@
       <c r="AY224" s="3"/>
       <c r="AZ224" s="3"/>
       <c r="BA224" s="3"/>
-    </row>
-    <row r="225" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB224" s="3"/>
+      <c r="BC224" s="3"/>
+      <c r="BD224" s="3"/>
+      <c r="BE224" s="3"/>
+    </row>
+    <row r="225" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -13628,8 +14626,12 @@
       <c r="AY225" s="3"/>
       <c r="AZ225" s="3"/>
       <c r="BA225" s="3"/>
-    </row>
-    <row r="226" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB225" s="3"/>
+      <c r="BC225" s="3"/>
+      <c r="BD225" s="3"/>
+      <c r="BE225" s="3"/>
+    </row>
+    <row r="226" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -13681,8 +14683,12 @@
       <c r="AY226" s="3"/>
       <c r="AZ226" s="3"/>
       <c r="BA226" s="3"/>
-    </row>
-    <row r="227" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB226" s="3"/>
+      <c r="BC226" s="3"/>
+      <c r="BD226" s="3"/>
+      <c r="BE226" s="3"/>
+    </row>
+    <row r="227" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -13734,8 +14740,12 @@
       <c r="AY227" s="3"/>
       <c r="AZ227" s="3"/>
       <c r="BA227" s="3"/>
-    </row>
-    <row r="228" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB227" s="3"/>
+      <c r="BC227" s="3"/>
+      <c r="BD227" s="3"/>
+      <c r="BE227" s="3"/>
+    </row>
+    <row r="228" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -13787,8 +14797,12 @@
       <c r="AY228" s="3"/>
       <c r="AZ228" s="3"/>
       <c r="BA228" s="3"/>
-    </row>
-    <row r="229" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB228" s="3"/>
+      <c r="BC228" s="3"/>
+      <c r="BD228" s="3"/>
+      <c r="BE228" s="3"/>
+    </row>
+    <row r="229" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -13840,8 +14854,12 @@
       <c r="AY229" s="3"/>
       <c r="AZ229" s="3"/>
       <c r="BA229" s="3"/>
-    </row>
-    <row r="230" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB229" s="3"/>
+      <c r="BC229" s="3"/>
+      <c r="BD229" s="3"/>
+      <c r="BE229" s="3"/>
+    </row>
+    <row r="230" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -13893,8 +14911,12 @@
       <c r="AY230" s="3"/>
       <c r="AZ230" s="3"/>
       <c r="BA230" s="3"/>
-    </row>
-    <row r="231" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB230" s="3"/>
+      <c r="BC230" s="3"/>
+      <c r="BD230" s="3"/>
+      <c r="BE230" s="3"/>
+    </row>
+    <row r="231" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -13946,8 +14968,12 @@
       <c r="AY231" s="3"/>
       <c r="AZ231" s="3"/>
       <c r="BA231" s="3"/>
-    </row>
-    <row r="232" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB231" s="3"/>
+      <c r="BC231" s="3"/>
+      <c r="BD231" s="3"/>
+      <c r="BE231" s="3"/>
+    </row>
+    <row r="232" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -13999,8 +15025,12 @@
       <c r="AY232" s="3"/>
       <c r="AZ232" s="3"/>
       <c r="BA232" s="3"/>
-    </row>
-    <row r="233" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB232" s="3"/>
+      <c r="BC232" s="3"/>
+      <c r="BD232" s="3"/>
+      <c r="BE232" s="3"/>
+    </row>
+    <row r="233" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -14052,8 +15082,12 @@
       <c r="AY233" s="3"/>
       <c r="AZ233" s="3"/>
       <c r="BA233" s="3"/>
-    </row>
-    <row r="234" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB233" s="3"/>
+      <c r="BC233" s="3"/>
+      <c r="BD233" s="3"/>
+      <c r="BE233" s="3"/>
+    </row>
+    <row r="234" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -14105,8 +15139,12 @@
       <c r="AY234" s="3"/>
       <c r="AZ234" s="3"/>
       <c r="BA234" s="3"/>
-    </row>
-    <row r="235" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB234" s="3"/>
+      <c r="BC234" s="3"/>
+      <c r="BD234" s="3"/>
+      <c r="BE234" s="3"/>
+    </row>
+    <row r="235" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -14158,8 +15196,12 @@
       <c r="AY235" s="3"/>
       <c r="AZ235" s="3"/>
       <c r="BA235" s="3"/>
-    </row>
-    <row r="236" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB235" s="3"/>
+      <c r="BC235" s="3"/>
+      <c r="BD235" s="3"/>
+      <c r="BE235" s="3"/>
+    </row>
+    <row r="236" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -14211,8 +15253,12 @@
       <c r="AY236" s="3"/>
       <c r="AZ236" s="3"/>
       <c r="BA236" s="3"/>
-    </row>
-    <row r="237" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB236" s="3"/>
+      <c r="BC236" s="3"/>
+      <c r="BD236" s="3"/>
+      <c r="BE236" s="3"/>
+    </row>
+    <row r="237" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -14264,8 +15310,12 @@
       <c r="AY237" s="3"/>
       <c r="AZ237" s="3"/>
       <c r="BA237" s="3"/>
-    </row>
-    <row r="238" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB237" s="3"/>
+      <c r="BC237" s="3"/>
+      <c r="BD237" s="3"/>
+      <c r="BE237" s="3"/>
+    </row>
+    <row r="238" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -14317,8 +15367,12 @@
       <c r="AY238" s="3"/>
       <c r="AZ238" s="3"/>
       <c r="BA238" s="3"/>
-    </row>
-    <row r="239" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB238" s="3"/>
+      <c r="BC238" s="3"/>
+      <c r="BD238" s="3"/>
+      <c r="BE238" s="3"/>
+    </row>
+    <row r="239" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -14370,8 +15424,12 @@
       <c r="AY239" s="3"/>
       <c r="AZ239" s="3"/>
       <c r="BA239" s="3"/>
-    </row>
-    <row r="240" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB239" s="3"/>
+      <c r="BC239" s="3"/>
+      <c r="BD239" s="3"/>
+      <c r="BE239" s="3"/>
+    </row>
+    <row r="240" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -14423,8 +15481,12 @@
       <c r="AY240" s="3"/>
       <c r="AZ240" s="3"/>
       <c r="BA240" s="3"/>
-    </row>
-    <row r="241" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB240" s="3"/>
+      <c r="BC240" s="3"/>
+      <c r="BD240" s="3"/>
+      <c r="BE240" s="3"/>
+    </row>
+    <row r="241" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -14476,8 +15538,12 @@
       <c r="AY241" s="3"/>
       <c r="AZ241" s="3"/>
       <c r="BA241" s="3"/>
-    </row>
-    <row r="242" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB241" s="3"/>
+      <c r="BC241" s="3"/>
+      <c r="BD241" s="3"/>
+      <c r="BE241" s="3"/>
+    </row>
+    <row r="242" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -14529,8 +15595,12 @@
       <c r="AY242" s="3"/>
       <c r="AZ242" s="3"/>
       <c r="BA242" s="3"/>
-    </row>
-    <row r="243" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB242" s="3"/>
+      <c r="BC242" s="3"/>
+      <c r="BD242" s="3"/>
+      <c r="BE242" s="3"/>
+    </row>
+    <row r="243" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -14582,8 +15652,12 @@
       <c r="AY243" s="3"/>
       <c r="AZ243" s="3"/>
       <c r="BA243" s="3"/>
-    </row>
-    <row r="244" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB243" s="3"/>
+      <c r="BC243" s="3"/>
+      <c r="BD243" s="3"/>
+      <c r="BE243" s="3"/>
+    </row>
+    <row r="244" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -14635,8 +15709,12 @@
       <c r="AY244" s="3"/>
       <c r="AZ244" s="3"/>
       <c r="BA244" s="3"/>
-    </row>
-    <row r="245" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB244" s="3"/>
+      <c r="BC244" s="3"/>
+      <c r="BD244" s="3"/>
+      <c r="BE244" s="3"/>
+    </row>
+    <row r="245" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -14688,8 +15766,12 @@
       <c r="AY245" s="3"/>
       <c r="AZ245" s="3"/>
       <c r="BA245" s="3"/>
-    </row>
-    <row r="246" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB245" s="3"/>
+      <c r="BC245" s="3"/>
+      <c r="BD245" s="3"/>
+      <c r="BE245" s="3"/>
+    </row>
+    <row r="246" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -14741,8 +15823,12 @@
       <c r="AY246" s="3"/>
       <c r="AZ246" s="3"/>
       <c r="BA246" s="3"/>
-    </row>
-    <row r="247" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB246" s="3"/>
+      <c r="BC246" s="3"/>
+      <c r="BD246" s="3"/>
+      <c r="BE246" s="3"/>
+    </row>
+    <row r="247" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -14794,8 +15880,12 @@
       <c r="AY247" s="3"/>
       <c r="AZ247" s="3"/>
       <c r="BA247" s="3"/>
-    </row>
-    <row r="248" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB247" s="3"/>
+      <c r="BC247" s="3"/>
+      <c r="BD247" s="3"/>
+      <c r="BE247" s="3"/>
+    </row>
+    <row r="248" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -14847,8 +15937,12 @@
       <c r="AY248" s="3"/>
       <c r="AZ248" s="3"/>
       <c r="BA248" s="3"/>
-    </row>
-    <row r="249" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB248" s="3"/>
+      <c r="BC248" s="3"/>
+      <c r="BD248" s="3"/>
+      <c r="BE248" s="3"/>
+    </row>
+    <row r="249" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -14900,8 +15994,12 @@
       <c r="AY249" s="3"/>
       <c r="AZ249" s="3"/>
       <c r="BA249" s="3"/>
-    </row>
-    <row r="250" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB249" s="3"/>
+      <c r="BC249" s="3"/>
+      <c r="BD249" s="3"/>
+      <c r="BE249" s="3"/>
+    </row>
+    <row r="250" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -14953,8 +16051,12 @@
       <c r="AY250" s="3"/>
       <c r="AZ250" s="3"/>
       <c r="BA250" s="3"/>
-    </row>
-    <row r="251" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB250" s="3"/>
+      <c r="BC250" s="3"/>
+      <c r="BD250" s="3"/>
+      <c r="BE250" s="3"/>
+    </row>
+    <row r="251" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -15006,8 +16108,12 @@
       <c r="AY251" s="3"/>
       <c r="AZ251" s="3"/>
       <c r="BA251" s="3"/>
-    </row>
-    <row r="252" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB251" s="3"/>
+      <c r="BC251" s="3"/>
+      <c r="BD251" s="3"/>
+      <c r="BE251" s="3"/>
+    </row>
+    <row r="252" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -15059,8 +16165,12 @@
       <c r="AY252" s="3"/>
       <c r="AZ252" s="3"/>
       <c r="BA252" s="3"/>
-    </row>
-    <row r="253" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB252" s="3"/>
+      <c r="BC252" s="3"/>
+      <c r="BD252" s="3"/>
+      <c r="BE252" s="3"/>
+    </row>
+    <row r="253" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -15112,8 +16222,12 @@
       <c r="AY253" s="3"/>
       <c r="AZ253" s="3"/>
       <c r="BA253" s="3"/>
-    </row>
-    <row r="254" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB253" s="3"/>
+      <c r="BC253" s="3"/>
+      <c r="BD253" s="3"/>
+      <c r="BE253" s="3"/>
+    </row>
+    <row r="254" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -15165,8 +16279,12 @@
       <c r="AY254" s="3"/>
       <c r="AZ254" s="3"/>
       <c r="BA254" s="3"/>
-    </row>
-    <row r="255" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB254" s="3"/>
+      <c r="BC254" s="3"/>
+      <c r="BD254" s="3"/>
+      <c r="BE254" s="3"/>
+    </row>
+    <row r="255" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -15218,8 +16336,12 @@
       <c r="AY255" s="3"/>
       <c r="AZ255" s="3"/>
       <c r="BA255" s="3"/>
-    </row>
-    <row r="256" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB255" s="3"/>
+      <c r="BC255" s="3"/>
+      <c r="BD255" s="3"/>
+      <c r="BE255" s="3"/>
+    </row>
+    <row r="256" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -15271,8 +16393,12 @@
       <c r="AY256" s="3"/>
       <c r="AZ256" s="3"/>
       <c r="BA256" s="3"/>
-    </row>
-    <row r="257" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB256" s="3"/>
+      <c r="BC256" s="3"/>
+      <c r="BD256" s="3"/>
+      <c r="BE256" s="3"/>
+    </row>
+    <row r="257" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -15324,8 +16450,12 @@
       <c r="AY257" s="3"/>
       <c r="AZ257" s="3"/>
       <c r="BA257" s="3"/>
-    </row>
-    <row r="258" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB257" s="3"/>
+      <c r="BC257" s="3"/>
+      <c r="BD257" s="3"/>
+      <c r="BE257" s="3"/>
+    </row>
+    <row r="258" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -15377,8 +16507,12 @@
       <c r="AY258" s="3"/>
       <c r="AZ258" s="3"/>
       <c r="BA258" s="3"/>
-    </row>
-    <row r="259" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB258" s="3"/>
+      <c r="BC258" s="3"/>
+      <c r="BD258" s="3"/>
+      <c r="BE258" s="3"/>
+    </row>
+    <row r="259" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -15430,8 +16564,12 @@
       <c r="AY259" s="3"/>
       <c r="AZ259" s="3"/>
       <c r="BA259" s="3"/>
-    </row>
-    <row r="260" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB259" s="3"/>
+      <c r="BC259" s="3"/>
+      <c r="BD259" s="3"/>
+      <c r="BE259" s="3"/>
+    </row>
+    <row r="260" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -15483,8 +16621,12 @@
       <c r="AY260" s="3"/>
       <c r="AZ260" s="3"/>
       <c r="BA260" s="3"/>
-    </row>
-    <row r="261" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB260" s="3"/>
+      <c r="BC260" s="3"/>
+      <c r="BD260" s="3"/>
+      <c r="BE260" s="3"/>
+    </row>
+    <row r="261" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -15536,8 +16678,12 @@
       <c r="AY261" s="3"/>
       <c r="AZ261" s="3"/>
       <c r="BA261" s="3"/>
-    </row>
-    <row r="262" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB261" s="3"/>
+      <c r="BC261" s="3"/>
+      <c r="BD261" s="3"/>
+      <c r="BE261" s="3"/>
+    </row>
+    <row r="262" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -15589,8 +16735,12 @@
       <c r="AY262" s="3"/>
       <c r="AZ262" s="3"/>
       <c r="BA262" s="3"/>
-    </row>
-    <row r="263" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB262" s="3"/>
+      <c r="BC262" s="3"/>
+      <c r="BD262" s="3"/>
+      <c r="BE262" s="3"/>
+    </row>
+    <row r="263" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -15642,8 +16792,12 @@
       <c r="AY263" s="3"/>
       <c r="AZ263" s="3"/>
       <c r="BA263" s="3"/>
-    </row>
-    <row r="264" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB263" s="3"/>
+      <c r="BC263" s="3"/>
+      <c r="BD263" s="3"/>
+      <c r="BE263" s="3"/>
+    </row>
+    <row r="264" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -15695,8 +16849,12 @@
       <c r="AY264" s="3"/>
       <c r="AZ264" s="3"/>
       <c r="BA264" s="3"/>
-    </row>
-    <row r="265" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB264" s="3"/>
+      <c r="BC264" s="3"/>
+      <c r="BD264" s="3"/>
+      <c r="BE264" s="3"/>
+    </row>
+    <row r="265" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -15748,8 +16906,12 @@
       <c r="AY265" s="3"/>
       <c r="AZ265" s="3"/>
       <c r="BA265" s="3"/>
-    </row>
-    <row r="266" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB265" s="3"/>
+      <c r="BC265" s="3"/>
+      <c r="BD265" s="3"/>
+      <c r="BE265" s="3"/>
+    </row>
+    <row r="266" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -15801,8 +16963,12 @@
       <c r="AY266" s="3"/>
       <c r="AZ266" s="3"/>
       <c r="BA266" s="3"/>
-    </row>
-    <row r="267" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB266" s="3"/>
+      <c r="BC266" s="3"/>
+      <c r="BD266" s="3"/>
+      <c r="BE266" s="3"/>
+    </row>
+    <row r="267" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -15854,8 +17020,12 @@
       <c r="AY267" s="3"/>
       <c r="AZ267" s="3"/>
       <c r="BA267" s="3"/>
-    </row>
-    <row r="268" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB267" s="3"/>
+      <c r="BC267" s="3"/>
+      <c r="BD267" s="3"/>
+      <c r="BE267" s="3"/>
+    </row>
+    <row r="268" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -15907,8 +17077,12 @@
       <c r="AY268" s="3"/>
       <c r="AZ268" s="3"/>
       <c r="BA268" s="3"/>
-    </row>
-    <row r="269" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB268" s="3"/>
+      <c r="BC268" s="3"/>
+      <c r="BD268" s="3"/>
+      <c r="BE268" s="3"/>
+    </row>
+    <row r="269" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -15960,8 +17134,12 @@
       <c r="AY269" s="3"/>
       <c r="AZ269" s="3"/>
       <c r="BA269" s="3"/>
-    </row>
-    <row r="270" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB269" s="3"/>
+      <c r="BC269" s="3"/>
+      <c r="BD269" s="3"/>
+      <c r="BE269" s="3"/>
+    </row>
+    <row r="270" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -16013,8 +17191,12 @@
       <c r="AY270" s="3"/>
       <c r="AZ270" s="3"/>
       <c r="BA270" s="3"/>
-    </row>
-    <row r="271" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB270" s="3"/>
+      <c r="BC270" s="3"/>
+      <c r="BD270" s="3"/>
+      <c r="BE270" s="3"/>
+    </row>
+    <row r="271" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -16066,8 +17248,12 @@
       <c r="AY271" s="3"/>
       <c r="AZ271" s="3"/>
       <c r="BA271" s="3"/>
-    </row>
-    <row r="272" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB271" s="3"/>
+      <c r="BC271" s="3"/>
+      <c r="BD271" s="3"/>
+      <c r="BE271" s="3"/>
+    </row>
+    <row r="272" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -16119,8 +17305,12 @@
       <c r="AY272" s="3"/>
       <c r="AZ272" s="3"/>
       <c r="BA272" s="3"/>
-    </row>
-    <row r="273" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB272" s="3"/>
+      <c r="BC272" s="3"/>
+      <c r="BD272" s="3"/>
+      <c r="BE272" s="3"/>
+    </row>
+    <row r="273" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -16172,8 +17362,12 @@
       <c r="AY273" s="3"/>
       <c r="AZ273" s="3"/>
       <c r="BA273" s="3"/>
-    </row>
-    <row r="274" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB273" s="3"/>
+      <c r="BC273" s="3"/>
+      <c r="BD273" s="3"/>
+      <c r="BE273" s="3"/>
+    </row>
+    <row r="274" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -16225,8 +17419,12 @@
       <c r="AY274" s="3"/>
       <c r="AZ274" s="3"/>
       <c r="BA274" s="3"/>
-    </row>
-    <row r="275" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB274" s="3"/>
+      <c r="BC274" s="3"/>
+      <c r="BD274" s="3"/>
+      <c r="BE274" s="3"/>
+    </row>
+    <row r="275" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -16278,8 +17476,12 @@
       <c r="AY275" s="3"/>
       <c r="AZ275" s="3"/>
       <c r="BA275" s="3"/>
-    </row>
-    <row r="276" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB275" s="3"/>
+      <c r="BC275" s="3"/>
+      <c r="BD275" s="3"/>
+      <c r="BE275" s="3"/>
+    </row>
+    <row r="276" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -16331,8 +17533,12 @@
       <c r="AY276" s="3"/>
       <c r="AZ276" s="3"/>
       <c r="BA276" s="3"/>
-    </row>
-    <row r="277" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB276" s="3"/>
+      <c r="BC276" s="3"/>
+      <c r="BD276" s="3"/>
+      <c r="BE276" s="3"/>
+    </row>
+    <row r="277" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -16384,8 +17590,12 @@
       <c r="AY277" s="3"/>
       <c r="AZ277" s="3"/>
       <c r="BA277" s="3"/>
-    </row>
-    <row r="278" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB277" s="3"/>
+      <c r="BC277" s="3"/>
+      <c r="BD277" s="3"/>
+      <c r="BE277" s="3"/>
+    </row>
+    <row r="278" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -16437,8 +17647,12 @@
       <c r="AY278" s="3"/>
       <c r="AZ278" s="3"/>
       <c r="BA278" s="3"/>
-    </row>
-    <row r="279" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB278" s="3"/>
+      <c r="BC278" s="3"/>
+      <c r="BD278" s="3"/>
+      <c r="BE278" s="3"/>
+    </row>
+    <row r="279" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -16490,8 +17704,12 @@
       <c r="AY279" s="3"/>
       <c r="AZ279" s="3"/>
       <c r="BA279" s="3"/>
-    </row>
-    <row r="280" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB279" s="3"/>
+      <c r="BC279" s="3"/>
+      <c r="BD279" s="3"/>
+      <c r="BE279" s="3"/>
+    </row>
+    <row r="280" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -16543,8 +17761,12 @@
       <c r="AY280" s="3"/>
       <c r="AZ280" s="3"/>
       <c r="BA280" s="3"/>
-    </row>
-    <row r="281" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB280" s="3"/>
+      <c r="BC280" s="3"/>
+      <c r="BD280" s="3"/>
+      <c r="BE280" s="3"/>
+    </row>
+    <row r="281" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -16596,8 +17818,12 @@
       <c r="AY281" s="3"/>
       <c r="AZ281" s="3"/>
       <c r="BA281" s="3"/>
-    </row>
-    <row r="282" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB281" s="3"/>
+      <c r="BC281" s="3"/>
+      <c r="BD281" s="3"/>
+      <c r="BE281" s="3"/>
+    </row>
+    <row r="282" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -16649,8 +17875,12 @@
       <c r="AY282" s="3"/>
       <c r="AZ282" s="3"/>
       <c r="BA282" s="3"/>
-    </row>
-    <row r="283" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB282" s="3"/>
+      <c r="BC282" s="3"/>
+      <c r="BD282" s="3"/>
+      <c r="BE282" s="3"/>
+    </row>
+    <row r="283" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -16702,8 +17932,12 @@
       <c r="AY283" s="3"/>
       <c r="AZ283" s="3"/>
       <c r="BA283" s="3"/>
-    </row>
-    <row r="284" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB283" s="3"/>
+      <c r="BC283" s="3"/>
+      <c r="BD283" s="3"/>
+      <c r="BE283" s="3"/>
+    </row>
+    <row r="284" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -16755,8 +17989,12 @@
       <c r="AY284" s="3"/>
       <c r="AZ284" s="3"/>
       <c r="BA284" s="3"/>
-    </row>
-    <row r="285" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB284" s="3"/>
+      <c r="BC284" s="3"/>
+      <c r="BD284" s="3"/>
+      <c r="BE284" s="3"/>
+    </row>
+    <row r="285" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -16808,8 +18046,12 @@
       <c r="AY285" s="3"/>
       <c r="AZ285" s="3"/>
       <c r="BA285" s="3"/>
-    </row>
-    <row r="286" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB285" s="3"/>
+      <c r="BC285" s="3"/>
+      <c r="BD285" s="3"/>
+      <c r="BE285" s="3"/>
+    </row>
+    <row r="286" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -16861,8 +18103,12 @@
       <c r="AY286" s="3"/>
       <c r="AZ286" s="3"/>
       <c r="BA286" s="3"/>
-    </row>
-    <row r="287" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB286" s="3"/>
+      <c r="BC286" s="3"/>
+      <c r="BD286" s="3"/>
+      <c r="BE286" s="3"/>
+    </row>
+    <row r="287" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -16914,8 +18160,12 @@
       <c r="AY287" s="3"/>
       <c r="AZ287" s="3"/>
       <c r="BA287" s="3"/>
-    </row>
-    <row r="288" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB287" s="3"/>
+      <c r="BC287" s="3"/>
+      <c r="BD287" s="3"/>
+      <c r="BE287" s="3"/>
+    </row>
+    <row r="288" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -16967,8 +18217,12 @@
       <c r="AY288" s="3"/>
       <c r="AZ288" s="3"/>
       <c r="BA288" s="3"/>
-    </row>
-    <row r="289" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB288" s="3"/>
+      <c r="BC288" s="3"/>
+      <c r="BD288" s="3"/>
+      <c r="BE288" s="3"/>
+    </row>
+    <row r="289" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -17020,8 +18274,12 @@
       <c r="AY289" s="3"/>
       <c r="AZ289" s="3"/>
       <c r="BA289" s="3"/>
-    </row>
-    <row r="290" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB289" s="3"/>
+      <c r="BC289" s="3"/>
+      <c r="BD289" s="3"/>
+      <c r="BE289" s="3"/>
+    </row>
+    <row r="290" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -17073,8 +18331,12 @@
       <c r="AY290" s="3"/>
       <c r="AZ290" s="3"/>
       <c r="BA290" s="3"/>
-    </row>
-    <row r="291" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB290" s="3"/>
+      <c r="BC290" s="3"/>
+      <c r="BD290" s="3"/>
+      <c r="BE290" s="3"/>
+    </row>
+    <row r="291" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -17126,8 +18388,12 @@
       <c r="AY291" s="3"/>
       <c r="AZ291" s="3"/>
       <c r="BA291" s="3"/>
-    </row>
-    <row r="292" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB291" s="3"/>
+      <c r="BC291" s="3"/>
+      <c r="BD291" s="3"/>
+      <c r="BE291" s="3"/>
+    </row>
+    <row r="292" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -17179,8 +18445,12 @@
       <c r="AY292" s="3"/>
       <c r="AZ292" s="3"/>
       <c r="BA292" s="3"/>
-    </row>
-    <row r="293" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB292" s="3"/>
+      <c r="BC292" s="3"/>
+      <c r="BD292" s="3"/>
+      <c r="BE292" s="3"/>
+    </row>
+    <row r="293" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -17232,8 +18502,12 @@
       <c r="AY293" s="3"/>
       <c r="AZ293" s="3"/>
       <c r="BA293" s="3"/>
-    </row>
-    <row r="294" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB293" s="3"/>
+      <c r="BC293" s="3"/>
+      <c r="BD293" s="3"/>
+      <c r="BE293" s="3"/>
+    </row>
+    <row r="294" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -17285,8 +18559,12 @@
       <c r="AY294" s="3"/>
       <c r="AZ294" s="3"/>
       <c r="BA294" s="3"/>
-    </row>
-    <row r="295" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB294" s="3"/>
+      <c r="BC294" s="3"/>
+      <c r="BD294" s="3"/>
+      <c r="BE294" s="3"/>
+    </row>
+    <row r="295" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -17338,8 +18616,12 @@
       <c r="AY295" s="3"/>
       <c r="AZ295" s="3"/>
       <c r="BA295" s="3"/>
-    </row>
-    <row r="296" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB295" s="3"/>
+      <c r="BC295" s="3"/>
+      <c r="BD295" s="3"/>
+      <c r="BE295" s="3"/>
+    </row>
+    <row r="296" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -17391,8 +18673,12 @@
       <c r="AY296" s="3"/>
       <c r="AZ296" s="3"/>
       <c r="BA296" s="3"/>
-    </row>
-    <row r="297" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB296" s="3"/>
+      <c r="BC296" s="3"/>
+      <c r="BD296" s="3"/>
+      <c r="BE296" s="3"/>
+    </row>
+    <row r="297" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -17444,8 +18730,12 @@
       <c r="AY297" s="3"/>
       <c r="AZ297" s="3"/>
       <c r="BA297" s="3"/>
-    </row>
-    <row r="298" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB297" s="3"/>
+      <c r="BC297" s="3"/>
+      <c r="BD297" s="3"/>
+      <c r="BE297" s="3"/>
+    </row>
+    <row r="298" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -17497,8 +18787,12 @@
       <c r="AY298" s="3"/>
       <c r="AZ298" s="3"/>
       <c r="BA298" s="3"/>
-    </row>
-    <row r="299" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB298" s="3"/>
+      <c r="BC298" s="3"/>
+      <c r="BD298" s="3"/>
+      <c r="BE298" s="3"/>
+    </row>
+    <row r="299" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -17550,8 +18844,12 @@
       <c r="AY299" s="3"/>
       <c r="AZ299" s="3"/>
       <c r="BA299" s="3"/>
-    </row>
-    <row r="300" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB299" s="3"/>
+      <c r="BC299" s="3"/>
+      <c r="BD299" s="3"/>
+      <c r="BE299" s="3"/>
+    </row>
+    <row r="300" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -17603,8 +18901,12 @@
       <c r="AY300" s="3"/>
       <c r="AZ300" s="3"/>
       <c r="BA300" s="3"/>
-    </row>
-    <row r="301" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB300" s="3"/>
+      <c r="BC300" s="3"/>
+      <c r="BD300" s="3"/>
+      <c r="BE300" s="3"/>
+    </row>
+    <row r="301" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -17656,8 +18958,12 @@
       <c r="AY301" s="3"/>
       <c r="AZ301" s="3"/>
       <c r="BA301" s="3"/>
-    </row>
-    <row r="302" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB301" s="3"/>
+      <c r="BC301" s="3"/>
+      <c r="BD301" s="3"/>
+      <c r="BE301" s="3"/>
+    </row>
+    <row r="302" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -17709,8 +19015,12 @@
       <c r="AY302" s="3"/>
       <c r="AZ302" s="3"/>
       <c r="BA302" s="3"/>
-    </row>
-    <row r="303" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB302" s="3"/>
+      <c r="BC302" s="3"/>
+      <c r="BD302" s="3"/>
+      <c r="BE302" s="3"/>
+    </row>
+    <row r="303" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -17762,8 +19072,12 @@
       <c r="AY303" s="3"/>
       <c r="AZ303" s="3"/>
       <c r="BA303" s="3"/>
-    </row>
-    <row r="304" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB303" s="3"/>
+      <c r="BC303" s="3"/>
+      <c r="BD303" s="3"/>
+      <c r="BE303" s="3"/>
+    </row>
+    <row r="304" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -17815,8 +19129,12 @@
       <c r="AY304" s="3"/>
       <c r="AZ304" s="3"/>
       <c r="BA304" s="3"/>
-    </row>
-    <row r="305" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB304" s="3"/>
+      <c r="BC304" s="3"/>
+      <c r="BD304" s="3"/>
+      <c r="BE304" s="3"/>
+    </row>
+    <row r="305" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -17868,8 +19186,12 @@
       <c r="AY305" s="3"/>
       <c r="AZ305" s="3"/>
       <c r="BA305" s="3"/>
-    </row>
-    <row r="306" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB305" s="3"/>
+      <c r="BC305" s="3"/>
+      <c r="BD305" s="3"/>
+      <c r="BE305" s="3"/>
+    </row>
+    <row r="306" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -17921,8 +19243,12 @@
       <c r="AY306" s="3"/>
       <c r="AZ306" s="3"/>
       <c r="BA306" s="3"/>
-    </row>
-    <row r="307" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB306" s="3"/>
+      <c r="BC306" s="3"/>
+      <c r="BD306" s="3"/>
+      <c r="BE306" s="3"/>
+    </row>
+    <row r="307" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -17974,8 +19300,12 @@
       <c r="AY307" s="3"/>
       <c r="AZ307" s="3"/>
       <c r="BA307" s="3"/>
-    </row>
-    <row r="308" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB307" s="3"/>
+      <c r="BC307" s="3"/>
+      <c r="BD307" s="3"/>
+      <c r="BE307" s="3"/>
+    </row>
+    <row r="308" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -18027,8 +19357,12 @@
       <c r="AY308" s="3"/>
       <c r="AZ308" s="3"/>
       <c r="BA308" s="3"/>
-    </row>
-    <row r="309" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB308" s="3"/>
+      <c r="BC308" s="3"/>
+      <c r="BD308" s="3"/>
+      <c r="BE308" s="3"/>
+    </row>
+    <row r="309" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -18080,8 +19414,12 @@
       <c r="AY309" s="3"/>
       <c r="AZ309" s="3"/>
       <c r="BA309" s="3"/>
-    </row>
-    <row r="310" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB309" s="3"/>
+      <c r="BC309" s="3"/>
+      <c r="BD309" s="3"/>
+      <c r="BE309" s="3"/>
+    </row>
+    <row r="310" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -18133,8 +19471,12 @@
       <c r="AY310" s="3"/>
       <c r="AZ310" s="3"/>
       <c r="BA310" s="3"/>
-    </row>
-    <row r="311" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB310" s="3"/>
+      <c r="BC310" s="3"/>
+      <c r="BD310" s="3"/>
+      <c r="BE310" s="3"/>
+    </row>
+    <row r="311" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -18186,8 +19528,12 @@
       <c r="AY311" s="3"/>
       <c r="AZ311" s="3"/>
       <c r="BA311" s="3"/>
-    </row>
-    <row r="312" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB311" s="3"/>
+      <c r="BC311" s="3"/>
+      <c r="BD311" s="3"/>
+      <c r="BE311" s="3"/>
+    </row>
+    <row r="312" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -18239,8 +19585,12 @@
       <c r="AY312" s="3"/>
       <c r="AZ312" s="3"/>
       <c r="BA312" s="3"/>
-    </row>
-    <row r="313" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB312" s="3"/>
+      <c r="BC312" s="3"/>
+      <c r="BD312" s="3"/>
+      <c r="BE312" s="3"/>
+    </row>
+    <row r="313" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -18292,8 +19642,12 @@
       <c r="AY313" s="3"/>
       <c r="AZ313" s="3"/>
       <c r="BA313" s="3"/>
-    </row>
-    <row r="314" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB313" s="3"/>
+      <c r="BC313" s="3"/>
+      <c r="BD313" s="3"/>
+      <c r="BE313" s="3"/>
+    </row>
+    <row r="314" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -18345,8 +19699,12 @@
       <c r="AY314" s="3"/>
       <c r="AZ314" s="3"/>
       <c r="BA314" s="3"/>
-    </row>
-    <row r="315" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB314" s="3"/>
+      <c r="BC314" s="3"/>
+      <c r="BD314" s="3"/>
+      <c r="BE314" s="3"/>
+    </row>
+    <row r="315" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -18398,8 +19756,12 @@
       <c r="AY315" s="3"/>
       <c r="AZ315" s="3"/>
       <c r="BA315" s="3"/>
-    </row>
-    <row r="316" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB315" s="3"/>
+      <c r="BC315" s="3"/>
+      <c r="BD315" s="3"/>
+      <c r="BE315" s="3"/>
+    </row>
+    <row r="316" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -18451,8 +19813,12 @@
       <c r="AY316" s="3"/>
       <c r="AZ316" s="3"/>
       <c r="BA316" s="3"/>
-    </row>
-    <row r="317" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB316" s="3"/>
+      <c r="BC316" s="3"/>
+      <c r="BD316" s="3"/>
+      <c r="BE316" s="3"/>
+    </row>
+    <row r="317" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -18504,8 +19870,12 @@
       <c r="AY317" s="3"/>
       <c r="AZ317" s="3"/>
       <c r="BA317" s="3"/>
-    </row>
-    <row r="318" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB317" s="3"/>
+      <c r="BC317" s="3"/>
+      <c r="BD317" s="3"/>
+      <c r="BE317" s="3"/>
+    </row>
+    <row r="318" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -18557,8 +19927,12 @@
       <c r="AY318" s="3"/>
       <c r="AZ318" s="3"/>
       <c r="BA318" s="3"/>
-    </row>
-    <row r="319" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB318" s="3"/>
+      <c r="BC318" s="3"/>
+      <c r="BD318" s="3"/>
+      <c r="BE318" s="3"/>
+    </row>
+    <row r="319" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -18610,8 +19984,12 @@
       <c r="AY319" s="3"/>
       <c r="AZ319" s="3"/>
       <c r="BA319" s="3"/>
-    </row>
-    <row r="320" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB319" s="3"/>
+      <c r="BC319" s="3"/>
+      <c r="BD319" s="3"/>
+      <c r="BE319" s="3"/>
+    </row>
+    <row r="320" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -18663,8 +20041,12 @@
       <c r="AY320" s="3"/>
       <c r="AZ320" s="3"/>
       <c r="BA320" s="3"/>
-    </row>
-    <row r="321" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB320" s="3"/>
+      <c r="BC320" s="3"/>
+      <c r="BD320" s="3"/>
+      <c r="BE320" s="3"/>
+    </row>
+    <row r="321" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -18716,8 +20098,12 @@
       <c r="AY321" s="3"/>
       <c r="AZ321" s="3"/>
       <c r="BA321" s="3"/>
-    </row>
-    <row r="322" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB321" s="3"/>
+      <c r="BC321" s="3"/>
+      <c r="BD321" s="3"/>
+      <c r="BE321" s="3"/>
+    </row>
+    <row r="322" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -18769,8 +20155,12 @@
       <c r="AY322" s="3"/>
       <c r="AZ322" s="3"/>
       <c r="BA322" s="3"/>
-    </row>
-    <row r="323" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB322" s="3"/>
+      <c r="BC322" s="3"/>
+      <c r="BD322" s="3"/>
+      <c r="BE322" s="3"/>
+    </row>
+    <row r="323" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -18822,8 +20212,12 @@
       <c r="AY323" s="3"/>
       <c r="AZ323" s="3"/>
       <c r="BA323" s="3"/>
-    </row>
-    <row r="324" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB323" s="3"/>
+      <c r="BC323" s="3"/>
+      <c r="BD323" s="3"/>
+      <c r="BE323" s="3"/>
+    </row>
+    <row r="324" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -18875,8 +20269,12 @@
       <c r="AY324" s="3"/>
       <c r="AZ324" s="3"/>
       <c r="BA324" s="3"/>
-    </row>
-    <row r="325" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB324" s="3"/>
+      <c r="BC324" s="3"/>
+      <c r="BD324" s="3"/>
+      <c r="BE324" s="3"/>
+    </row>
+    <row r="325" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="3"/>
@@ -18928,8 +20326,12 @@
       <c r="AY325" s="3"/>
       <c r="AZ325" s="3"/>
       <c r="BA325" s="3"/>
-    </row>
-    <row r="326" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB325" s="3"/>
+      <c r="BC325" s="3"/>
+      <c r="BD325" s="3"/>
+      <c r="BE325" s="3"/>
+    </row>
+    <row r="326" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -18981,8 +20383,12 @@
       <c r="AY326" s="3"/>
       <c r="AZ326" s="3"/>
       <c r="BA326" s="3"/>
-    </row>
-    <row r="327" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB326" s="3"/>
+      <c r="BC326" s="3"/>
+      <c r="BD326" s="3"/>
+      <c r="BE326" s="3"/>
+    </row>
+    <row r="327" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="3"/>
@@ -19034,8 +20440,12 @@
       <c r="AY327" s="3"/>
       <c r="AZ327" s="3"/>
       <c r="BA327" s="3"/>
-    </row>
-    <row r="328" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB327" s="3"/>
+      <c r="BC327" s="3"/>
+      <c r="BD327" s="3"/>
+      <c r="BE327" s="3"/>
+    </row>
+    <row r="328" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -19087,8 +20497,12 @@
       <c r="AY328" s="3"/>
       <c r="AZ328" s="3"/>
       <c r="BA328" s="3"/>
-    </row>
-    <row r="329" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB328" s="3"/>
+      <c r="BC328" s="3"/>
+      <c r="BD328" s="3"/>
+      <c r="BE328" s="3"/>
+    </row>
+    <row r="329" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="3"/>
@@ -19140,8 +20554,12 @@
       <c r="AY329" s="3"/>
       <c r="AZ329" s="3"/>
       <c r="BA329" s="3"/>
-    </row>
-    <row r="330" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB329" s="3"/>
+      <c r="BC329" s="3"/>
+      <c r="BD329" s="3"/>
+      <c r="BE329" s="3"/>
+    </row>
+    <row r="330" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -19193,8 +20611,12 @@
       <c r="AY330" s="3"/>
       <c r="AZ330" s="3"/>
       <c r="BA330" s="3"/>
-    </row>
-    <row r="331" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB330" s="3"/>
+      <c r="BC330" s="3"/>
+      <c r="BD330" s="3"/>
+      <c r="BE330" s="3"/>
+    </row>
+    <row r="331" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="3"/>
@@ -19246,8 +20668,12 @@
       <c r="AY331" s="3"/>
       <c r="AZ331" s="3"/>
       <c r="BA331" s="3"/>
-    </row>
-    <row r="332" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB331" s="3"/>
+      <c r="BC331" s="3"/>
+      <c r="BD331" s="3"/>
+      <c r="BE331" s="3"/>
+    </row>
+    <row r="332" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -19299,8 +20725,12 @@
       <c r="AY332" s="3"/>
       <c r="AZ332" s="3"/>
       <c r="BA332" s="3"/>
-    </row>
-    <row r="333" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB332" s="3"/>
+      <c r="BC332" s="3"/>
+      <c r="BD332" s="3"/>
+      <c r="BE332" s="3"/>
+    </row>
+    <row r="333" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
       <c r="E333" s="3"/>
@@ -19352,8 +20782,12 @@
       <c r="AY333" s="3"/>
       <c r="AZ333" s="3"/>
       <c r="BA333" s="3"/>
-    </row>
-    <row r="334" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB333" s="3"/>
+      <c r="BC333" s="3"/>
+      <c r="BD333" s="3"/>
+      <c r="BE333" s="3"/>
+    </row>
+    <row r="334" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
@@ -19405,8 +20839,12 @@
       <c r="AY334" s="3"/>
       <c r="AZ334" s="3"/>
       <c r="BA334" s="3"/>
-    </row>
-    <row r="335" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB334" s="3"/>
+      <c r="BC334" s="3"/>
+      <c r="BD334" s="3"/>
+      <c r="BE334" s="3"/>
+    </row>
+    <row r="335" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
@@ -19458,8 +20896,12 @@
       <c r="AY335" s="3"/>
       <c r="AZ335" s="3"/>
       <c r="BA335" s="3"/>
-    </row>
-    <row r="336" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB335" s="3"/>
+      <c r="BC335" s="3"/>
+      <c r="BD335" s="3"/>
+      <c r="BE335" s="3"/>
+    </row>
+    <row r="336" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
@@ -19511,8 +20953,12 @@
       <c r="AY336" s="3"/>
       <c r="AZ336" s="3"/>
       <c r="BA336" s="3"/>
-    </row>
-    <row r="337" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB336" s="3"/>
+      <c r="BC336" s="3"/>
+      <c r="BD336" s="3"/>
+      <c r="BE336" s="3"/>
+    </row>
+    <row r="337" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
       <c r="E337" s="3"/>
@@ -19564,8 +21010,12 @@
       <c r="AY337" s="3"/>
       <c r="AZ337" s="3"/>
       <c r="BA337" s="3"/>
-    </row>
-    <row r="338" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB337" s="3"/>
+      <c r="BC337" s="3"/>
+      <c r="BD337" s="3"/>
+      <c r="BE337" s="3"/>
+    </row>
+    <row r="338" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
       <c r="E338" s="3"/>
@@ -19617,8 +21067,12 @@
       <c r="AY338" s="3"/>
       <c r="AZ338" s="3"/>
       <c r="BA338" s="3"/>
-    </row>
-    <row r="339" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB338" s="3"/>
+      <c r="BC338" s="3"/>
+      <c r="BD338" s="3"/>
+      <c r="BE338" s="3"/>
+    </row>
+    <row r="339" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
       <c r="E339" s="3"/>
@@ -19670,8 +21124,12 @@
       <c r="AY339" s="3"/>
       <c r="AZ339" s="3"/>
       <c r="BA339" s="3"/>
-    </row>
-    <row r="340" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB339" s="3"/>
+      <c r="BC339" s="3"/>
+      <c r="BD339" s="3"/>
+      <c r="BE339" s="3"/>
+    </row>
+    <row r="340" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
       <c r="E340" s="3"/>
@@ -19723,8 +21181,12 @@
       <c r="AY340" s="3"/>
       <c r="AZ340" s="3"/>
       <c r="BA340" s="3"/>
-    </row>
-    <row r="341" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB340" s="3"/>
+      <c r="BC340" s="3"/>
+      <c r="BD340" s="3"/>
+      <c r="BE340" s="3"/>
+    </row>
+    <row r="341" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
       <c r="E341" s="3"/>
@@ -19776,8 +21238,12 @@
       <c r="AY341" s="3"/>
       <c r="AZ341" s="3"/>
       <c r="BA341" s="3"/>
-    </row>
-    <row r="342" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB341" s="3"/>
+      <c r="BC341" s="3"/>
+      <c r="BD341" s="3"/>
+      <c r="BE341" s="3"/>
+    </row>
+    <row r="342" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
       <c r="E342" s="3"/>
@@ -19829,8 +21295,12 @@
       <c r="AY342" s="3"/>
       <c r="AZ342" s="3"/>
       <c r="BA342" s="3"/>
-    </row>
-    <row r="343" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB342" s="3"/>
+      <c r="BC342" s="3"/>
+      <c r="BD342" s="3"/>
+      <c r="BE342" s="3"/>
+    </row>
+    <row r="343" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="3"/>
@@ -19882,8 +21352,12 @@
       <c r="AY343" s="3"/>
       <c r="AZ343" s="3"/>
       <c r="BA343" s="3"/>
-    </row>
-    <row r="344" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB343" s="3"/>
+      <c r="BC343" s="3"/>
+      <c r="BD343" s="3"/>
+      <c r="BE343" s="3"/>
+    </row>
+    <row r="344" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="3"/>
@@ -19935,8 +21409,12 @@
       <c r="AY344" s="3"/>
       <c r="AZ344" s="3"/>
       <c r="BA344" s="3"/>
-    </row>
-    <row r="345" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB344" s="3"/>
+      <c r="BC344" s="3"/>
+      <c r="BD344" s="3"/>
+      <c r="BE344" s="3"/>
+    </row>
+    <row r="345" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="3"/>
@@ -19988,8 +21466,12 @@
       <c r="AY345" s="3"/>
       <c r="AZ345" s="3"/>
       <c r="BA345" s="3"/>
-    </row>
-    <row r="346" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB345" s="3"/>
+      <c r="BC345" s="3"/>
+      <c r="BD345" s="3"/>
+      <c r="BE345" s="3"/>
+    </row>
+    <row r="346" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="3"/>
@@ -20041,8 +21523,12 @@
       <c r="AY346" s="3"/>
       <c r="AZ346" s="3"/>
       <c r="BA346" s="3"/>
-    </row>
-    <row r="347" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB346" s="3"/>
+      <c r="BC346" s="3"/>
+      <c r="BD346" s="3"/>
+      <c r="BE346" s="3"/>
+    </row>
+    <row r="347" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="3"/>
@@ -20094,8 +21580,12 @@
       <c r="AY347" s="3"/>
       <c r="AZ347" s="3"/>
       <c r="BA347" s="3"/>
-    </row>
-    <row r="348" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB347" s="3"/>
+      <c r="BC347" s="3"/>
+      <c r="BD347" s="3"/>
+      <c r="BE347" s="3"/>
+    </row>
+    <row r="348" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="3"/>
@@ -20147,8 +21637,12 @@
       <c r="AY348" s="3"/>
       <c r="AZ348" s="3"/>
       <c r="BA348" s="3"/>
-    </row>
-    <row r="349" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB348" s="3"/>
+      <c r="BC348" s="3"/>
+      <c r="BD348" s="3"/>
+      <c r="BE348" s="3"/>
+    </row>
+    <row r="349" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
       <c r="E349" s="3"/>
@@ -20200,8 +21694,12 @@
       <c r="AY349" s="3"/>
       <c r="AZ349" s="3"/>
       <c r="BA349" s="3"/>
-    </row>
-    <row r="350" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB349" s="3"/>
+      <c r="BC349" s="3"/>
+      <c r="BD349" s="3"/>
+      <c r="BE349" s="3"/>
+    </row>
+    <row r="350" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
       <c r="E350" s="3"/>
@@ -20253,8 +21751,12 @@
       <c r="AY350" s="3"/>
       <c r="AZ350" s="3"/>
       <c r="BA350" s="3"/>
-    </row>
-    <row r="351" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB350" s="3"/>
+      <c r="BC350" s="3"/>
+      <c r="BD350" s="3"/>
+      <c r="BE350" s="3"/>
+    </row>
+    <row r="351" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C351" s="3"/>
       <c r="D351" s="3"/>
       <c r="E351" s="3"/>
@@ -20306,8 +21808,12 @@
       <c r="AY351" s="3"/>
       <c r="AZ351" s="3"/>
       <c r="BA351" s="3"/>
-    </row>
-    <row r="352" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB351" s="3"/>
+      <c r="BC351" s="3"/>
+      <c r="BD351" s="3"/>
+      <c r="BE351" s="3"/>
+    </row>
+    <row r="352" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C352" s="3"/>
       <c r="D352" s="3"/>
       <c r="E352" s="3"/>
@@ -20359,8 +21865,12 @@
       <c r="AY352" s="3"/>
       <c r="AZ352" s="3"/>
       <c r="BA352" s="3"/>
-    </row>
-    <row r="353" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB352" s="3"/>
+      <c r="BC352" s="3"/>
+      <c r="BD352" s="3"/>
+      <c r="BE352" s="3"/>
+    </row>
+    <row r="353" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C353" s="3"/>
       <c r="D353" s="3"/>
       <c r="E353" s="3"/>
@@ -20412,8 +21922,12 @@
       <c r="AY353" s="3"/>
       <c r="AZ353" s="3"/>
       <c r="BA353" s="3"/>
-    </row>
-    <row r="354" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB353" s="3"/>
+      <c r="BC353" s="3"/>
+      <c r="BD353" s="3"/>
+      <c r="BE353" s="3"/>
+    </row>
+    <row r="354" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C354" s="3"/>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -20465,8 +21979,12 @@
       <c r="AY354" s="3"/>
       <c r="AZ354" s="3"/>
       <c r="BA354" s="3"/>
-    </row>
-    <row r="355" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB354" s="3"/>
+      <c r="BC354" s="3"/>
+      <c r="BD354" s="3"/>
+      <c r="BE354" s="3"/>
+    </row>
+    <row r="355" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C355" s="3"/>
       <c r="D355" s="3"/>
       <c r="E355" s="3"/>
@@ -20518,8 +22036,12 @@
       <c r="AY355" s="3"/>
       <c r="AZ355" s="3"/>
       <c r="BA355" s="3"/>
-    </row>
-    <row r="356" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB355" s="3"/>
+      <c r="BC355" s="3"/>
+      <c r="BD355" s="3"/>
+      <c r="BE355" s="3"/>
+    </row>
+    <row r="356" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
       <c r="E356" s="3"/>
@@ -20571,8 +22093,12 @@
       <c r="AY356" s="3"/>
       <c r="AZ356" s="3"/>
       <c r="BA356" s="3"/>
-    </row>
-    <row r="357" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB356" s="3"/>
+      <c r="BC356" s="3"/>
+      <c r="BD356" s="3"/>
+      <c r="BE356" s="3"/>
+    </row>
+    <row r="357" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C357" s="3"/>
       <c r="D357" s="3"/>
       <c r="E357" s="3"/>
@@ -20624,8 +22150,12 @@
       <c r="AY357" s="3"/>
       <c r="AZ357" s="3"/>
       <c r="BA357" s="3"/>
-    </row>
-    <row r="358" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB357" s="3"/>
+      <c r="BC357" s="3"/>
+      <c r="BD357" s="3"/>
+      <c r="BE357" s="3"/>
+    </row>
+    <row r="358" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C358" s="3"/>
       <c r="D358" s="3"/>
       <c r="E358" s="3"/>
@@ -20677,8 +22207,12 @@
       <c r="AY358" s="3"/>
       <c r="AZ358" s="3"/>
       <c r="BA358" s="3"/>
-    </row>
-    <row r="359" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB358" s="3"/>
+      <c r="BC358" s="3"/>
+      <c r="BD358" s="3"/>
+      <c r="BE358" s="3"/>
+    </row>
+    <row r="359" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C359" s="3"/>
       <c r="D359" s="3"/>
       <c r="E359" s="3"/>
@@ -20730,8 +22264,12 @@
       <c r="AY359" s="3"/>
       <c r="AZ359" s="3"/>
       <c r="BA359" s="3"/>
-    </row>
-    <row r="360" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB359" s="3"/>
+      <c r="BC359" s="3"/>
+      <c r="BD359" s="3"/>
+      <c r="BE359" s="3"/>
+    </row>
+    <row r="360" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C360" s="3"/>
       <c r="D360" s="3"/>
       <c r="E360" s="3"/>
@@ -20783,8 +22321,12 @@
       <c r="AY360" s="3"/>
       <c r="AZ360" s="3"/>
       <c r="BA360" s="3"/>
-    </row>
-    <row r="361" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB360" s="3"/>
+      <c r="BC360" s="3"/>
+      <c r="BD360" s="3"/>
+      <c r="BE360" s="3"/>
+    </row>
+    <row r="361" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C361" s="3"/>
       <c r="D361" s="3"/>
       <c r="E361" s="3"/>
@@ -20836,8 +22378,12 @@
       <c r="AY361" s="3"/>
       <c r="AZ361" s="3"/>
       <c r="BA361" s="3"/>
-    </row>
-    <row r="362" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB361" s="3"/>
+      <c r="BC361" s="3"/>
+      <c r="BD361" s="3"/>
+      <c r="BE361" s="3"/>
+    </row>
+    <row r="362" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
       <c r="E362" s="3"/>
@@ -20889,8 +22435,12 @@
       <c r="AY362" s="3"/>
       <c r="AZ362" s="3"/>
       <c r="BA362" s="3"/>
-    </row>
-    <row r="363" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB362" s="3"/>
+      <c r="BC362" s="3"/>
+      <c r="BD362" s="3"/>
+      <c r="BE362" s="3"/>
+    </row>
+    <row r="363" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C363" s="3"/>
       <c r="D363" s="3"/>
       <c r="E363" s="3"/>
@@ -20942,8 +22492,12 @@
       <c r="AY363" s="3"/>
       <c r="AZ363" s="3"/>
       <c r="BA363" s="3"/>
-    </row>
-    <row r="364" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB363" s="3"/>
+      <c r="BC363" s="3"/>
+      <c r="BD363" s="3"/>
+      <c r="BE363" s="3"/>
+    </row>
+    <row r="364" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C364" s="3"/>
       <c r="D364" s="3"/>
       <c r="E364" s="3"/>
@@ -20995,8 +22549,12 @@
       <c r="AY364" s="3"/>
       <c r="AZ364" s="3"/>
       <c r="BA364" s="3"/>
-    </row>
-    <row r="365" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB364" s="3"/>
+      <c r="BC364" s="3"/>
+      <c r="BD364" s="3"/>
+      <c r="BE364" s="3"/>
+    </row>
+    <row r="365" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C365" s="3"/>
       <c r="D365" s="3"/>
       <c r="E365" s="3"/>
@@ -21048,8 +22606,12 @@
       <c r="AY365" s="3"/>
       <c r="AZ365" s="3"/>
       <c r="BA365" s="3"/>
-    </row>
-    <row r="366" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB365" s="3"/>
+      <c r="BC365" s="3"/>
+      <c r="BD365" s="3"/>
+      <c r="BE365" s="3"/>
+    </row>
+    <row r="366" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C366" s="3"/>
       <c r="D366" s="3"/>
       <c r="E366" s="3"/>
@@ -21101,8 +22663,12 @@
       <c r="AY366" s="3"/>
       <c r="AZ366" s="3"/>
       <c r="BA366" s="3"/>
-    </row>
-    <row r="367" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB366" s="3"/>
+      <c r="BC366" s="3"/>
+      <c r="BD366" s="3"/>
+      <c r="BE366" s="3"/>
+    </row>
+    <row r="367" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C367" s="3"/>
       <c r="D367" s="3"/>
       <c r="E367" s="3"/>
@@ -21154,8 +22720,12 @@
       <c r="AY367" s="3"/>
       <c r="AZ367" s="3"/>
       <c r="BA367" s="3"/>
-    </row>
-    <row r="368" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB367" s="3"/>
+      <c r="BC367" s="3"/>
+      <c r="BD367" s="3"/>
+      <c r="BE367" s="3"/>
+    </row>
+    <row r="368" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
       <c r="E368" s="3"/>
@@ -21207,8 +22777,12 @@
       <c r="AY368" s="3"/>
       <c r="AZ368" s="3"/>
       <c r="BA368" s="3"/>
-    </row>
-    <row r="369" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB368" s="3"/>
+      <c r="BC368" s="3"/>
+      <c r="BD368" s="3"/>
+      <c r="BE368" s="3"/>
+    </row>
+    <row r="369" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C369" s="3"/>
       <c r="D369" s="3"/>
       <c r="E369" s="3"/>
@@ -21260,8 +22834,12 @@
       <c r="AY369" s="3"/>
       <c r="AZ369" s="3"/>
       <c r="BA369" s="3"/>
-    </row>
-    <row r="370" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB369" s="3"/>
+      <c r="BC369" s="3"/>
+      <c r="BD369" s="3"/>
+      <c r="BE369" s="3"/>
+    </row>
+    <row r="370" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C370" s="3"/>
       <c r="D370" s="3"/>
       <c r="E370" s="3"/>
@@ -21313,8 +22891,12 @@
       <c r="AY370" s="3"/>
       <c r="AZ370" s="3"/>
       <c r="BA370" s="3"/>
-    </row>
-    <row r="371" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB370" s="3"/>
+      <c r="BC370" s="3"/>
+      <c r="BD370" s="3"/>
+      <c r="BE370" s="3"/>
+    </row>
+    <row r="371" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C371" s="3"/>
       <c r="D371" s="3"/>
       <c r="E371" s="3"/>
@@ -21366,8 +22948,12 @@
       <c r="AY371" s="3"/>
       <c r="AZ371" s="3"/>
       <c r="BA371" s="3"/>
-    </row>
-    <row r="372" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB371" s="3"/>
+      <c r="BC371" s="3"/>
+      <c r="BD371" s="3"/>
+      <c r="BE371" s="3"/>
+    </row>
+    <row r="372" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
       <c r="E372" s="3"/>
@@ -21419,8 +23005,12 @@
       <c r="AY372" s="3"/>
       <c r="AZ372" s="3"/>
       <c r="BA372" s="3"/>
-    </row>
-    <row r="373" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB372" s="3"/>
+      <c r="BC372" s="3"/>
+      <c r="BD372" s="3"/>
+      <c r="BE372" s="3"/>
+    </row>
+    <row r="373" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C373" s="3"/>
       <c r="D373" s="3"/>
       <c r="E373" s="3"/>
@@ -21472,8 +23062,12 @@
       <c r="AY373" s="3"/>
       <c r="AZ373" s="3"/>
       <c r="BA373" s="3"/>
-    </row>
-    <row r="374" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB373" s="3"/>
+      <c r="BC373" s="3"/>
+      <c r="BD373" s="3"/>
+      <c r="BE373" s="3"/>
+    </row>
+    <row r="374" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C374" s="3"/>
       <c r="D374" s="3"/>
       <c r="E374" s="3"/>
@@ -21525,8 +23119,12 @@
       <c r="AY374" s="3"/>
       <c r="AZ374" s="3"/>
       <c r="BA374" s="3"/>
-    </row>
-    <row r="375" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB374" s="3"/>
+      <c r="BC374" s="3"/>
+      <c r="BD374" s="3"/>
+      <c r="BE374" s="3"/>
+    </row>
+    <row r="375" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C375" s="3"/>
       <c r="D375" s="3"/>
       <c r="E375" s="3"/>
@@ -21578,8 +23176,12 @@
       <c r="AY375" s="3"/>
       <c r="AZ375" s="3"/>
       <c r="BA375" s="3"/>
-    </row>
-    <row r="376" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB375" s="3"/>
+      <c r="BC375" s="3"/>
+      <c r="BD375" s="3"/>
+      <c r="BE375" s="3"/>
+    </row>
+    <row r="376" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
       <c r="E376" s="3"/>
@@ -21631,8 +23233,12 @@
       <c r="AY376" s="3"/>
       <c r="AZ376" s="3"/>
       <c r="BA376" s="3"/>
-    </row>
-    <row r="377" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB376" s="3"/>
+      <c r="BC376" s="3"/>
+      <c r="BD376" s="3"/>
+      <c r="BE376" s="3"/>
+    </row>
+    <row r="377" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
       <c r="E377" s="3"/>
@@ -21684,8 +23290,12 @@
       <c r="AY377" s="3"/>
       <c r="AZ377" s="3"/>
       <c r="BA377" s="3"/>
-    </row>
-    <row r="378" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB377" s="3"/>
+      <c r="BC377" s="3"/>
+      <c r="BD377" s="3"/>
+      <c r="BE377" s="3"/>
+    </row>
+    <row r="378" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
       <c r="E378" s="3"/>
@@ -21737,8 +23347,12 @@
       <c r="AY378" s="3"/>
       <c r="AZ378" s="3"/>
       <c r="BA378" s="3"/>
-    </row>
-    <row r="379" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB378" s="3"/>
+      <c r="BC378" s="3"/>
+      <c r="BD378" s="3"/>
+      <c r="BE378" s="3"/>
+    </row>
+    <row r="379" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
       <c r="E379" s="3"/>
@@ -21790,8 +23404,12 @@
       <c r="AY379" s="3"/>
       <c r="AZ379" s="3"/>
       <c r="BA379" s="3"/>
-    </row>
-    <row r="380" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB379" s="3"/>
+      <c r="BC379" s="3"/>
+      <c r="BD379" s="3"/>
+      <c r="BE379" s="3"/>
+    </row>
+    <row r="380" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
       <c r="E380" s="3"/>
@@ -21843,8 +23461,12 @@
       <c r="AY380" s="3"/>
       <c r="AZ380" s="3"/>
       <c r="BA380" s="3"/>
-    </row>
-    <row r="381" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB380" s="3"/>
+      <c r="BC380" s="3"/>
+      <c r="BD380" s="3"/>
+      <c r="BE380" s="3"/>
+    </row>
+    <row r="381" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
       <c r="E381" s="3"/>
@@ -21896,8 +23518,12 @@
       <c r="AY381" s="3"/>
       <c r="AZ381" s="3"/>
       <c r="BA381" s="3"/>
-    </row>
-    <row r="382" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB381" s="3"/>
+      <c r="BC381" s="3"/>
+      <c r="BD381" s="3"/>
+      <c r="BE381" s="3"/>
+    </row>
+    <row r="382" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
       <c r="E382" s="3"/>
@@ -21949,8 +23575,12 @@
       <c r="AY382" s="3"/>
       <c r="AZ382" s="3"/>
       <c r="BA382" s="3"/>
-    </row>
-    <row r="383" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB382" s="3"/>
+      <c r="BC382" s="3"/>
+      <c r="BD382" s="3"/>
+      <c r="BE382" s="3"/>
+    </row>
+    <row r="383" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
       <c r="E383" s="3"/>
@@ -22002,8 +23632,12 @@
       <c r="AY383" s="3"/>
       <c r="AZ383" s="3"/>
       <c r="BA383" s="3"/>
-    </row>
-    <row r="384" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB383" s="3"/>
+      <c r="BC383" s="3"/>
+      <c r="BD383" s="3"/>
+      <c r="BE383" s="3"/>
+    </row>
+    <row r="384" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
       <c r="E384" s="3"/>
@@ -22055,8 +23689,12 @@
       <c r="AY384" s="3"/>
       <c r="AZ384" s="3"/>
       <c r="BA384" s="3"/>
-    </row>
-    <row r="385" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB384" s="3"/>
+      <c r="BC384" s="3"/>
+      <c r="BD384" s="3"/>
+      <c r="BE384" s="3"/>
+    </row>
+    <row r="385" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
       <c r="E385" s="3"/>
@@ -22108,8 +23746,12 @@
       <c r="AY385" s="3"/>
       <c r="AZ385" s="3"/>
       <c r="BA385" s="3"/>
-    </row>
-    <row r="386" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB385" s="3"/>
+      <c r="BC385" s="3"/>
+      <c r="BD385" s="3"/>
+      <c r="BE385" s="3"/>
+    </row>
+    <row r="386" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
       <c r="E386" s="3"/>
@@ -22161,8 +23803,12 @@
       <c r="AY386" s="3"/>
       <c r="AZ386" s="3"/>
       <c r="BA386" s="3"/>
-    </row>
-    <row r="387" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB386" s="3"/>
+      <c r="BC386" s="3"/>
+      <c r="BD386" s="3"/>
+      <c r="BE386" s="3"/>
+    </row>
+    <row r="387" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
       <c r="E387" s="3"/>
@@ -22214,8 +23860,12 @@
       <c r="AY387" s="3"/>
       <c r="AZ387" s="3"/>
       <c r="BA387" s="3"/>
-    </row>
-    <row r="388" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB387" s="3"/>
+      <c r="BC387" s="3"/>
+      <c r="BD387" s="3"/>
+      <c r="BE387" s="3"/>
+    </row>
+    <row r="388" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
       <c r="E388" s="3"/>
@@ -22267,8 +23917,12 @@
       <c r="AY388" s="3"/>
       <c r="AZ388" s="3"/>
       <c r="BA388" s="3"/>
-    </row>
-    <row r="389" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB388" s="3"/>
+      <c r="BC388" s="3"/>
+      <c r="BD388" s="3"/>
+      <c r="BE388" s="3"/>
+    </row>
+    <row r="389" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
       <c r="E389" s="3"/>
@@ -22320,8 +23974,12 @@
       <c r="AY389" s="3"/>
       <c r="AZ389" s="3"/>
       <c r="BA389" s="3"/>
-    </row>
-    <row r="390" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB389" s="3"/>
+      <c r="BC389" s="3"/>
+      <c r="BD389" s="3"/>
+      <c r="BE389" s="3"/>
+    </row>
+    <row r="390" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
       <c r="E390" s="3"/>
@@ -22373,8 +24031,12 @@
       <c r="AY390" s="3"/>
       <c r="AZ390" s="3"/>
       <c r="BA390" s="3"/>
-    </row>
-    <row r="391" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB390" s="3"/>
+      <c r="BC390" s="3"/>
+      <c r="BD390" s="3"/>
+      <c r="BE390" s="3"/>
+    </row>
+    <row r="391" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
       <c r="E391" s="3"/>
@@ -22426,8 +24088,12 @@
       <c r="AY391" s="3"/>
       <c r="AZ391" s="3"/>
       <c r="BA391" s="3"/>
-    </row>
-    <row r="392" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB391" s="3"/>
+      <c r="BC391" s="3"/>
+      <c r="BD391" s="3"/>
+      <c r="BE391" s="3"/>
+    </row>
+    <row r="392" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
       <c r="E392" s="3"/>
@@ -22479,8 +24145,12 @@
       <c r="AY392" s="3"/>
       <c r="AZ392" s="3"/>
       <c r="BA392" s="3"/>
-    </row>
-    <row r="393" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB392" s="3"/>
+      <c r="BC392" s="3"/>
+      <c r="BD392" s="3"/>
+      <c r="BE392" s="3"/>
+    </row>
+    <row r="393" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
       <c r="E393" s="3"/>
@@ -22532,8 +24202,12 @@
       <c r="AY393" s="3"/>
       <c r="AZ393" s="3"/>
       <c r="BA393" s="3"/>
-    </row>
-    <row r="394" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB393" s="3"/>
+      <c r="BC393" s="3"/>
+      <c r="BD393" s="3"/>
+      <c r="BE393" s="3"/>
+    </row>
+    <row r="394" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
       <c r="E394" s="3"/>
@@ -22585,8 +24259,12 @@
       <c r="AY394" s="3"/>
       <c r="AZ394" s="3"/>
       <c r="BA394" s="3"/>
-    </row>
-    <row r="395" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB394" s="3"/>
+      <c r="BC394" s="3"/>
+      <c r="BD394" s="3"/>
+      <c r="BE394" s="3"/>
+    </row>
+    <row r="395" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
       <c r="E395" s="3"/>
@@ -22638,8 +24316,12 @@
       <c r="AY395" s="3"/>
       <c r="AZ395" s="3"/>
       <c r="BA395" s="3"/>
-    </row>
-    <row r="396" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB395" s="3"/>
+      <c r="BC395" s="3"/>
+      <c r="BD395" s="3"/>
+      <c r="BE395" s="3"/>
+    </row>
+    <row r="396" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
       <c r="E396" s="3"/>
@@ -22691,8 +24373,12 @@
       <c r="AY396" s="3"/>
       <c r="AZ396" s="3"/>
       <c r="BA396" s="3"/>
-    </row>
-    <row r="397" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB396" s="3"/>
+      <c r="BC396" s="3"/>
+      <c r="BD396" s="3"/>
+      <c r="BE396" s="3"/>
+    </row>
+    <row r="397" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
       <c r="E397" s="3"/>
@@ -22744,8 +24430,12 @@
       <c r="AY397" s="3"/>
       <c r="AZ397" s="3"/>
       <c r="BA397" s="3"/>
-    </row>
-    <row r="398" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB397" s="3"/>
+      <c r="BC397" s="3"/>
+      <c r="BD397" s="3"/>
+      <c r="BE397" s="3"/>
+    </row>
+    <row r="398" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
       <c r="E398" s="3"/>
@@ -22797,8 +24487,12 @@
       <c r="AY398" s="3"/>
       <c r="AZ398" s="3"/>
       <c r="BA398" s="3"/>
-    </row>
-    <row r="399" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB398" s="3"/>
+      <c r="BC398" s="3"/>
+      <c r="BD398" s="3"/>
+      <c r="BE398" s="3"/>
+    </row>
+    <row r="399" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
       <c r="E399" s="3"/>
@@ -22850,8 +24544,12 @@
       <c r="AY399" s="3"/>
       <c r="AZ399" s="3"/>
       <c r="BA399" s="3"/>
-    </row>
-    <row r="400" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB399" s="3"/>
+      <c r="BC399" s="3"/>
+      <c r="BD399" s="3"/>
+      <c r="BE399" s="3"/>
+    </row>
+    <row r="400" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
       <c r="E400" s="3"/>
@@ -22903,8 +24601,12 @@
       <c r="AY400" s="3"/>
       <c r="AZ400" s="3"/>
       <c r="BA400" s="3"/>
-    </row>
-    <row r="401" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB400" s="3"/>
+      <c r="BC400" s="3"/>
+      <c r="BD400" s="3"/>
+      <c r="BE400" s="3"/>
+    </row>
+    <row r="401" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
       <c r="E401" s="3"/>
@@ -22956,8 +24658,12 @@
       <c r="AY401" s="3"/>
       <c r="AZ401" s="3"/>
       <c r="BA401" s="3"/>
-    </row>
-    <row r="402" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB401" s="3"/>
+      <c r="BC401" s="3"/>
+      <c r="BD401" s="3"/>
+      <c r="BE401" s="3"/>
+    </row>
+    <row r="402" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C402" s="3"/>
       <c r="D402" s="3"/>
       <c r="E402" s="3"/>
@@ -23009,8 +24715,12 @@
       <c r="AY402" s="3"/>
       <c r="AZ402" s="3"/>
       <c r="BA402" s="3"/>
-    </row>
-    <row r="403" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB402" s="3"/>
+      <c r="BC402" s="3"/>
+      <c r="BD402" s="3"/>
+      <c r="BE402" s="3"/>
+    </row>
+    <row r="403" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C403" s="3"/>
       <c r="D403" s="3"/>
       <c r="E403" s="3"/>
@@ -23062,8 +24772,12 @@
       <c r="AY403" s="3"/>
       <c r="AZ403" s="3"/>
       <c r="BA403" s="3"/>
-    </row>
-    <row r="404" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB403" s="3"/>
+      <c r="BC403" s="3"/>
+      <c r="BD403" s="3"/>
+      <c r="BE403" s="3"/>
+    </row>
+    <row r="404" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C404" s="3"/>
       <c r="D404" s="3"/>
       <c r="E404" s="3"/>
@@ -23115,8 +24829,12 @@
       <c r="AY404" s="3"/>
       <c r="AZ404" s="3"/>
       <c r="BA404" s="3"/>
-    </row>
-    <row r="405" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB404" s="3"/>
+      <c r="BC404" s="3"/>
+      <c r="BD404" s="3"/>
+      <c r="BE404" s="3"/>
+    </row>
+    <row r="405" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C405" s="3"/>
       <c r="D405" s="3"/>
       <c r="E405" s="3"/>
@@ -23168,8 +24886,12 @@
       <c r="AY405" s="3"/>
       <c r="AZ405" s="3"/>
       <c r="BA405" s="3"/>
-    </row>
-    <row r="406" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB405" s="3"/>
+      <c r="BC405" s="3"/>
+      <c r="BD405" s="3"/>
+      <c r="BE405" s="3"/>
+    </row>
+    <row r="406" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C406" s="3"/>
       <c r="D406" s="3"/>
       <c r="E406" s="3"/>
@@ -23221,8 +24943,12 @@
       <c r="AY406" s="3"/>
       <c r="AZ406" s="3"/>
       <c r="BA406" s="3"/>
-    </row>
-    <row r="407" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB406" s="3"/>
+      <c r="BC406" s="3"/>
+      <c r="BD406" s="3"/>
+      <c r="BE406" s="3"/>
+    </row>
+    <row r="407" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C407" s="3"/>
       <c r="D407" s="3"/>
       <c r="E407" s="3"/>
@@ -23274,8 +25000,12 @@
       <c r="AY407" s="3"/>
       <c r="AZ407" s="3"/>
       <c r="BA407" s="3"/>
-    </row>
-    <row r="408" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB407" s="3"/>
+      <c r="BC407" s="3"/>
+      <c r="BD407" s="3"/>
+      <c r="BE407" s="3"/>
+    </row>
+    <row r="408" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C408" s="3"/>
       <c r="D408" s="3"/>
       <c r="E408" s="3"/>
@@ -23327,8 +25057,12 @@
       <c r="AY408" s="3"/>
       <c r="AZ408" s="3"/>
       <c r="BA408" s="3"/>
-    </row>
-    <row r="409" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB408" s="3"/>
+      <c r="BC408" s="3"/>
+      <c r="BD408" s="3"/>
+      <c r="BE408" s="3"/>
+    </row>
+    <row r="409" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C409" s="3"/>
       <c r="D409" s="3"/>
       <c r="E409" s="3"/>
@@ -23380,8 +25114,12 @@
       <c r="AY409" s="3"/>
       <c r="AZ409" s="3"/>
       <c r="BA409" s="3"/>
-    </row>
-    <row r="410" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB409" s="3"/>
+      <c r="BC409" s="3"/>
+      <c r="BD409" s="3"/>
+      <c r="BE409" s="3"/>
+    </row>
+    <row r="410" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C410" s="3"/>
       <c r="D410" s="3"/>
       <c r="E410" s="3"/>
@@ -23433,8 +25171,12 @@
       <c r="AY410" s="3"/>
       <c r="AZ410" s="3"/>
       <c r="BA410" s="3"/>
-    </row>
-    <row r="411" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB410" s="3"/>
+      <c r="BC410" s="3"/>
+      <c r="BD410" s="3"/>
+      <c r="BE410" s="3"/>
+    </row>
+    <row r="411" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C411" s="3"/>
       <c r="D411" s="3"/>
       <c r="E411" s="3"/>
@@ -23486,8 +25228,12 @@
       <c r="AY411" s="3"/>
       <c r="AZ411" s="3"/>
       <c r="BA411" s="3"/>
-    </row>
-    <row r="412" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB411" s="3"/>
+      <c r="BC411" s="3"/>
+      <c r="BD411" s="3"/>
+      <c r="BE411" s="3"/>
+    </row>
+    <row r="412" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C412" s="3"/>
       <c r="D412" s="3"/>
       <c r="E412" s="3"/>
@@ -23539,8 +25285,12 @@
       <c r="AY412" s="3"/>
       <c r="AZ412" s="3"/>
       <c r="BA412" s="3"/>
-    </row>
-    <row r="413" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB412" s="3"/>
+      <c r="BC412" s="3"/>
+      <c r="BD412" s="3"/>
+      <c r="BE412" s="3"/>
+    </row>
+    <row r="413" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C413" s="3"/>
       <c r="D413" s="3"/>
       <c r="E413" s="3"/>
@@ -23592,8 +25342,12 @@
       <c r="AY413" s="3"/>
       <c r="AZ413" s="3"/>
       <c r="BA413" s="3"/>
-    </row>
-    <row r="414" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB413" s="3"/>
+      <c r="BC413" s="3"/>
+      <c r="BD413" s="3"/>
+      <c r="BE413" s="3"/>
+    </row>
+    <row r="414" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C414" s="3"/>
       <c r="D414" s="3"/>
       <c r="E414" s="3"/>
@@ -23645,8 +25399,12 @@
       <c r="AY414" s="3"/>
       <c r="AZ414" s="3"/>
       <c r="BA414" s="3"/>
-    </row>
-    <row r="415" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB414" s="3"/>
+      <c r="BC414" s="3"/>
+      <c r="BD414" s="3"/>
+      <c r="BE414" s="3"/>
+    </row>
+    <row r="415" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C415" s="3"/>
       <c r="D415" s="3"/>
       <c r="E415" s="3"/>
@@ -23698,8 +25456,12 @@
       <c r="AY415" s="3"/>
       <c r="AZ415" s="3"/>
       <c r="BA415" s="3"/>
-    </row>
-    <row r="416" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB415" s="3"/>
+      <c r="BC415" s="3"/>
+      <c r="BD415" s="3"/>
+      <c r="BE415" s="3"/>
+    </row>
+    <row r="416" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C416" s="3"/>
       <c r="D416" s="3"/>
       <c r="E416" s="3"/>
@@ -23751,8 +25513,12 @@
       <c r="AY416" s="3"/>
       <c r="AZ416" s="3"/>
       <c r="BA416" s="3"/>
-    </row>
-    <row r="417" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB416" s="3"/>
+      <c r="BC416" s="3"/>
+      <c r="BD416" s="3"/>
+      <c r="BE416" s="3"/>
+    </row>
+    <row r="417" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C417" s="3"/>
       <c r="D417" s="3"/>
       <c r="E417" s="3"/>
@@ -23804,8 +25570,12 @@
       <c r="AY417" s="3"/>
       <c r="AZ417" s="3"/>
       <c r="BA417" s="3"/>
-    </row>
-    <row r="418" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB417" s="3"/>
+      <c r="BC417" s="3"/>
+      <c r="BD417" s="3"/>
+      <c r="BE417" s="3"/>
+    </row>
+    <row r="418" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C418" s="3"/>
       <c r="D418" s="3"/>
       <c r="E418" s="3"/>
@@ -23857,8 +25627,12 @@
       <c r="AY418" s="3"/>
       <c r="AZ418" s="3"/>
       <c r="BA418" s="3"/>
-    </row>
-    <row r="419" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB418" s="3"/>
+      <c r="BC418" s="3"/>
+      <c r="BD418" s="3"/>
+      <c r="BE418" s="3"/>
+    </row>
+    <row r="419" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C419" s="3"/>
       <c r="D419" s="3"/>
       <c r="E419" s="3"/>
@@ -23910,8 +25684,12 @@
       <c r="AY419" s="3"/>
       <c r="AZ419" s="3"/>
       <c r="BA419" s="3"/>
-    </row>
-    <row r="420" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB419" s="3"/>
+      <c r="BC419" s="3"/>
+      <c r="BD419" s="3"/>
+      <c r="BE419" s="3"/>
+    </row>
+    <row r="420" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C420" s="3"/>
       <c r="D420" s="3"/>
       <c r="E420" s="3"/>
@@ -23963,8 +25741,12 @@
       <c r="AY420" s="3"/>
       <c r="AZ420" s="3"/>
       <c r="BA420" s="3"/>
-    </row>
-    <row r="421" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB420" s="3"/>
+      <c r="BC420" s="3"/>
+      <c r="BD420" s="3"/>
+      <c r="BE420" s="3"/>
+    </row>
+    <row r="421" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C421" s="3"/>
       <c r="D421" s="3"/>
       <c r="E421" s="3"/>
@@ -24016,8 +25798,12 @@
       <c r="AY421" s="3"/>
       <c r="AZ421" s="3"/>
       <c r="BA421" s="3"/>
-    </row>
-    <row r="422" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB421" s="3"/>
+      <c r="BC421" s="3"/>
+      <c r="BD421" s="3"/>
+      <c r="BE421" s="3"/>
+    </row>
+    <row r="422" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C422" s="3"/>
       <c r="D422" s="3"/>
       <c r="E422" s="3"/>
@@ -24069,8 +25855,12 @@
       <c r="AY422" s="3"/>
       <c r="AZ422" s="3"/>
       <c r="BA422" s="3"/>
-    </row>
-    <row r="423" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB422" s="3"/>
+      <c r="BC422" s="3"/>
+      <c r="BD422" s="3"/>
+      <c r="BE422" s="3"/>
+    </row>
+    <row r="423" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C423" s="3"/>
       <c r="D423" s="3"/>
       <c r="E423" s="3"/>
@@ -24122,8 +25912,12 @@
       <c r="AY423" s="3"/>
       <c r="AZ423" s="3"/>
       <c r="BA423" s="3"/>
-    </row>
-    <row r="424" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB423" s="3"/>
+      <c r="BC423" s="3"/>
+      <c r="BD423" s="3"/>
+      <c r="BE423" s="3"/>
+    </row>
+    <row r="424" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C424" s="3"/>
       <c r="D424" s="3"/>
       <c r="E424" s="3"/>
@@ -24175,8 +25969,12 @@
       <c r="AY424" s="3"/>
       <c r="AZ424" s="3"/>
       <c r="BA424" s="3"/>
-    </row>
-    <row r="425" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB424" s="3"/>
+      <c r="BC424" s="3"/>
+      <c r="BD424" s="3"/>
+      <c r="BE424" s="3"/>
+    </row>
+    <row r="425" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C425" s="3"/>
       <c r="D425" s="3"/>
       <c r="E425" s="3"/>
@@ -24228,8 +26026,12 @@
       <c r="AY425" s="3"/>
       <c r="AZ425" s="3"/>
       <c r="BA425" s="3"/>
-    </row>
-    <row r="426" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB425" s="3"/>
+      <c r="BC425" s="3"/>
+      <c r="BD425" s="3"/>
+      <c r="BE425" s="3"/>
+    </row>
+    <row r="426" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C426" s="3"/>
       <c r="D426" s="3"/>
       <c r="E426" s="3"/>
@@ -24281,8 +26083,12 @@
       <c r="AY426" s="3"/>
       <c r="AZ426" s="3"/>
       <c r="BA426" s="3"/>
-    </row>
-    <row r="427" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB426" s="3"/>
+      <c r="BC426" s="3"/>
+      <c r="BD426" s="3"/>
+      <c r="BE426" s="3"/>
+    </row>
+    <row r="427" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C427" s="3"/>
       <c r="D427" s="3"/>
       <c r="E427" s="3"/>
@@ -24334,8 +26140,12 @@
       <c r="AY427" s="3"/>
       <c r="AZ427" s="3"/>
       <c r="BA427" s="3"/>
-    </row>
-    <row r="428" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB427" s="3"/>
+      <c r="BC427" s="3"/>
+      <c r="BD427" s="3"/>
+      <c r="BE427" s="3"/>
+    </row>
+    <row r="428" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C428" s="3"/>
       <c r="D428" s="3"/>
       <c r="E428" s="3"/>
@@ -24387,8 +26197,12 @@
       <c r="AY428" s="3"/>
       <c r="AZ428" s="3"/>
       <c r="BA428" s="3"/>
-    </row>
-    <row r="429" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB428" s="3"/>
+      <c r="BC428" s="3"/>
+      <c r="BD428" s="3"/>
+      <c r="BE428" s="3"/>
+    </row>
+    <row r="429" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C429" s="3"/>
       <c r="D429" s="3"/>
       <c r="E429" s="3"/>
@@ -24440,8 +26254,12 @@
       <c r="AY429" s="3"/>
       <c r="AZ429" s="3"/>
       <c r="BA429" s="3"/>
-    </row>
-    <row r="430" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB429" s="3"/>
+      <c r="BC429" s="3"/>
+      <c r="BD429" s="3"/>
+      <c r="BE429" s="3"/>
+    </row>
+    <row r="430" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C430" s="3"/>
       <c r="D430" s="3"/>
       <c r="E430" s="3"/>
@@ -24493,8 +26311,12 @@
       <c r="AY430" s="3"/>
       <c r="AZ430" s="3"/>
       <c r="BA430" s="3"/>
-    </row>
-    <row r="431" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB430" s="3"/>
+      <c r="BC430" s="3"/>
+      <c r="BD430" s="3"/>
+      <c r="BE430" s="3"/>
+    </row>
+    <row r="431" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C431" s="3"/>
       <c r="D431" s="3"/>
       <c r="E431" s="3"/>
@@ -24546,8 +26368,12 @@
       <c r="AY431" s="3"/>
       <c r="AZ431" s="3"/>
       <c r="BA431" s="3"/>
-    </row>
-    <row r="432" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB431" s="3"/>
+      <c r="BC431" s="3"/>
+      <c r="BD431" s="3"/>
+      <c r="BE431" s="3"/>
+    </row>
+    <row r="432" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C432" s="3"/>
       <c r="D432" s="3"/>
       <c r="E432" s="3"/>
@@ -24599,8 +26425,12 @@
       <c r="AY432" s="3"/>
       <c r="AZ432" s="3"/>
       <c r="BA432" s="3"/>
-    </row>
-    <row r="433" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB432" s="3"/>
+      <c r="BC432" s="3"/>
+      <c r="BD432" s="3"/>
+      <c r="BE432" s="3"/>
+    </row>
+    <row r="433" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C433" s="3"/>
       <c r="D433" s="3"/>
       <c r="E433" s="3"/>
@@ -24652,8 +26482,12 @@
       <c r="AY433" s="3"/>
       <c r="AZ433" s="3"/>
       <c r="BA433" s="3"/>
-    </row>
-    <row r="434" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB433" s="3"/>
+      <c r="BC433" s="3"/>
+      <c r="BD433" s="3"/>
+      <c r="BE433" s="3"/>
+    </row>
+    <row r="434" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C434" s="3"/>
       <c r="D434" s="3"/>
       <c r="E434" s="3"/>
@@ -24705,8 +26539,12 @@
       <c r="AY434" s="3"/>
       <c r="AZ434" s="3"/>
       <c r="BA434" s="3"/>
-    </row>
-    <row r="435" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB434" s="3"/>
+      <c r="BC434" s="3"/>
+      <c r="BD434" s="3"/>
+      <c r="BE434" s="3"/>
+    </row>
+    <row r="435" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C435" s="3"/>
       <c r="D435" s="3"/>
       <c r="E435" s="3"/>
@@ -24758,8 +26596,12 @@
       <c r="AY435" s="3"/>
       <c r="AZ435" s="3"/>
       <c r="BA435" s="3"/>
-    </row>
-    <row r="436" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB435" s="3"/>
+      <c r="BC435" s="3"/>
+      <c r="BD435" s="3"/>
+      <c r="BE435" s="3"/>
+    </row>
+    <row r="436" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C436" s="3"/>
       <c r="D436" s="3"/>
       <c r="E436" s="3"/>
@@ -24811,8 +26653,12 @@
       <c r="AY436" s="3"/>
       <c r="AZ436" s="3"/>
       <c r="BA436" s="3"/>
-    </row>
-    <row r="437" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB436" s="3"/>
+      <c r="BC436" s="3"/>
+      <c r="BD436" s="3"/>
+      <c r="BE436" s="3"/>
+    </row>
+    <row r="437" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C437" s="3"/>
       <c r="D437" s="3"/>
       <c r="E437" s="3"/>
@@ -24864,8 +26710,12 @@
       <c r="AY437" s="3"/>
       <c r="AZ437" s="3"/>
       <c r="BA437" s="3"/>
-    </row>
-    <row r="438" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB437" s="3"/>
+      <c r="BC437" s="3"/>
+      <c r="BD437" s="3"/>
+      <c r="BE437" s="3"/>
+    </row>
+    <row r="438" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C438" s="3"/>
       <c r="D438" s="3"/>
       <c r="E438" s="3"/>
@@ -24917,8 +26767,12 @@
       <c r="AY438" s="3"/>
       <c r="AZ438" s="3"/>
       <c r="BA438" s="3"/>
-    </row>
-    <row r="439" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB438" s="3"/>
+      <c r="BC438" s="3"/>
+      <c r="BD438" s="3"/>
+      <c r="BE438" s="3"/>
+    </row>
+    <row r="439" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C439" s="3"/>
       <c r="D439" s="3"/>
       <c r="E439" s="3"/>
@@ -24970,8 +26824,12 @@
       <c r="AY439" s="3"/>
       <c r="AZ439" s="3"/>
       <c r="BA439" s="3"/>
-    </row>
-    <row r="440" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB439" s="3"/>
+      <c r="BC439" s="3"/>
+      <c r="BD439" s="3"/>
+      <c r="BE439" s="3"/>
+    </row>
+    <row r="440" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C440" s="3"/>
       <c r="D440" s="3"/>
       <c r="E440" s="3"/>
@@ -25023,8 +26881,12 @@
       <c r="AY440" s="3"/>
       <c r="AZ440" s="3"/>
       <c r="BA440" s="3"/>
-    </row>
-    <row r="441" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB440" s="3"/>
+      <c r="BC440" s="3"/>
+      <c r="BD440" s="3"/>
+      <c r="BE440" s="3"/>
+    </row>
+    <row r="441" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C441" s="3"/>
       <c r="D441" s="3"/>
       <c r="E441" s="3"/>
@@ -25076,8 +26938,12 @@
       <c r="AY441" s="3"/>
       <c r="AZ441" s="3"/>
       <c r="BA441" s="3"/>
-    </row>
-    <row r="442" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB441" s="3"/>
+      <c r="BC441" s="3"/>
+      <c r="BD441" s="3"/>
+      <c r="BE441" s="3"/>
+    </row>
+    <row r="442" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C442" s="3"/>
       <c r="D442" s="3"/>
       <c r="E442" s="3"/>
@@ -25129,8 +26995,12 @@
       <c r="AY442" s="3"/>
       <c r="AZ442" s="3"/>
       <c r="BA442" s="3"/>
-    </row>
-    <row r="443" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB442" s="3"/>
+      <c r="BC442" s="3"/>
+      <c r="BD442" s="3"/>
+      <c r="BE442" s="3"/>
+    </row>
+    <row r="443" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C443" s="3"/>
       <c r="D443" s="3"/>
       <c r="E443" s="3"/>
@@ -25182,8 +27052,12 @@
       <c r="AY443" s="3"/>
       <c r="AZ443" s="3"/>
       <c r="BA443" s="3"/>
-    </row>
-    <row r="444" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB443" s="3"/>
+      <c r="BC443" s="3"/>
+      <c r="BD443" s="3"/>
+      <c r="BE443" s="3"/>
+    </row>
+    <row r="444" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C444" s="3"/>
       <c r="D444" s="3"/>
       <c r="E444" s="3"/>
@@ -25235,8 +27109,12 @@
       <c r="AY444" s="3"/>
       <c r="AZ444" s="3"/>
       <c r="BA444" s="3"/>
-    </row>
-    <row r="445" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB444" s="3"/>
+      <c r="BC444" s="3"/>
+      <c r="BD444" s="3"/>
+      <c r="BE444" s="3"/>
+    </row>
+    <row r="445" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C445" s="3"/>
       <c r="D445" s="3"/>
       <c r="E445" s="3"/>
@@ -25288,8 +27166,12 @@
       <c r="AY445" s="3"/>
       <c r="AZ445" s="3"/>
       <c r="BA445" s="3"/>
-    </row>
-    <row r="446" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB445" s="3"/>
+      <c r="BC445" s="3"/>
+      <c r="BD445" s="3"/>
+      <c r="BE445" s="3"/>
+    </row>
+    <row r="446" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C446" s="3"/>
       <c r="D446" s="3"/>
       <c r="E446" s="3"/>
@@ -25341,8 +27223,12 @@
       <c r="AY446" s="3"/>
       <c r="AZ446" s="3"/>
       <c r="BA446" s="3"/>
-    </row>
-    <row r="447" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB446" s="3"/>
+      <c r="BC446" s="3"/>
+      <c r="BD446" s="3"/>
+      <c r="BE446" s="3"/>
+    </row>
+    <row r="447" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C447" s="3"/>
       <c r="D447" s="3"/>
       <c r="E447" s="3"/>
@@ -25394,8 +27280,12 @@
       <c r="AY447" s="3"/>
       <c r="AZ447" s="3"/>
       <c r="BA447" s="3"/>
-    </row>
-    <row r="448" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB447" s="3"/>
+      <c r="BC447" s="3"/>
+      <c r="BD447" s="3"/>
+      <c r="BE447" s="3"/>
+    </row>
+    <row r="448" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C448" s="3"/>
       <c r="D448" s="3"/>
       <c r="E448" s="3"/>
@@ -25447,8 +27337,12 @@
       <c r="AY448" s="3"/>
       <c r="AZ448" s="3"/>
       <c r="BA448" s="3"/>
-    </row>
-    <row r="449" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB448" s="3"/>
+      <c r="BC448" s="3"/>
+      <c r="BD448" s="3"/>
+      <c r="BE448" s="3"/>
+    </row>
+    <row r="449" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C449" s="3"/>
       <c r="D449" s="3"/>
       <c r="E449" s="3"/>
@@ -25500,8 +27394,12 @@
       <c r="AY449" s="3"/>
       <c r="AZ449" s="3"/>
       <c r="BA449" s="3"/>
-    </row>
-    <row r="450" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB449" s="3"/>
+      <c r="BC449" s="3"/>
+      <c r="BD449" s="3"/>
+      <c r="BE449" s="3"/>
+    </row>
+    <row r="450" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C450" s="3"/>
       <c r="D450" s="3"/>
       <c r="E450" s="3"/>
@@ -25553,8 +27451,12 @@
       <c r="AY450" s="3"/>
       <c r="AZ450" s="3"/>
       <c r="BA450" s="3"/>
-    </row>
-    <row r="451" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB450" s="3"/>
+      <c r="BC450" s="3"/>
+      <c r="BD450" s="3"/>
+      <c r="BE450" s="3"/>
+    </row>
+    <row r="451" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C451" s="3"/>
       <c r="D451" s="3"/>
       <c r="E451" s="3"/>
@@ -25606,8 +27508,12 @@
       <c r="AY451" s="3"/>
       <c r="AZ451" s="3"/>
       <c r="BA451" s="3"/>
-    </row>
-    <row r="452" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB451" s="3"/>
+      <c r="BC451" s="3"/>
+      <c r="BD451" s="3"/>
+      <c r="BE451" s="3"/>
+    </row>
+    <row r="452" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C452" s="3"/>
       <c r="D452" s="3"/>
       <c r="E452" s="3"/>
@@ -25659,8 +27565,12 @@
       <c r="AY452" s="3"/>
       <c r="AZ452" s="3"/>
       <c r="BA452" s="3"/>
-    </row>
-    <row r="453" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB452" s="3"/>
+      <c r="BC452" s="3"/>
+      <c r="BD452" s="3"/>
+      <c r="BE452" s="3"/>
+    </row>
+    <row r="453" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C453" s="3"/>
       <c r="D453" s="3"/>
       <c r="E453" s="3"/>
@@ -25712,8 +27622,12 @@
       <c r="AY453" s="3"/>
       <c r="AZ453" s="3"/>
       <c r="BA453" s="3"/>
-    </row>
-    <row r="454" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB453" s="3"/>
+      <c r="BC453" s="3"/>
+      <c r="BD453" s="3"/>
+      <c r="BE453" s="3"/>
+    </row>
+    <row r="454" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C454" s="3"/>
       <c r="D454" s="3"/>
       <c r="E454" s="3"/>
@@ -25765,8 +27679,12 @@
       <c r="AY454" s="3"/>
       <c r="AZ454" s="3"/>
       <c r="BA454" s="3"/>
-    </row>
-    <row r="455" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB454" s="3"/>
+      <c r="BC454" s="3"/>
+      <c r="BD454" s="3"/>
+      <c r="BE454" s="3"/>
+    </row>
+    <row r="455" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C455" s="3"/>
       <c r="D455" s="3"/>
       <c r="E455" s="3"/>
@@ -25818,8 +27736,12 @@
       <c r="AY455" s="3"/>
       <c r="AZ455" s="3"/>
       <c r="BA455" s="3"/>
-    </row>
-    <row r="456" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB455" s="3"/>
+      <c r="BC455" s="3"/>
+      <c r="BD455" s="3"/>
+      <c r="BE455" s="3"/>
+    </row>
+    <row r="456" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C456" s="3"/>
       <c r="D456" s="3"/>
       <c r="E456" s="3"/>
@@ -25871,8 +27793,12 @@
       <c r="AY456" s="3"/>
       <c r="AZ456" s="3"/>
       <c r="BA456" s="3"/>
-    </row>
-    <row r="457" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB456" s="3"/>
+      <c r="BC456" s="3"/>
+      <c r="BD456" s="3"/>
+      <c r="BE456" s="3"/>
+    </row>
+    <row r="457" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C457" s="3"/>
       <c r="D457" s="3"/>
       <c r="E457" s="3"/>
@@ -25924,8 +27850,12 @@
       <c r="AY457" s="3"/>
       <c r="AZ457" s="3"/>
       <c r="BA457" s="3"/>
-    </row>
-    <row r="458" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB457" s="3"/>
+      <c r="BC457" s="3"/>
+      <c r="BD457" s="3"/>
+      <c r="BE457" s="3"/>
+    </row>
+    <row r="458" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C458" s="3"/>
       <c r="D458" s="3"/>
       <c r="E458" s="3"/>
@@ -25977,8 +27907,12 @@
       <c r="AY458" s="3"/>
       <c r="AZ458" s="3"/>
       <c r="BA458" s="3"/>
-    </row>
-    <row r="459" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB458" s="3"/>
+      <c r="BC458" s="3"/>
+      <c r="BD458" s="3"/>
+      <c r="BE458" s="3"/>
+    </row>
+    <row r="459" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C459" s="3"/>
       <c r="D459" s="3"/>
       <c r="E459" s="3"/>
@@ -26030,8 +27964,12 @@
       <c r="AY459" s="3"/>
       <c r="AZ459" s="3"/>
       <c r="BA459" s="3"/>
-    </row>
-    <row r="460" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB459" s="3"/>
+      <c r="BC459" s="3"/>
+      <c r="BD459" s="3"/>
+      <c r="BE459" s="3"/>
+    </row>
+    <row r="460" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C460" s="3"/>
       <c r="D460" s="3"/>
       <c r="E460" s="3"/>
@@ -26083,8 +28021,12 @@
       <c r="AY460" s="3"/>
       <c r="AZ460" s="3"/>
       <c r="BA460" s="3"/>
-    </row>
-    <row r="461" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB460" s="3"/>
+      <c r="BC460" s="3"/>
+      <c r="BD460" s="3"/>
+      <c r="BE460" s="3"/>
+    </row>
+    <row r="461" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C461" s="3"/>
       <c r="D461" s="3"/>
       <c r="E461" s="3"/>
@@ -26136,8 +28078,12 @@
       <c r="AY461" s="3"/>
       <c r="AZ461" s="3"/>
       <c r="BA461" s="3"/>
-    </row>
-    <row r="462" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB461" s="3"/>
+      <c r="BC461" s="3"/>
+      <c r="BD461" s="3"/>
+      <c r="BE461" s="3"/>
+    </row>
+    <row r="462" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C462" s="3"/>
       <c r="D462" s="3"/>
       <c r="E462" s="3"/>
@@ -26189,8 +28135,12 @@
       <c r="AY462" s="3"/>
       <c r="AZ462" s="3"/>
       <c r="BA462" s="3"/>
-    </row>
-    <row r="463" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB462" s="3"/>
+      <c r="BC462" s="3"/>
+      <c r="BD462" s="3"/>
+      <c r="BE462" s="3"/>
+    </row>
+    <row r="463" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C463" s="3"/>
       <c r="D463" s="3"/>
       <c r="E463" s="3"/>
@@ -26242,8 +28192,12 @@
       <c r="AY463" s="3"/>
       <c r="AZ463" s="3"/>
       <c r="BA463" s="3"/>
-    </row>
-    <row r="464" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB463" s="3"/>
+      <c r="BC463" s="3"/>
+      <c r="BD463" s="3"/>
+      <c r="BE463" s="3"/>
+    </row>
+    <row r="464" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C464" s="3"/>
       <c r="D464" s="3"/>
       <c r="E464" s="3"/>
@@ -26295,8 +28249,12 @@
       <c r="AY464" s="3"/>
       <c r="AZ464" s="3"/>
       <c r="BA464" s="3"/>
-    </row>
-    <row r="465" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB464" s="3"/>
+      <c r="BC464" s="3"/>
+      <c r="BD464" s="3"/>
+      <c r="BE464" s="3"/>
+    </row>
+    <row r="465" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C465" s="3"/>
       <c r="D465" s="3"/>
       <c r="E465" s="3"/>
@@ -26348,8 +28306,12 @@
       <c r="AY465" s="3"/>
       <c r="AZ465" s="3"/>
       <c r="BA465" s="3"/>
-    </row>
-    <row r="466" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB465" s="3"/>
+      <c r="BC465" s="3"/>
+      <c r="BD465" s="3"/>
+      <c r="BE465" s="3"/>
+    </row>
+    <row r="466" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C466" s="3"/>
       <c r="D466" s="3"/>
       <c r="E466" s="3"/>
@@ -26401,8 +28363,12 @@
       <c r="AY466" s="3"/>
       <c r="AZ466" s="3"/>
       <c r="BA466" s="3"/>
-    </row>
-    <row r="467" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB466" s="3"/>
+      <c r="BC466" s="3"/>
+      <c r="BD466" s="3"/>
+      <c r="BE466" s="3"/>
+    </row>
+    <row r="467" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C467" s="3"/>
       <c r="D467" s="3"/>
       <c r="E467" s="3"/>
@@ -26454,8 +28420,12 @@
       <c r="AY467" s="3"/>
       <c r="AZ467" s="3"/>
       <c r="BA467" s="3"/>
-    </row>
-    <row r="468" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB467" s="3"/>
+      <c r="BC467" s="3"/>
+      <c r="BD467" s="3"/>
+      <c r="BE467" s="3"/>
+    </row>
+    <row r="468" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C468" s="3"/>
       <c r="D468" s="3"/>
       <c r="E468" s="3"/>
@@ -26507,8 +28477,12 @@
       <c r="AY468" s="3"/>
       <c r="AZ468" s="3"/>
       <c r="BA468" s="3"/>
-    </row>
-    <row r="469" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB468" s="3"/>
+      <c r="BC468" s="3"/>
+      <c r="BD468" s="3"/>
+      <c r="BE468" s="3"/>
+    </row>
+    <row r="469" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C469" s="3"/>
       <c r="D469" s="3"/>
       <c r="E469" s="3"/>
@@ -26560,8 +28534,12 @@
       <c r="AY469" s="3"/>
       <c r="AZ469" s="3"/>
       <c r="BA469" s="3"/>
-    </row>
-    <row r="470" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB469" s="3"/>
+      <c r="BC469" s="3"/>
+      <c r="BD469" s="3"/>
+      <c r="BE469" s="3"/>
+    </row>
+    <row r="470" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C470" s="3"/>
       <c r="D470" s="3"/>
       <c r="E470" s="3"/>
@@ -26613,8 +28591,12 @@
       <c r="AY470" s="3"/>
       <c r="AZ470" s="3"/>
       <c r="BA470" s="3"/>
-    </row>
-    <row r="471" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB470" s="3"/>
+      <c r="BC470" s="3"/>
+      <c r="BD470" s="3"/>
+      <c r="BE470" s="3"/>
+    </row>
+    <row r="471" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C471" s="3"/>
       <c r="D471" s="3"/>
       <c r="E471" s="3"/>
@@ -26666,8 +28648,12 @@
       <c r="AY471" s="3"/>
       <c r="AZ471" s="3"/>
       <c r="BA471" s="3"/>
-    </row>
-    <row r="472" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB471" s="3"/>
+      <c r="BC471" s="3"/>
+      <c r="BD471" s="3"/>
+      <c r="BE471" s="3"/>
+    </row>
+    <row r="472" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C472" s="3"/>
       <c r="D472" s="3"/>
       <c r="E472" s="3"/>
@@ -26719,8 +28705,12 @@
       <c r="AY472" s="3"/>
       <c r="AZ472" s="3"/>
       <c r="BA472" s="3"/>
-    </row>
-    <row r="473" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB472" s="3"/>
+      <c r="BC472" s="3"/>
+      <c r="BD472" s="3"/>
+      <c r="BE472" s="3"/>
+    </row>
+    <row r="473" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C473" s="3"/>
       <c r="D473" s="3"/>
       <c r="E473" s="3"/>
@@ -26772,8 +28762,12 @@
       <c r="AY473" s="3"/>
       <c r="AZ473" s="3"/>
       <c r="BA473" s="3"/>
-    </row>
-    <row r="474" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB473" s="3"/>
+      <c r="BC473" s="3"/>
+      <c r="BD473" s="3"/>
+      <c r="BE473" s="3"/>
+    </row>
+    <row r="474" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C474" s="3"/>
       <c r="D474" s="3"/>
       <c r="E474" s="3"/>
@@ -26825,8 +28819,12 @@
       <c r="AY474" s="3"/>
       <c r="AZ474" s="3"/>
       <c r="BA474" s="3"/>
-    </row>
-    <row r="475" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB474" s="3"/>
+      <c r="BC474" s="3"/>
+      <c r="BD474" s="3"/>
+      <c r="BE474" s="3"/>
+    </row>
+    <row r="475" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C475" s="3"/>
       <c r="D475" s="3"/>
       <c r="E475" s="3"/>
@@ -26878,8 +28876,12 @@
       <c r="AY475" s="3"/>
       <c r="AZ475" s="3"/>
       <c r="BA475" s="3"/>
-    </row>
-    <row r="476" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB475" s="3"/>
+      <c r="BC475" s="3"/>
+      <c r="BD475" s="3"/>
+      <c r="BE475" s="3"/>
+    </row>
+    <row r="476" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C476" s="3"/>
       <c r="D476" s="3"/>
       <c r="E476" s="3"/>
@@ -26931,8 +28933,12 @@
       <c r="AY476" s="3"/>
       <c r="AZ476" s="3"/>
       <c r="BA476" s="3"/>
-    </row>
-    <row r="477" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB476" s="3"/>
+      <c r="BC476" s="3"/>
+      <c r="BD476" s="3"/>
+      <c r="BE476" s="3"/>
+    </row>
+    <row r="477" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C477" s="3"/>
       <c r="D477" s="3"/>
       <c r="E477" s="3"/>
@@ -26984,8 +28990,12 @@
       <c r="AY477" s="3"/>
       <c r="AZ477" s="3"/>
       <c r="BA477" s="3"/>
-    </row>
-    <row r="478" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB477" s="3"/>
+      <c r="BC477" s="3"/>
+      <c r="BD477" s="3"/>
+      <c r="BE477" s="3"/>
+    </row>
+    <row r="478" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C478" s="3"/>
       <c r="D478" s="3"/>
       <c r="E478" s="3"/>
@@ -27037,8 +29047,12 @@
       <c r="AY478" s="3"/>
       <c r="AZ478" s="3"/>
       <c r="BA478" s="3"/>
-    </row>
-    <row r="479" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB478" s="3"/>
+      <c r="BC478" s="3"/>
+      <c r="BD478" s="3"/>
+      <c r="BE478" s="3"/>
+    </row>
+    <row r="479" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C479" s="3"/>
       <c r="D479" s="3"/>
       <c r="E479" s="3"/>
@@ -27090,8 +29104,12 @@
       <c r="AY479" s="3"/>
       <c r="AZ479" s="3"/>
       <c r="BA479" s="3"/>
-    </row>
-    <row r="480" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB479" s="3"/>
+      <c r="BC479" s="3"/>
+      <c r="BD479" s="3"/>
+      <c r="BE479" s="3"/>
+    </row>
+    <row r="480" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C480" s="3"/>
       <c r="D480" s="3"/>
       <c r="E480" s="3"/>
@@ -27143,8 +29161,12 @@
       <c r="AY480" s="3"/>
       <c r="AZ480" s="3"/>
       <c r="BA480" s="3"/>
-    </row>
-    <row r="481" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB480" s="3"/>
+      <c r="BC480" s="3"/>
+      <c r="BD480" s="3"/>
+      <c r="BE480" s="3"/>
+    </row>
+    <row r="481" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C481" s="3"/>
       <c r="D481" s="3"/>
       <c r="E481" s="3"/>
@@ -27196,8 +29218,12 @@
       <c r="AY481" s="3"/>
       <c r="AZ481" s="3"/>
       <c r="BA481" s="3"/>
-    </row>
-    <row r="482" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB481" s="3"/>
+      <c r="BC481" s="3"/>
+      <c r="BD481" s="3"/>
+      <c r="BE481" s="3"/>
+    </row>
+    <row r="482" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C482" s="3"/>
       <c r="D482" s="3"/>
       <c r="E482" s="3"/>
@@ -27249,8 +29275,12 @@
       <c r="AY482" s="3"/>
       <c r="AZ482" s="3"/>
       <c r="BA482" s="3"/>
-    </row>
-    <row r="483" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB482" s="3"/>
+      <c r="BC482" s="3"/>
+      <c r="BD482" s="3"/>
+      <c r="BE482" s="3"/>
+    </row>
+    <row r="483" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C483" s="3"/>
       <c r="D483" s="3"/>
       <c r="E483" s="3"/>
@@ -27302,8 +29332,12 @@
       <c r="AY483" s="3"/>
       <c r="AZ483" s="3"/>
       <c r="BA483" s="3"/>
-    </row>
-    <row r="484" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB483" s="3"/>
+      <c r="BC483" s="3"/>
+      <c r="BD483" s="3"/>
+      <c r="BE483" s="3"/>
+    </row>
+    <row r="484" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C484" s="3"/>
       <c r="D484" s="3"/>
       <c r="E484" s="3"/>
@@ -27355,8 +29389,12 @@
       <c r="AY484" s="3"/>
       <c r="AZ484" s="3"/>
       <c r="BA484" s="3"/>
-    </row>
-    <row r="485" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB484" s="3"/>
+      <c r="BC484" s="3"/>
+      <c r="BD484" s="3"/>
+      <c r="BE484" s="3"/>
+    </row>
+    <row r="485" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C485" s="3"/>
       <c r="D485" s="3"/>
       <c r="E485" s="3"/>
@@ -27408,8 +29446,12 @@
       <c r="AY485" s="3"/>
       <c r="AZ485" s="3"/>
       <c r="BA485" s="3"/>
-    </row>
-    <row r="486" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB485" s="3"/>
+      <c r="BC485" s="3"/>
+      <c r="BD485" s="3"/>
+      <c r="BE485" s="3"/>
+    </row>
+    <row r="486" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C486" s="3"/>
       <c r="D486" s="3"/>
       <c r="E486" s="3"/>
@@ -27461,8 +29503,12 @@
       <c r="AY486" s="3"/>
       <c r="AZ486" s="3"/>
       <c r="BA486" s="3"/>
-    </row>
-    <row r="487" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB486" s="3"/>
+      <c r="BC486" s="3"/>
+      <c r="BD486" s="3"/>
+      <c r="BE486" s="3"/>
+    </row>
+    <row r="487" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C487" s="3"/>
       <c r="D487" s="3"/>
       <c r="E487" s="3"/>
@@ -27514,8 +29560,12 @@
       <c r="AY487" s="3"/>
       <c r="AZ487" s="3"/>
       <c r="BA487" s="3"/>
-    </row>
-    <row r="488" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB487" s="3"/>
+      <c r="BC487" s="3"/>
+      <c r="BD487" s="3"/>
+      <c r="BE487" s="3"/>
+    </row>
+    <row r="488" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C488" s="3"/>
       <c r="D488" s="3"/>
       <c r="E488" s="3"/>
@@ -27567,8 +29617,12 @@
       <c r="AY488" s="3"/>
       <c r="AZ488" s="3"/>
       <c r="BA488" s="3"/>
-    </row>
-    <row r="489" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB488" s="3"/>
+      <c r="BC488" s="3"/>
+      <c r="BD488" s="3"/>
+      <c r="BE488" s="3"/>
+    </row>
+    <row r="489" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C489" s="3"/>
       <c r="D489" s="3"/>
       <c r="E489" s="3"/>
@@ -27620,8 +29674,12 @@
       <c r="AY489" s="3"/>
       <c r="AZ489" s="3"/>
       <c r="BA489" s="3"/>
-    </row>
-    <row r="490" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB489" s="3"/>
+      <c r="BC489" s="3"/>
+      <c r="BD489" s="3"/>
+      <c r="BE489" s="3"/>
+    </row>
+    <row r="490" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C490" s="3"/>
       <c r="D490" s="3"/>
       <c r="E490" s="3"/>
@@ -27673,8 +29731,12 @@
       <c r="AY490" s="3"/>
       <c r="AZ490" s="3"/>
       <c r="BA490" s="3"/>
-    </row>
-    <row r="491" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB490" s="3"/>
+      <c r="BC490" s="3"/>
+      <c r="BD490" s="3"/>
+      <c r="BE490" s="3"/>
+    </row>
+    <row r="491" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C491" s="3"/>
       <c r="D491" s="3"/>
       <c r="E491" s="3"/>
@@ -27726,8 +29788,12 @@
       <c r="AY491" s="3"/>
       <c r="AZ491" s="3"/>
       <c r="BA491" s="3"/>
-    </row>
-    <row r="492" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB491" s="3"/>
+      <c r="BC491" s="3"/>
+      <c r="BD491" s="3"/>
+      <c r="BE491" s="3"/>
+    </row>
+    <row r="492" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C492" s="3"/>
       <c r="D492" s="3"/>
       <c r="E492" s="3"/>
@@ -27779,8 +29845,12 @@
       <c r="AY492" s="3"/>
       <c r="AZ492" s="3"/>
       <c r="BA492" s="3"/>
-    </row>
-    <row r="493" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB492" s="3"/>
+      <c r="BC492" s="3"/>
+      <c r="BD492" s="3"/>
+      <c r="BE492" s="3"/>
+    </row>
+    <row r="493" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C493" s="3"/>
       <c r="D493" s="3"/>
       <c r="E493" s="3"/>
@@ -27832,8 +29902,12 @@
       <c r="AY493" s="3"/>
       <c r="AZ493" s="3"/>
       <c r="BA493" s="3"/>
-    </row>
-    <row r="494" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB493" s="3"/>
+      <c r="BC493" s="3"/>
+      <c r="BD493" s="3"/>
+      <c r="BE493" s="3"/>
+    </row>
+    <row r="494" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C494" s="3"/>
       <c r="D494" s="3"/>
       <c r="E494" s="3"/>
@@ -27885,8 +29959,12 @@
       <c r="AY494" s="3"/>
       <c r="AZ494" s="3"/>
       <c r="BA494" s="3"/>
-    </row>
-    <row r="495" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB494" s="3"/>
+      <c r="BC494" s="3"/>
+      <c r="BD494" s="3"/>
+      <c r="BE494" s="3"/>
+    </row>
+    <row r="495" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C495" s="3"/>
       <c r="D495" s="3"/>
       <c r="E495" s="3"/>
@@ -27938,8 +30016,12 @@
       <c r="AY495" s="3"/>
       <c r="AZ495" s="3"/>
       <c r="BA495" s="3"/>
-    </row>
-    <row r="496" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB495" s="3"/>
+      <c r="BC495" s="3"/>
+      <c r="BD495" s="3"/>
+      <c r="BE495" s="3"/>
+    </row>
+    <row r="496" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C496" s="3"/>
       <c r="D496" s="3"/>
       <c r="E496" s="3"/>
@@ -27991,8 +30073,12 @@
       <c r="AY496" s="3"/>
       <c r="AZ496" s="3"/>
       <c r="BA496" s="3"/>
-    </row>
-    <row r="497" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB496" s="3"/>
+      <c r="BC496" s="3"/>
+      <c r="BD496" s="3"/>
+      <c r="BE496" s="3"/>
+    </row>
+    <row r="497" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C497" s="3"/>
       <c r="D497" s="3"/>
       <c r="E497" s="3"/>
@@ -28044,8 +30130,12 @@
       <c r="AY497" s="3"/>
       <c r="AZ497" s="3"/>
       <c r="BA497" s="3"/>
-    </row>
-    <row r="498" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB497" s="3"/>
+      <c r="BC497" s="3"/>
+      <c r="BD497" s="3"/>
+      <c r="BE497" s="3"/>
+    </row>
+    <row r="498" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C498" s="3"/>
       <c r="D498" s="3"/>
       <c r="E498" s="3"/>
@@ -28097,8 +30187,12 @@
       <c r="AY498" s="3"/>
       <c r="AZ498" s="3"/>
       <c r="BA498" s="3"/>
-    </row>
-    <row r="499" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB498" s="3"/>
+      <c r="BC498" s="3"/>
+      <c r="BD498" s="3"/>
+      <c r="BE498" s="3"/>
+    </row>
+    <row r="499" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C499" s="3"/>
       <c r="D499" s="3"/>
       <c r="E499" s="3"/>
@@ -28150,8 +30244,12 @@
       <c r="AY499" s="3"/>
       <c r="AZ499" s="3"/>
       <c r="BA499" s="3"/>
-    </row>
-    <row r="500" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB499" s="3"/>
+      <c r="BC499" s="3"/>
+      <c r="BD499" s="3"/>
+      <c r="BE499" s="3"/>
+    </row>
+    <row r="500" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C500" s="3"/>
       <c r="D500" s="3"/>
       <c r="E500" s="3"/>
@@ -28203,8 +30301,12 @@
       <c r="AY500" s="3"/>
       <c r="AZ500" s="3"/>
       <c r="BA500" s="3"/>
-    </row>
-    <row r="501" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB500" s="3"/>
+      <c r="BC500" s="3"/>
+      <c r="BD500" s="3"/>
+      <c r="BE500" s="3"/>
+    </row>
+    <row r="501" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C501" s="3"/>
       <c r="D501" s="3"/>
       <c r="E501" s="3"/>
@@ -28256,8 +30358,12 @@
       <c r="AY501" s="3"/>
       <c r="AZ501" s="3"/>
       <c r="BA501" s="3"/>
-    </row>
-    <row r="502" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB501" s="3"/>
+      <c r="BC501" s="3"/>
+      <c r="BD501" s="3"/>
+      <c r="BE501" s="3"/>
+    </row>
+    <row r="502" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C502" s="3"/>
       <c r="D502" s="3"/>
       <c r="E502" s="3"/>
@@ -28309,8 +30415,12 @@
       <c r="AY502" s="3"/>
       <c r="AZ502" s="3"/>
       <c r="BA502" s="3"/>
-    </row>
-    <row r="503" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB502" s="3"/>
+      <c r="BC502" s="3"/>
+      <c r="BD502" s="3"/>
+      <c r="BE502" s="3"/>
+    </row>
+    <row r="503" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C503" s="3"/>
       <c r="D503" s="3"/>
       <c r="E503" s="3"/>
@@ -28362,8 +30472,12 @@
       <c r="AY503" s="3"/>
       <c r="AZ503" s="3"/>
       <c r="BA503" s="3"/>
-    </row>
-    <row r="504" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB503" s="3"/>
+      <c r="BC503" s="3"/>
+      <c r="BD503" s="3"/>
+      <c r="BE503" s="3"/>
+    </row>
+    <row r="504" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C504" s="3"/>
       <c r="D504" s="3"/>
       <c r="E504" s="3"/>
@@ -28415,8 +30529,12 @@
       <c r="AY504" s="3"/>
       <c r="AZ504" s="3"/>
       <c r="BA504" s="3"/>
-    </row>
-    <row r="505" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB504" s="3"/>
+      <c r="BC504" s="3"/>
+      <c r="BD504" s="3"/>
+      <c r="BE504" s="3"/>
+    </row>
+    <row r="505" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C505" s="3"/>
       <c r="D505" s="3"/>
       <c r="E505" s="3"/>
@@ -28468,8 +30586,12 @@
       <c r="AY505" s="3"/>
       <c r="AZ505" s="3"/>
       <c r="BA505" s="3"/>
-    </row>
-    <row r="506" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB505" s="3"/>
+      <c r="BC505" s="3"/>
+      <c r="BD505" s="3"/>
+      <c r="BE505" s="3"/>
+    </row>
+    <row r="506" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C506" s="3"/>
       <c r="D506" s="3"/>
       <c r="E506" s="3"/>
@@ -28521,8 +30643,12 @@
       <c r="AY506" s="3"/>
       <c r="AZ506" s="3"/>
       <c r="BA506" s="3"/>
-    </row>
-    <row r="507" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB506" s="3"/>
+      <c r="BC506" s="3"/>
+      <c r="BD506" s="3"/>
+      <c r="BE506" s="3"/>
+    </row>
+    <row r="507" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C507" s="3"/>
       <c r="D507" s="3"/>
       <c r="E507" s="3"/>
@@ -28574,8 +30700,12 @@
       <c r="AY507" s="3"/>
       <c r="AZ507" s="3"/>
       <c r="BA507" s="3"/>
-    </row>
-    <row r="508" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB507" s="3"/>
+      <c r="BC507" s="3"/>
+      <c r="BD507" s="3"/>
+      <c r="BE507" s="3"/>
+    </row>
+    <row r="508" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C508" s="3"/>
       <c r="D508" s="3"/>
       <c r="E508" s="3"/>
@@ -28627,8 +30757,12 @@
       <c r="AY508" s="3"/>
       <c r="AZ508" s="3"/>
       <c r="BA508" s="3"/>
-    </row>
-    <row r="509" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB508" s="3"/>
+      <c r="BC508" s="3"/>
+      <c r="BD508" s="3"/>
+      <c r="BE508" s="3"/>
+    </row>
+    <row r="509" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C509" s="3"/>
       <c r="D509" s="3"/>
       <c r="E509" s="3"/>
@@ -28680,8 +30814,12 @@
       <c r="AY509" s="3"/>
       <c r="AZ509" s="3"/>
       <c r="BA509" s="3"/>
-    </row>
-    <row r="510" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB509" s="3"/>
+      <c r="BC509" s="3"/>
+      <c r="BD509" s="3"/>
+      <c r="BE509" s="3"/>
+    </row>
+    <row r="510" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C510" s="3"/>
       <c r="D510" s="3"/>
       <c r="E510" s="3"/>
@@ -28733,8 +30871,12 @@
       <c r="AY510" s="3"/>
       <c r="AZ510" s="3"/>
       <c r="BA510" s="3"/>
-    </row>
-    <row r="511" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB510" s="3"/>
+      <c r="BC510" s="3"/>
+      <c r="BD510" s="3"/>
+      <c r="BE510" s="3"/>
+    </row>
+    <row r="511" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C511" s="3"/>
       <c r="D511" s="3"/>
       <c r="E511" s="3"/>
@@ -28786,8 +30928,12 @@
       <c r="AY511" s="3"/>
       <c r="AZ511" s="3"/>
       <c r="BA511" s="3"/>
-    </row>
-    <row r="512" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB511" s="3"/>
+      <c r="BC511" s="3"/>
+      <c r="BD511" s="3"/>
+      <c r="BE511" s="3"/>
+    </row>
+    <row r="512" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C512" s="3"/>
       <c r="D512" s="3"/>
       <c r="E512" s="3"/>
@@ -28839,8 +30985,12 @@
       <c r="AY512" s="3"/>
       <c r="AZ512" s="3"/>
       <c r="BA512" s="3"/>
-    </row>
-    <row r="513" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB512" s="3"/>
+      <c r="BC512" s="3"/>
+      <c r="BD512" s="3"/>
+      <c r="BE512" s="3"/>
+    </row>
+    <row r="513" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C513" s="3"/>
       <c r="D513" s="3"/>
       <c r="E513" s="3"/>
@@ -28892,8 +31042,12 @@
       <c r="AY513" s="3"/>
       <c r="AZ513" s="3"/>
       <c r="BA513" s="3"/>
-    </row>
-    <row r="514" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB513" s="3"/>
+      <c r="BC513" s="3"/>
+      <c r="BD513" s="3"/>
+      <c r="BE513" s="3"/>
+    </row>
+    <row r="514" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C514" s="3"/>
       <c r="D514" s="3"/>
       <c r="E514" s="3"/>
@@ -28945,8 +31099,12 @@
       <c r="AY514" s="3"/>
       <c r="AZ514" s="3"/>
       <c r="BA514" s="3"/>
-    </row>
-    <row r="515" spans="3:53" x14ac:dyDescent="0.2">
+      <c r="BB514" s="3"/>
+      <c r="BC514" s="3"/>
+      <c r="BD514" s="3"/>
+      <c r="BE514" s="3"/>
+    </row>
+    <row r="515" spans="3:57" x14ac:dyDescent="0.2">
       <c r="C515" s="3"/>
       <c r="D515" s="3"/>
       <c r="E515" s="3"/>
@@ -28998,6 +31156,10 @@
       <c r="AY515" s="3"/>
       <c r="AZ515" s="3"/>
       <c r="BA515" s="3"/>
+      <c r="BB515" s="3"/>
+      <c r="BC515" s="3"/>
+      <c r="BD515" s="3"/>
+      <c r="BE515" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
